--- a/quizzes/sculpture-17e.xlsx
+++ b/quizzes/sculpture-17e.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers simplifiés\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31CDD984-5EF6-4DBA-A1F7-E96C38E7454C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -1102,7 +1108,7 @@
     <t>Résidence de Munich</t>
   </si>
   <si>
-    <t xml:space="preserve"> Basilique Santa Maria della Salute</t>
+    <t> Basilique Santa Maria della Salute</t>
   </si>
   <si>
     <t>Trafalgar square</t>
@@ -1429,7 +1435,7 @@
     <t>Buste de Michel-Ange Buonarroti le Jeune</t>
   </si>
   <si>
-    <t xml:space="preserve">L'Apparition de la Vierge à saint Andrea Corsini </t>
+    <t>L'Apparition de la Vierge à saint Andrea Corsini </t>
   </si>
   <si>
     <t>Décor sculpté des stalles</t>
@@ -2473,8 +2479,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2519,18 +2525,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2568,7 +2582,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -2602,6 +2616,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2636,9 +2651,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2811,11 +2827,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X125"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2889,7 +2905,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -2933,7 +2949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -2974,7 +2990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -3024,7 +3040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -3068,7 +3084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -3115,7 +3131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -3165,7 +3181,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -3215,7 +3231,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -3256,7 +3272,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -3300,7 +3316,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -3353,7 +3369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -3400,7 +3416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -3450,7 +3466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -3497,7 +3513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -3544,7 +3560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -3591,7 +3607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -3638,7 +3654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -3688,7 +3704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -3741,7 +3757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -3794,7 +3810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>27</v>
       </c>
@@ -3841,7 +3857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -3888,7 +3904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -3941,7 +3957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -3988,7 +4004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -4041,7 +4057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -4091,7 +4107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -4141,7 +4157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -4194,7 +4210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -4244,7 +4260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -4297,7 +4313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>27</v>
       </c>
@@ -4344,7 +4360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -4397,7 +4413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>27</v>
       </c>
@@ -4450,7 +4466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>27</v>
       </c>
@@ -4497,7 +4513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>27</v>
       </c>
@@ -4553,7 +4569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>27</v>
       </c>
@@ -4600,7 +4616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>28</v>
       </c>
@@ -4647,7 +4663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>29</v>
       </c>
@@ -4691,7 +4707,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>30</v>
       </c>
@@ -4735,7 +4751,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>31</v>
       </c>
@@ -4779,7 +4795,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>32</v>
       </c>
@@ -4826,7 +4842,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>33</v>
       </c>
@@ -4876,7 +4892,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>34</v>
       </c>
@@ -4923,7 +4939,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>34</v>
       </c>
@@ -4973,7 +4989,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>35</v>
       </c>
@@ -5023,7 +5039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>35</v>
       </c>
@@ -5070,7 +5086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>35</v>
       </c>
@@ -5114,7 +5130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>35</v>
       </c>
@@ -5164,7 +5180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>35</v>
       </c>
@@ -5217,7 +5233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>35</v>
       </c>
@@ -5267,7 +5283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>35</v>
       </c>
@@ -5311,7 +5327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>35</v>
       </c>
@@ -5364,7 +5380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>35</v>
       </c>
@@ -5417,7 +5433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>36</v>
       </c>
@@ -5464,7 +5480,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>36</v>
       </c>
@@ -5508,7 +5524,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>37</v>
       </c>
@@ -5555,7 +5571,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>38</v>
       </c>
@@ -5599,7 +5615,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>38</v>
       </c>
@@ -5649,7 +5665,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>38</v>
       </c>
@@ -5699,7 +5715,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>38</v>
       </c>
@@ -5740,7 +5756,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>39</v>
       </c>
@@ -5790,7 +5806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>40</v>
       </c>
@@ -5840,7 +5856,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:24">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>40</v>
       </c>
@@ -5887,7 +5903,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:24">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>25</v>
       </c>
@@ -5931,7 +5947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:24">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -5978,7 +5994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:24">
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>25</v>
       </c>
@@ -6022,7 +6038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:24">
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>41</v>
       </c>
@@ -6063,7 +6079,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:24">
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>42</v>
       </c>
@@ -6107,7 +6123,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:24">
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>43</v>
       </c>
@@ -6151,7 +6167,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:24">
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>44</v>
       </c>
@@ -6198,7 +6214,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:24">
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>43</v>
       </c>
@@ -6242,7 +6258,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:24">
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>45</v>
       </c>
@@ -6283,7 +6299,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:24">
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>45</v>
       </c>
@@ -6327,7 +6343,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:24">
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>46</v>
       </c>
@@ -6377,7 +6393,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:24">
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>46</v>
       </c>
@@ -6430,7 +6446,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:24">
+    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>46</v>
       </c>
@@ -6480,7 +6496,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:24">
+    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>47</v>
       </c>
@@ -6518,7 +6534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:24">
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>47</v>
       </c>
@@ -6562,7 +6578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:24">
+    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>48</v>
       </c>
@@ -6606,7 +6622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:24">
+    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>48</v>
       </c>
@@ -6650,7 +6666,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:24">
+    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>49</v>
       </c>
@@ -6697,7 +6713,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:24">
+    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>50</v>
       </c>
@@ -6738,7 +6754,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:24">
+    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>25</v>
       </c>
@@ -6779,7 +6795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:24">
+    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>25</v>
       </c>
@@ -6817,7 +6833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:24">
+    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>25</v>
       </c>
@@ -6867,7 +6883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:24">
+    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>25</v>
       </c>
@@ -6917,7 +6933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:24">
+    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>25</v>
       </c>
@@ -6967,7 +6983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:24">
+    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>51</v>
       </c>
@@ -7008,7 +7024,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:24">
+    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>51</v>
       </c>
@@ -7055,7 +7071,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:24">
+    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>52</v>
       </c>
@@ -7099,7 +7115,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:24">
+    <row r="91" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>53</v>
       </c>
@@ -7140,7 +7156,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:24">
+    <row r="92" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>54</v>
       </c>
@@ -7181,7 +7197,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:24">
+    <row r="93" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>55</v>
       </c>
@@ -7222,7 +7238,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:24">
+    <row r="94" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>56</v>
       </c>
@@ -7263,7 +7279,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:24">
+    <row r="95" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>57</v>
       </c>
@@ -7304,7 +7320,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:24">
+    <row r="96" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>57</v>
       </c>
@@ -7345,7 +7361,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:24">
+    <row r="97" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>58</v>
       </c>
@@ -7389,7 +7405,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:24">
+    <row r="98" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>59</v>
       </c>
@@ -7433,7 +7449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:24">
+    <row r="99" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>37</v>
       </c>
@@ -7474,7 +7490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:24">
+    <row r="100" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>60</v>
       </c>
@@ -7518,7 +7534,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="1:24">
+    <row r="101" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>61</v>
       </c>
@@ -7559,7 +7575,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:24">
+    <row r="102" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>61</v>
       </c>
@@ -7603,7 +7619,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:24">
+    <row r="103" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>62</v>
       </c>
@@ -7647,7 +7663,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:24">
+    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>63</v>
       </c>
@@ -7688,7 +7704,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:24">
+    <row r="105" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>64</v>
       </c>
@@ -7732,7 +7748,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="1:24">
+    <row r="106" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>65</v>
       </c>
@@ -7773,7 +7789,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="1:24">
+    <row r="107" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>57</v>
       </c>
@@ -7814,7 +7830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:24">
+    <row r="108" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>57</v>
       </c>
@@ -7831,7 +7847,7 @@
         <v>266</v>
       </c>
       <c r="I108" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
       <c r="J108" t="s">
         <v>320</v>
@@ -7864,7 +7880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:24">
+    <row r="109" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>57</v>
       </c>
@@ -7914,7 +7930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:24">
+    <row r="110" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>57</v>
       </c>
@@ -7964,7 +7980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:24">
+    <row r="111" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>57</v>
       </c>
@@ -8008,7 +8024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:24">
+    <row r="112" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>66</v>
       </c>
@@ -8049,7 +8065,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:24">
+    <row r="113" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>67</v>
       </c>
@@ -8093,7 +8109,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="114" spans="1:24">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>68</v>
       </c>
@@ -8134,7 +8150,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:24">
+    <row r="115" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>69</v>
       </c>
@@ -8172,7 +8188,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:24">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>53</v>
       </c>
@@ -8216,7 +8232,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:24">
+    <row r="117" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>70</v>
       </c>
@@ -8266,7 +8282,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:24">
+    <row r="118" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>38</v>
       </c>
@@ -8310,7 +8326,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:24">
+    <row r="119" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>71</v>
       </c>
@@ -8351,7 +8367,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:24">
+    <row r="120" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>72</v>
       </c>
@@ -8392,7 +8408,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:24">
+    <row r="121" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>73</v>
       </c>
@@ -8433,7 +8449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="122" spans="1:24">
+    <row r="122" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>74</v>
       </c>
@@ -8483,7 +8499,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:24">
+    <row r="123" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>75</v>
       </c>
@@ -8524,7 +8540,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:24">
+    <row r="124" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>76</v>
       </c>
@@ -8571,7 +8587,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:24">
+    <row r="125" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>77</v>
       </c>
@@ -8620,130 +8636,130 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="N2" r:id="rId1"/>
-    <hyperlink ref="N3" r:id="rId2"/>
-    <hyperlink ref="N4" r:id="rId3"/>
-    <hyperlink ref="N5" r:id="rId4"/>
-    <hyperlink ref="N6" r:id="rId5"/>
-    <hyperlink ref="N7" r:id="rId6"/>
-    <hyperlink ref="N8" r:id="rId7"/>
-    <hyperlink ref="N9" r:id="rId8"/>
-    <hyperlink ref="N10" r:id="rId9"/>
-    <hyperlink ref="N11" r:id="rId10"/>
-    <hyperlink ref="N12" r:id="rId11"/>
-    <hyperlink ref="N13" r:id="rId12"/>
-    <hyperlink ref="N14" r:id="rId13"/>
-    <hyperlink ref="N15" r:id="rId14"/>
-    <hyperlink ref="N16" r:id="rId15"/>
-    <hyperlink ref="N17" r:id="rId16"/>
-    <hyperlink ref="N18" r:id="rId17"/>
-    <hyperlink ref="N19" r:id="rId18"/>
-    <hyperlink ref="N20" r:id="rId19"/>
-    <hyperlink ref="N21" r:id="rId20"/>
-    <hyperlink ref="N22" r:id="rId21"/>
-    <hyperlink ref="N23" r:id="rId22"/>
-    <hyperlink ref="N24" r:id="rId23"/>
-    <hyperlink ref="N25" r:id="rId24"/>
-    <hyperlink ref="N26" r:id="rId25"/>
-    <hyperlink ref="N27" r:id="rId26"/>
-    <hyperlink ref="N28" r:id="rId27"/>
-    <hyperlink ref="N29" r:id="rId28"/>
-    <hyperlink ref="N30" r:id="rId29"/>
-    <hyperlink ref="N31" r:id="rId30"/>
-    <hyperlink ref="N32" r:id="rId31"/>
-    <hyperlink ref="N33" r:id="rId32"/>
-    <hyperlink ref="N34" r:id="rId33"/>
-    <hyperlink ref="N35" r:id="rId34"/>
-    <hyperlink ref="N36" r:id="rId35"/>
-    <hyperlink ref="N37" r:id="rId36"/>
-    <hyperlink ref="N38" r:id="rId37"/>
-    <hyperlink ref="N39" r:id="rId38"/>
-    <hyperlink ref="N40" r:id="rId39"/>
-    <hyperlink ref="N41" r:id="rId40"/>
-    <hyperlink ref="N42" r:id="rId41"/>
-    <hyperlink ref="N43" r:id="rId42"/>
-    <hyperlink ref="N44" r:id="rId43"/>
-    <hyperlink ref="N45" r:id="rId44"/>
-    <hyperlink ref="N46" r:id="rId45"/>
-    <hyperlink ref="N47" r:id="rId46"/>
-    <hyperlink ref="N48" r:id="rId47"/>
-    <hyperlink ref="N49" r:id="rId48"/>
-    <hyperlink ref="N50" r:id="rId49"/>
-    <hyperlink ref="N51" r:id="rId50"/>
-    <hyperlink ref="N52" r:id="rId51"/>
-    <hyperlink ref="N53" r:id="rId52"/>
-    <hyperlink ref="N54" r:id="rId53"/>
-    <hyperlink ref="N55" r:id="rId54"/>
-    <hyperlink ref="N56" r:id="rId55"/>
-    <hyperlink ref="N57" r:id="rId56"/>
-    <hyperlink ref="N58" r:id="rId57"/>
-    <hyperlink ref="N59" r:id="rId58"/>
-    <hyperlink ref="N60" r:id="rId59"/>
-    <hyperlink ref="N61" r:id="rId60"/>
-    <hyperlink ref="N62" r:id="rId61"/>
-    <hyperlink ref="N63" r:id="rId62"/>
-    <hyperlink ref="N64" r:id="rId63"/>
-    <hyperlink ref="N65" r:id="rId64"/>
-    <hyperlink ref="N66" r:id="rId65"/>
-    <hyperlink ref="N67" r:id="rId66"/>
-    <hyperlink ref="N68" r:id="rId67"/>
-    <hyperlink ref="N69" r:id="rId68"/>
-    <hyperlink ref="N70" r:id="rId69"/>
-    <hyperlink ref="N71" r:id="rId70"/>
-    <hyperlink ref="N72" r:id="rId71"/>
-    <hyperlink ref="N73" r:id="rId72"/>
-    <hyperlink ref="N74" r:id="rId73"/>
-    <hyperlink ref="N75" r:id="rId74"/>
-    <hyperlink ref="N76" r:id="rId75"/>
-    <hyperlink ref="N77" r:id="rId76"/>
-    <hyperlink ref="N78" r:id="rId77"/>
-    <hyperlink ref="N79" r:id="rId78"/>
-    <hyperlink ref="N80" r:id="rId79"/>
-    <hyperlink ref="N81" r:id="rId80"/>
-    <hyperlink ref="N82" r:id="rId81"/>
-    <hyperlink ref="N83" r:id="rId82"/>
-    <hyperlink ref="N84" r:id="rId83"/>
-    <hyperlink ref="N85" r:id="rId84"/>
-    <hyperlink ref="N86" r:id="rId85"/>
-    <hyperlink ref="N87" r:id="rId86"/>
-    <hyperlink ref="N88" r:id="rId87"/>
-    <hyperlink ref="N89" r:id="rId88"/>
-    <hyperlink ref="N90" r:id="rId89"/>
-    <hyperlink ref="N91" r:id="rId90"/>
-    <hyperlink ref="N92" r:id="rId91"/>
-    <hyperlink ref="N93" r:id="rId92"/>
-    <hyperlink ref="N94" r:id="rId93"/>
-    <hyperlink ref="N95" r:id="rId94"/>
-    <hyperlink ref="N96" r:id="rId95"/>
-    <hyperlink ref="N97" r:id="rId96"/>
-    <hyperlink ref="N98" r:id="rId97"/>
-    <hyperlink ref="N99" r:id="rId98"/>
-    <hyperlink ref="N100" r:id="rId99"/>
-    <hyperlink ref="N101" r:id="rId100"/>
-    <hyperlink ref="N102" r:id="rId101"/>
-    <hyperlink ref="N103" r:id="rId102"/>
-    <hyperlink ref="N104" r:id="rId103"/>
-    <hyperlink ref="N105" r:id="rId104"/>
-    <hyperlink ref="N106" r:id="rId105"/>
-    <hyperlink ref="N107" r:id="rId106"/>
-    <hyperlink ref="N108" r:id="rId107"/>
-    <hyperlink ref="N109" r:id="rId108"/>
-    <hyperlink ref="N110" r:id="rId109"/>
-    <hyperlink ref="N111" r:id="rId110"/>
-    <hyperlink ref="N112" r:id="rId111"/>
-    <hyperlink ref="N113" r:id="rId112"/>
-    <hyperlink ref="N114" r:id="rId113"/>
-    <hyperlink ref="N115" r:id="rId114"/>
-    <hyperlink ref="N116" r:id="rId115"/>
-    <hyperlink ref="N117" r:id="rId116"/>
-    <hyperlink ref="N118" r:id="rId117"/>
-    <hyperlink ref="N119" r:id="rId118"/>
-    <hyperlink ref="N120" r:id="rId119"/>
-    <hyperlink ref="N121" r:id="rId120"/>
-    <hyperlink ref="N122" r:id="rId121"/>
-    <hyperlink ref="N123" r:id="rId122"/>
-    <hyperlink ref="N124" r:id="rId123"/>
-    <hyperlink ref="N125" r:id="rId124"/>
+    <hyperlink ref="N2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="N3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="N4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="N5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="N6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="N7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="N8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="N9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="N10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="N11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="N12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="N13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="N14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="N15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="N16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="N17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="N18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="N19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="N20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="N21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="N22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="N23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="N24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="N25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="N26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="N27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="N28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="N29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="N30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="N31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="N32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="N33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="N34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="N35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="N36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="N37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="N38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="N39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="N40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="N41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="N42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="N43" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="N44" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="N45" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="N46" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="N47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="N48" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="N49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="N50" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="N51" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="N52" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="N53" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="N54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="N55" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="N56" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="N57" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="N58" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="N59" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="N60" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="N61" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="N62" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="N63" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="N64" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="N65" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="N66" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="N67" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="N68" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="N69" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="N70" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="N71" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="N72" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="N73" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="N74" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="N75" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="N76" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="N77" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="N78" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="N79" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="N80" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="N81" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="N82" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="N83" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="N84" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="N85" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="N86" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="N87" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="N88" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="N89" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="N90" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="N91" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="N92" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="N93" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="N94" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="N95" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="N96" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="N97" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="N98" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="N99" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="N100" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="N101" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="N102" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="N103" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="N104" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="N105" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="N106" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="N107" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="N108" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="N109" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="N110" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="N111" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="N112" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="N113" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="N114" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="N115" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="N116" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="N117" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="N118" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="N119" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="N120" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="N121" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="N122" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="N123" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="N124" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="N125" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-17e.xlsx
+++ b/quizzes/sculpture-17e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31CDD984-5EF6-4DBA-A1F7-E96C38E7454C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29A2A693-A92B-4945-A173-453D797EFF8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1594" uniqueCount="818">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="683">
   <si>
     <t>Prénom</t>
   </si>
@@ -940,9 +940,6 @@
     <t>Toulon</t>
   </si>
   <si>
-    <t>Marseille</t>
-  </si>
-  <si>
     <t>Marseile</t>
   </si>
   <si>
@@ -2042,408 +2039,6 @@
   </si>
   <si>
     <t>Bois polychrome doré</t>
-  </si>
-  <si>
-    <t>280 cm</t>
-  </si>
-  <si>
-    <t>286 cm</t>
-  </si>
-  <si>
-    <t>78 cm</t>
-  </si>
-  <si>
-    <t>750 cm</t>
-  </si>
-  <si>
-    <t>700 cm</t>
-  </si>
-  <si>
-    <t>146 cm</t>
-  </si>
-  <si>
-    <t>160 cm</t>
-  </si>
-  <si>
-    <t>132 cm</t>
-  </si>
-  <si>
-    <t>243 cm</t>
-  </si>
-  <si>
-    <t>255 cm</t>
-  </si>
-  <si>
-    <t>182 cm</t>
-  </si>
-  <si>
-    <t>170 cm</t>
-  </si>
-  <si>
-    <t>2900 cm</t>
-  </si>
-  <si>
-    <t>600 cm environ, pour l'ensemble</t>
-  </si>
-  <si>
-    <t>72 cm</t>
-  </si>
-  <si>
-    <t>83 cm</t>
-  </si>
-  <si>
-    <t>470 cm</t>
-  </si>
-  <si>
-    <t>350 cm</t>
-  </si>
-  <si>
-    <t>2100 cm</t>
-  </si>
-  <si>
-    <t>106 cm</t>
-  </si>
-  <si>
-    <t>150 cm</t>
-  </si>
-  <si>
-    <t>200 cm</t>
-  </si>
-  <si>
-    <t>1677 cm</t>
-  </si>
-  <si>
-    <t>900 cm</t>
-  </si>
-  <si>
-    <t>105 cm</t>
-  </si>
-  <si>
-    <t>1269 cm</t>
-  </si>
-  <si>
-    <t>330 cm</t>
-  </si>
-  <si>
-    <t>188 cm</t>
-  </si>
-  <si>
-    <t>103 cm</t>
-  </si>
-  <si>
-    <t>138 cm</t>
-  </si>
-  <si>
-    <t>450 cm</t>
-  </si>
-  <si>
-    <t>190 cm</t>
-  </si>
-  <si>
-    <t>220 cm</t>
-  </si>
-  <si>
-    <t>175 cm</t>
-  </si>
-  <si>
-    <t>85 cm</t>
-  </si>
-  <si>
-    <t>240 cm</t>
-  </si>
-  <si>
-    <t>242 cm</t>
-  </si>
-  <si>
-    <t>62 cm</t>
-  </si>
-  <si>
-    <t>104 cm</t>
-  </si>
-  <si>
-    <t>233 cm</t>
-  </si>
-  <si>
-    <t>390 cm</t>
-  </si>
-  <si>
-    <t>89 cm</t>
-  </si>
-  <si>
-    <t>60 cm</t>
-  </si>
-  <si>
-    <t>400 cm</t>
-  </si>
-  <si>
-    <t>315 cm</t>
-  </si>
-  <si>
-    <t>223 cm</t>
-  </si>
-  <si>
-    <t>765 cm</t>
-  </si>
-  <si>
-    <t>130 cm</t>
-  </si>
-  <si>
-    <t>165 cm</t>
-  </si>
-  <si>
-    <t>65 cm</t>
-  </si>
-  <si>
-    <t>47 cm</t>
-  </si>
-  <si>
-    <t>230 cm</t>
-  </si>
-  <si>
-    <t>468 cm</t>
-  </si>
-  <si>
-    <t>61 cm</t>
-  </si>
-  <si>
-    <t>290 cm</t>
-  </si>
-  <si>
-    <t>550 cm</t>
-  </si>
-  <si>
-    <t>120 cm</t>
-  </si>
-  <si>
-    <t>1500 cm</t>
-  </si>
-  <si>
-    <t>51 cm</t>
-  </si>
-  <si>
-    <t>40 cm</t>
-  </si>
-  <si>
-    <t>310 cm</t>
-  </si>
-  <si>
-    <t>70 cm</t>
-  </si>
-  <si>
-    <t>87 cm</t>
-  </si>
-  <si>
-    <t>205 cm</t>
-  </si>
-  <si>
-    <t>288 cm</t>
-  </si>
-  <si>
-    <t>228 cm</t>
-  </si>
-  <si>
-    <t>292 cm</t>
-  </si>
-  <si>
-    <t>145 cm</t>
-  </si>
-  <si>
-    <t>204 cm</t>
-  </si>
-  <si>
-    <t>195 cm</t>
-  </si>
-  <si>
-    <t>250 cm</t>
-  </si>
-  <si>
-    <t>500 cm</t>
-  </si>
-  <si>
-    <t>50 cm</t>
-  </si>
-  <si>
-    <t>270 cm</t>
-  </si>
-  <si>
-    <t>320 cm</t>
-  </si>
-  <si>
-    <t>332 cm</t>
-  </si>
-  <si>
-    <t>66 cm</t>
-  </si>
-  <si>
-    <t>226 cm</t>
-  </si>
-  <si>
-    <t>180 cm</t>
-  </si>
-  <si>
-    <t>1000 cm</t>
-  </si>
-  <si>
-    <t>490 cm</t>
-  </si>
-  <si>
-    <t>202 cm</t>
-  </si>
-  <si>
-    <t>126 cm</t>
-  </si>
-  <si>
-    <t>74 cm</t>
-  </si>
-  <si>
-    <t>109 cm</t>
-  </si>
-  <si>
-    <t>300 cm environ</t>
-  </si>
-  <si>
-    <t>54 cm</t>
-  </si>
-  <si>
-    <t>279 cm</t>
-  </si>
-  <si>
-    <t>98 cm</t>
-  </si>
-  <si>
-    <t>2400 cm</t>
-  </si>
-  <si>
-    <t>99 cm</t>
-  </si>
-  <si>
-    <t>210 cm</t>
-  </si>
-  <si>
-    <t>173 cm</t>
-  </si>
-  <si>
-    <t>96 cm</t>
-  </si>
-  <si>
-    <t>58 cm</t>
-  </si>
-  <si>
-    <t>189 cm</t>
-  </si>
-  <si>
-    <t>176 cm</t>
-  </si>
-  <si>
-    <t>309 cm</t>
-  </si>
-  <si>
-    <t>75 cm</t>
-  </si>
-  <si>
-    <t>68 cm</t>
-  </si>
-  <si>
-    <t>291 cm</t>
-  </si>
-  <si>
-    <t>110 cm</t>
-  </si>
-  <si>
-    <t>55 cm</t>
-  </si>
-  <si>
-    <t>38 cm</t>
-  </si>
-  <si>
-    <t>184 cm</t>
-  </si>
-  <si>
-    <t>218 cm</t>
-  </si>
-  <si>
-    <t>192 cm</t>
-  </si>
-  <si>
-    <t>191 cm</t>
-  </si>
-  <si>
-    <t>460 cm</t>
-  </si>
-  <si>
-    <t>140 cm</t>
-  </si>
-  <si>
-    <t>296 cm</t>
-  </si>
-  <si>
-    <t>1350 cm</t>
-  </si>
-  <si>
-    <t>124 cm</t>
-  </si>
-  <si>
-    <t>63 cm</t>
-  </si>
-  <si>
-    <t>48 cm</t>
-  </si>
-  <si>
-    <t>30 cm</t>
-  </si>
-  <si>
-    <t>32 cm</t>
-  </si>
-  <si>
-    <t>206 cm</t>
-  </si>
-  <si>
-    <t>3400 cm</t>
-  </si>
-  <si>
-    <t>46 cm</t>
-  </si>
-  <si>
-    <t>100 cm</t>
-  </si>
-  <si>
-    <t>90 cm</t>
-  </si>
-  <si>
-    <t>34 cm</t>
-  </si>
-  <si>
-    <t>82 cm</t>
-  </si>
-  <si>
-    <t>35 cm</t>
-  </si>
-  <si>
-    <t>128 cm</t>
-  </si>
-  <si>
-    <t>171 cm</t>
-  </si>
-  <si>
-    <t>97 cm</t>
-  </si>
-  <si>
-    <t>28 cm</t>
-  </si>
-  <si>
-    <t>76 cm</t>
-  </si>
-  <si>
-    <t>80 cm</t>
-  </si>
-  <si>
-    <t>114 cm</t>
-  </si>
-  <si>
-    <t>44 cm</t>
-  </si>
-  <si>
-    <t>1370 cm</t>
   </si>
   <si>
     <t>italienne</t>
@@ -2496,12 +2091,24 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -2520,9 +2127,22 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -2830,6 +2450,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X125"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="20" max="22" width="9.140625" style="6"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -2889,13 +2512,13 @@
       <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="6" t="s">
         <v>21</v>
       </c>
       <c r="W1" t="s">
@@ -2925,25 +2548,25 @@
         <v>281</v>
       </c>
       <c r="J2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S2" t="s">
-        <v>654</v>
-      </c>
-      <c r="T2" t="s">
-        <v>674</v>
+        <v>653</v>
+      </c>
+      <c r="T2" s="6">
+        <v>280</v>
       </c>
       <c r="W2" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X2">
         <v>1</v>
@@ -2969,22 +2592,22 @@
         <v>281</v>
       </c>
       <c r="J3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="S3" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="W3" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X3">
         <v>1</v>
@@ -3010,31 +2633,31 @@
         <v>282</v>
       </c>
       <c r="J4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="M4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="R4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S4" t="s">
-        <v>654</v>
-      </c>
-      <c r="T4" t="s">
-        <v>675</v>
-      </c>
-      <c r="U4" t="s">
-        <v>709</v>
-      </c>
-      <c r="V4" t="s">
-        <v>752</v>
+        <v>653</v>
+      </c>
+      <c r="T4" s="6">
+        <v>286</v>
+      </c>
+      <c r="U4" s="6">
+        <v>240</v>
+      </c>
+      <c r="V4" s="6">
+        <v>180</v>
       </c>
       <c r="W4" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X4">
         <v>1</v>
@@ -3060,25 +2683,25 @@
         <v>281</v>
       </c>
       <c r="J5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="M5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="R5" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S5" t="s">
-        <v>656</v>
-      </c>
-      <c r="T5" t="s">
-        <v>676</v>
+        <v>655</v>
+      </c>
+      <c r="T5" s="6">
+        <v>78</v>
       </c>
       <c r="W5" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X5">
         <v>1</v>
@@ -3104,28 +2727,28 @@
         <v>281</v>
       </c>
       <c r="J6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="R6" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="S6" t="s">
-        <v>654</v>
-      </c>
-      <c r="T6" t="s">
-        <v>677</v>
-      </c>
-      <c r="U6" t="s">
-        <v>754</v>
+        <v>653</v>
+      </c>
+      <c r="T6" s="6">
+        <v>750</v>
+      </c>
+      <c r="U6" s="6">
+        <v>490</v>
       </c>
       <c r="W6" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X6">
         <v>1</v>
@@ -3151,31 +2774,31 @@
         <v>283</v>
       </c>
       <c r="J7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="R7" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="S7" t="s">
-        <v>654</v>
-      </c>
-      <c r="T7" t="s">
-        <v>678</v>
-      </c>
-      <c r="U7" t="s">
-        <v>755</v>
-      </c>
-      <c r="V7" t="s">
-        <v>786</v>
+        <v>653</v>
+      </c>
+      <c r="T7" s="6">
+        <v>700</v>
+      </c>
+      <c r="U7" s="6">
+        <v>202</v>
+      </c>
+      <c r="V7" s="6">
+        <v>124</v>
       </c>
       <c r="W7" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X7">
         <v>2</v>
@@ -3201,31 +2824,31 @@
         <v>283</v>
       </c>
       <c r="J8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M8" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="R8" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="S8" t="s">
-        <v>654</v>
-      </c>
-      <c r="T8" t="s">
-        <v>679</v>
-      </c>
-      <c r="U8" t="s">
-        <v>756</v>
-      </c>
-      <c r="V8" t="s">
-        <v>787</v>
+        <v>653</v>
+      </c>
+      <c r="T8" s="6">
+        <v>146</v>
+      </c>
+      <c r="U8" s="6">
+        <v>126</v>
+      </c>
+      <c r="V8" s="6">
+        <v>63</v>
       </c>
       <c r="W8" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X8">
         <v>2</v>
@@ -3251,22 +2874,22 @@
         <v>283</v>
       </c>
       <c r="J9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M9" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="R9" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="S9" t="s">
         <v>57</v>
       </c>
       <c r="W9" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X9">
         <v>2</v>
@@ -3292,25 +2915,25 @@
         <v>283</v>
       </c>
       <c r="J10" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M10" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="R10" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S10" t="s">
-        <v>654</v>
-      </c>
-      <c r="T10" t="s">
-        <v>680</v>
+        <v>653</v>
+      </c>
+      <c r="T10" s="6">
+        <v>160</v>
       </c>
       <c r="W10" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X10">
         <v>2</v>
@@ -3339,31 +2962,31 @@
         <v>284</v>
       </c>
       <c r="J11" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="M11" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="R11" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S11" t="s">
-        <v>654</v>
-      </c>
-      <c r="T11" t="s">
-        <v>681</v>
-      </c>
-      <c r="U11" t="s">
-        <v>757</v>
-      </c>
-      <c r="V11" t="s">
-        <v>788</v>
+        <v>653</v>
+      </c>
+      <c r="T11" s="6">
+        <v>132</v>
+      </c>
+      <c r="U11" s="6">
+        <v>74</v>
+      </c>
+      <c r="V11" s="6">
+        <v>48</v>
       </c>
       <c r="W11" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X11">
         <v>1</v>
@@ -3392,25 +3015,25 @@
         <v>281</v>
       </c>
       <c r="J12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M12" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="R12" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S12" t="s">
-        <v>654</v>
-      </c>
-      <c r="T12" t="s">
-        <v>682</v>
+        <v>653</v>
+      </c>
+      <c r="T12" s="6">
+        <v>243</v>
       </c>
       <c r="W12" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X12">
         <v>1</v>
@@ -3439,28 +3062,28 @@
         <v>281</v>
       </c>
       <c r="J13" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M13" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="R13" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S13" t="s">
-        <v>654</v>
-      </c>
-      <c r="T13" t="s">
-        <v>683</v>
-      </c>
-      <c r="U13" t="s">
-        <v>758</v>
+        <v>653</v>
+      </c>
+      <c r="T13" s="6">
+        <v>255</v>
+      </c>
+      <c r="U13" s="6">
+        <v>109</v>
       </c>
       <c r="W13" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X13">
         <v>1</v>
@@ -3489,25 +3112,25 @@
         <v>285</v>
       </c>
       <c r="J14" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="M14" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="R14" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S14" t="s">
-        <v>654</v>
-      </c>
-      <c r="T14" t="s">
-        <v>684</v>
+        <v>653</v>
+      </c>
+      <c r="T14" s="6">
+        <v>182</v>
       </c>
       <c r="W14" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X14">
         <v>1</v>
@@ -3536,25 +3159,25 @@
         <v>281</v>
       </c>
       <c r="J15" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M15" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="R15" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S15" t="s">
-        <v>654</v>
-      </c>
-      <c r="T15" t="s">
-        <v>685</v>
+        <v>653</v>
+      </c>
+      <c r="T15" s="6">
+        <v>170</v>
       </c>
       <c r="W15" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X15">
         <v>1</v>
@@ -3583,25 +3206,25 @@
         <v>281</v>
       </c>
       <c r="J16" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M16" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="R16" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="S16" t="s">
-        <v>656</v>
-      </c>
-      <c r="T16" t="s">
-        <v>686</v>
+        <v>655</v>
+      </c>
+      <c r="T16" s="6">
+        <v>2900</v>
       </c>
       <c r="W16" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X16">
         <v>1</v>
@@ -3630,25 +3253,25 @@
         <v>281</v>
       </c>
       <c r="J17" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M17" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="R17" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S17" t="s">
-        <v>654</v>
-      </c>
-      <c r="T17" t="s">
-        <v>676</v>
+        <v>653</v>
+      </c>
+      <c r="T17" s="6">
+        <v>78</v>
       </c>
       <c r="W17" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X17">
         <v>1</v>
@@ -3677,28 +3300,28 @@
         <v>281</v>
       </c>
       <c r="J18" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M18" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="R18" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="S18" t="s">
-        <v>654</v>
-      </c>
-      <c r="T18" t="s">
-        <v>687</v>
-      </c>
-      <c r="U18" t="s">
-        <v>759</v>
+        <v>653</v>
+      </c>
+      <c r="T18" s="6">
+        <v>600</v>
+      </c>
+      <c r="U18" s="6">
+        <v>300</v>
       </c>
       <c r="W18" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X18">
         <v>1</v>
@@ -3727,31 +3350,31 @@
         <v>286</v>
       </c>
       <c r="J19" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M19" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="R19" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S19" t="s">
-        <v>654</v>
-      </c>
-      <c r="T19" t="s">
-        <v>688</v>
-      </c>
-      <c r="U19" t="s">
-        <v>760</v>
-      </c>
-      <c r="V19" t="s">
-        <v>789</v>
+        <v>653</v>
+      </c>
+      <c r="T19" s="6">
+        <v>72</v>
+      </c>
+      <c r="U19" s="6">
+        <v>54</v>
+      </c>
+      <c r="V19" s="6">
+        <v>30</v>
       </c>
       <c r="W19" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X19">
         <v>1</v>
@@ -3780,31 +3403,31 @@
         <v>283</v>
       </c>
       <c r="J20" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M20" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="R20" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S20" t="s">
-        <v>654</v>
-      </c>
-      <c r="T20" t="s">
-        <v>689</v>
-      </c>
-      <c r="U20" t="s">
-        <v>735</v>
-      </c>
-      <c r="V20" t="s">
-        <v>790</v>
+        <v>653</v>
+      </c>
+      <c r="T20" s="6">
+        <v>83</v>
+      </c>
+      <c r="U20" s="6">
+        <v>70</v>
+      </c>
+      <c r="V20" s="6">
+        <v>32</v>
       </c>
       <c r="W20" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X20">
         <v>1</v>
@@ -3833,25 +3456,25 @@
         <v>281</v>
       </c>
       <c r="J21" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="M21" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="R21" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="S21" t="s">
-        <v>657</v>
-      </c>
-      <c r="T21" t="s">
-        <v>690</v>
+        <v>656</v>
+      </c>
+      <c r="T21" s="6">
+        <v>470</v>
       </c>
       <c r="W21" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X21">
         <v>1</v>
@@ -3880,25 +3503,25 @@
         <v>281</v>
       </c>
       <c r="J22" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M22" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="R22" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S22" t="s">
-        <v>654</v>
-      </c>
-      <c r="T22" t="s">
-        <v>674</v>
+        <v>653</v>
+      </c>
+      <c r="T22" s="6">
+        <v>280</v>
       </c>
       <c r="W22" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X22">
         <v>1</v>
@@ -3927,31 +3550,31 @@
         <v>281</v>
       </c>
       <c r="J23" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="M23" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="R23" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S23" t="s">
-        <v>654</v>
-      </c>
-      <c r="T23" t="s">
-        <v>691</v>
-      </c>
-      <c r="U23" t="s">
-        <v>761</v>
-      </c>
-      <c r="V23" t="s">
-        <v>791</v>
+        <v>653</v>
+      </c>
+      <c r="T23" s="6">
+        <v>350</v>
+      </c>
+      <c r="U23" s="6">
+        <v>279</v>
+      </c>
+      <c r="V23" s="6">
+        <v>206</v>
       </c>
       <c r="W23" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X23">
         <v>1</v>
@@ -3980,25 +3603,25 @@
         <v>281</v>
       </c>
       <c r="J24" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="M24" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="R24" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="S24" t="s">
-        <v>658</v>
-      </c>
-      <c r="T24" t="s">
-        <v>692</v>
+        <v>657</v>
+      </c>
+      <c r="T24" s="6">
+        <v>2100</v>
       </c>
       <c r="W24" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X24">
         <v>1</v>
@@ -4027,31 +3650,31 @@
         <v>287</v>
       </c>
       <c r="J25" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="M25" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="R25" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S25" t="s">
-        <v>654</v>
-      </c>
-      <c r="T25" t="s">
-        <v>693</v>
-      </c>
-      <c r="U25" t="s">
-        <v>762</v>
-      </c>
-      <c r="V25" t="s">
-        <v>746</v>
+        <v>653</v>
+      </c>
+      <c r="T25" s="6">
+        <v>106</v>
+      </c>
+      <c r="U25" s="6">
+        <v>98</v>
+      </c>
+      <c r="V25" s="6">
+        <v>50</v>
       </c>
       <c r="W25" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X25">
         <v>1</v>
@@ -4080,28 +3703,28 @@
         <v>281</v>
       </c>
       <c r="J26" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="M26" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="R26" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="S26" t="s">
-        <v>657</v>
-      </c>
-      <c r="T26" t="s">
-        <v>694</v>
-      </c>
-      <c r="U26" t="s">
-        <v>731</v>
+        <v>656</v>
+      </c>
+      <c r="T26" s="6">
+        <v>150</v>
+      </c>
+      <c r="U26" s="6">
+        <v>1500</v>
       </c>
       <c r="W26" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X26">
         <v>1</v>
@@ -4130,28 +3753,28 @@
         <v>281</v>
       </c>
       <c r="J27" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="M27" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="R27" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="S27" t="s">
-        <v>659</v>
-      </c>
-      <c r="T27" t="s">
-        <v>695</v>
-      </c>
-      <c r="U27" t="s">
-        <v>753</v>
+        <v>658</v>
+      </c>
+      <c r="T27" s="6">
+        <v>200</v>
+      </c>
+      <c r="U27" s="6">
+        <v>1000</v>
       </c>
       <c r="W27" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X27">
         <v>1</v>
@@ -4180,31 +3803,31 @@
         <v>281</v>
       </c>
       <c r="J28" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M28" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="R28" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="S28" t="s">
-        <v>657</v>
-      </c>
-      <c r="T28" t="s">
-        <v>696</v>
-      </c>
-      <c r="U28" t="s">
-        <v>763</v>
-      </c>
-      <c r="V28" t="s">
-        <v>792</v>
+        <v>656</v>
+      </c>
+      <c r="T28" s="6">
+        <v>1677</v>
+      </c>
+      <c r="U28" s="6">
+        <v>2400</v>
+      </c>
+      <c r="V28" s="6">
+        <v>3400</v>
       </c>
       <c r="W28" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X28">
         <v>1</v>
@@ -4233,28 +3856,28 @@
         <v>281</v>
       </c>
       <c r="J29" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M29" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="Q29" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="R29" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="S29" t="s">
-        <v>660</v>
-      </c>
-      <c r="T29" t="s">
-        <v>697</v>
+        <v>659</v>
+      </c>
+      <c r="T29" s="6">
+        <v>900</v>
       </c>
       <c r="W29" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X29">
         <v>1</v>
@@ -4279,35 +3902,32 @@
       <c r="H30" t="s">
         <v>193</v>
       </c>
-      <c r="I30" t="s">
-        <v>288</v>
-      </c>
       <c r="J30" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="M30" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="R30" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S30" t="s">
-        <v>654</v>
-      </c>
-      <c r="T30" t="s">
-        <v>698</v>
-      </c>
-      <c r="U30" t="s">
-        <v>764</v>
-      </c>
-      <c r="V30" t="s">
-        <v>793</v>
+        <v>653</v>
+      </c>
+      <c r="T30" s="6">
+        <v>105</v>
+      </c>
+      <c r="U30" s="6">
+        <v>99</v>
+      </c>
+      <c r="V30" s="6">
+        <v>46</v>
       </c>
       <c r="W30" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X30">
         <v>1</v>
@@ -4336,25 +3956,25 @@
         <v>281</v>
       </c>
       <c r="J31" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="M31" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="R31" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="S31" t="s">
-        <v>661</v>
-      </c>
-      <c r="T31" t="s">
-        <v>699</v>
+        <v>660</v>
+      </c>
+      <c r="T31" s="6">
+        <v>1269</v>
       </c>
       <c r="W31" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X31">
         <v>1</v>
@@ -4383,31 +4003,31 @@
         <v>281</v>
       </c>
       <c r="J32" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="M32" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="R32" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S32" t="s">
-        <v>654</v>
-      </c>
-      <c r="T32" t="s">
-        <v>700</v>
-      </c>
-      <c r="U32" t="s">
-        <v>707</v>
-      </c>
-      <c r="V32" t="s">
-        <v>794</v>
+        <v>653</v>
+      </c>
+      <c r="T32" s="6">
+        <v>330</v>
+      </c>
+      <c r="U32" s="6">
+        <v>175</v>
+      </c>
+      <c r="V32" s="6">
+        <v>100</v>
       </c>
       <c r="W32" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X32">
         <v>1</v>
@@ -4436,31 +4056,31 @@
         <v>281</v>
       </c>
       <c r="J33" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="M33" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="R33" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S33" t="s">
-        <v>654</v>
-      </c>
-      <c r="T33" t="s">
-        <v>700</v>
-      </c>
-      <c r="U33" t="s">
-        <v>707</v>
-      </c>
-      <c r="V33" t="s">
-        <v>794</v>
+        <v>653</v>
+      </c>
+      <c r="T33" s="6">
+        <v>330</v>
+      </c>
+      <c r="U33" s="6">
+        <v>175</v>
+      </c>
+      <c r="V33" s="6">
+        <v>100</v>
       </c>
       <c r="W33" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X33">
         <v>1</v>
@@ -4489,25 +4109,25 @@
         <v>281</v>
       </c>
       <c r="J34" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M34" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="R34" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="S34" t="s">
-        <v>655</v>
-      </c>
-      <c r="T34" t="s">
-        <v>678</v>
+        <v>654</v>
+      </c>
+      <c r="T34" s="6">
+        <v>700</v>
       </c>
       <c r="W34" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X34">
         <v>1</v>
@@ -4536,34 +4156,34 @@
         <v>281</v>
       </c>
       <c r="J35" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="L35" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="M35" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="R35" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S35" t="s">
-        <v>654</v>
-      </c>
-      <c r="T35" t="s">
-        <v>701</v>
-      </c>
-      <c r="U35" t="s">
-        <v>765</v>
-      </c>
-      <c r="V35" t="s">
-        <v>795</v>
+        <v>653</v>
+      </c>
+      <c r="T35" s="6">
+        <v>188</v>
+      </c>
+      <c r="U35" s="6">
+        <v>210</v>
+      </c>
+      <c r="V35" s="6">
+        <v>90</v>
       </c>
       <c r="W35" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X35">
         <v>1</v>
@@ -4592,25 +4212,25 @@
         <v>281</v>
       </c>
       <c r="J36" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M36" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="R36" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S36" t="s">
-        <v>654</v>
-      </c>
-      <c r="T36" t="s">
-        <v>702</v>
+        <v>653</v>
+      </c>
+      <c r="T36" s="6">
+        <v>103</v>
       </c>
       <c r="W36" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X36">
         <v>1</v>
@@ -4639,25 +4259,25 @@
         <v>289</v>
       </c>
       <c r="J37" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="M37" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="R37" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="S37" t="s">
-        <v>654</v>
-      </c>
-      <c r="T37" t="s">
-        <v>703</v>
+        <v>653</v>
+      </c>
+      <c r="T37" s="6">
+        <v>138</v>
       </c>
       <c r="W37" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X37">
         <v>1</v>
@@ -4683,25 +4303,25 @@
         <v>281</v>
       </c>
       <c r="J38" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M38" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="R38" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S38" t="s">
-        <v>654</v>
-      </c>
-      <c r="T38" t="s">
-        <v>704</v>
+        <v>653</v>
+      </c>
+      <c r="T38" s="6">
+        <v>450</v>
       </c>
       <c r="W38" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X38">
         <v>3</v>
@@ -4727,25 +4347,25 @@
         <v>285</v>
       </c>
       <c r="J39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="M39" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="R39" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S39" t="s">
-        <v>662</v>
-      </c>
-      <c r="T39" t="s">
-        <v>705</v>
+        <v>661</v>
+      </c>
+      <c r="T39" s="6">
+        <v>190</v>
       </c>
       <c r="W39" t="s">
-        <v>810</v>
+        <v>675</v>
       </c>
       <c r="X39">
         <v>3</v>
@@ -4771,25 +4391,25 @@
         <v>281</v>
       </c>
       <c r="J40" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M40" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="R40" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="S40" t="s">
-        <v>663</v>
-      </c>
-      <c r="T40" t="s">
-        <v>706</v>
+        <v>662</v>
+      </c>
+      <c r="T40" s="6">
+        <v>220</v>
       </c>
       <c r="W40" t="s">
-        <v>811</v>
+        <v>676</v>
       </c>
       <c r="X40">
         <v>2</v>
@@ -4815,28 +4435,28 @@
         <v>290</v>
       </c>
       <c r="J41" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M41" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="Q41" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="R41" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S41" t="s">
-        <v>664</v>
-      </c>
-      <c r="T41" t="s">
-        <v>707</v>
+        <v>663</v>
+      </c>
+      <c r="T41" s="6">
+        <v>175</v>
       </c>
       <c r="W41" t="s">
-        <v>812</v>
+        <v>677</v>
       </c>
       <c r="X41">
         <v>3</v>
@@ -4862,31 +4482,31 @@
         <v>285</v>
       </c>
       <c r="J42" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="M42" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="R42" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S42" t="s">
-        <v>662</v>
-      </c>
-      <c r="T42" t="s">
-        <v>708</v>
-      </c>
-      <c r="U42" t="s">
-        <v>766</v>
-      </c>
-      <c r="V42" t="s">
-        <v>757</v>
+        <v>661</v>
+      </c>
+      <c r="T42" s="6">
+        <v>85</v>
+      </c>
+      <c r="U42" s="6">
+        <v>173</v>
+      </c>
+      <c r="V42" s="6">
+        <v>74</v>
       </c>
       <c r="W42" t="s">
-        <v>813</v>
+        <v>678</v>
       </c>
       <c r="X42">
         <v>3</v>
@@ -4912,28 +4532,28 @@
         <v>281</v>
       </c>
       <c r="J43" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="L43" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="M43" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="R43" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S43" t="s">
-        <v>654</v>
-      </c>
-      <c r="T43" t="s">
-        <v>709</v>
+        <v>653</v>
+      </c>
+      <c r="T43" s="6">
+        <v>240</v>
       </c>
       <c r="W43" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X43">
         <v>3</v>
@@ -4959,31 +4579,31 @@
         <v>283</v>
       </c>
       <c r="J44" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M44" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="R44" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S44" t="s">
-        <v>654</v>
-      </c>
-      <c r="T44" t="s">
-        <v>710</v>
-      </c>
-      <c r="U44" t="s">
-        <v>767</v>
-      </c>
-      <c r="V44" t="s">
-        <v>767</v>
+        <v>653</v>
+      </c>
+      <c r="T44" s="6">
+        <v>242</v>
+      </c>
+      <c r="U44" s="6">
+        <v>96</v>
+      </c>
+      <c r="V44" s="6">
+        <v>96</v>
       </c>
       <c r="W44" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X44">
         <v>3</v>
@@ -5009,31 +4629,31 @@
         <v>283</v>
       </c>
       <c r="J45" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M45" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="R45" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S45" t="s">
-        <v>654</v>
-      </c>
-      <c r="T45" t="s">
-        <v>711</v>
-      </c>
-      <c r="U45" t="s">
-        <v>768</v>
-      </c>
-      <c r="V45" t="s">
-        <v>796</v>
+        <v>653</v>
+      </c>
+      <c r="T45" s="6">
+        <v>62</v>
+      </c>
+      <c r="U45" s="6">
+        <v>58</v>
+      </c>
+      <c r="V45" s="6">
+        <v>34</v>
       </c>
       <c r="W45" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X45">
         <v>1</v>
@@ -5056,31 +4676,31 @@
         <v>223</v>
       </c>
       <c r="J46" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="M46" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="R46" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S46" t="s">
-        <v>654</v>
-      </c>
-      <c r="T46" t="s">
-        <v>712</v>
-      </c>
-      <c r="U46" t="s">
-        <v>769</v>
-      </c>
-      <c r="V46" t="s">
-        <v>797</v>
+        <v>653</v>
+      </c>
+      <c r="T46" s="6">
+        <v>104</v>
+      </c>
+      <c r="U46" s="6">
+        <v>189</v>
+      </c>
+      <c r="V46" s="6">
+        <v>82</v>
       </c>
       <c r="W46" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X46">
         <v>1</v>
@@ -5103,28 +4723,28 @@
         <v>224</v>
       </c>
       <c r="J47" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="M47" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="R47" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S47" t="s">
-        <v>654</v>
-      </c>
-      <c r="T47" t="s">
-        <v>713</v>
-      </c>
-      <c r="U47" t="s">
-        <v>770</v>
+        <v>653</v>
+      </c>
+      <c r="T47" s="6">
+        <v>233</v>
+      </c>
+      <c r="U47" s="6">
+        <v>176</v>
       </c>
       <c r="W47" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X47">
         <v>1</v>
@@ -5147,34 +4767,34 @@
         <v>225</v>
       </c>
       <c r="J48" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L48" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="M48" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="R48" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="S48" t="s">
-        <v>665</v>
-      </c>
-      <c r="T48" t="s">
-        <v>714</v>
-      </c>
-      <c r="U48" t="s">
-        <v>771</v>
-      </c>
-      <c r="V48" t="s">
-        <v>789</v>
+        <v>664</v>
+      </c>
+      <c r="T48" s="6">
+        <v>390</v>
+      </c>
+      <c r="U48" s="6">
+        <v>309</v>
+      </c>
+      <c r="V48" s="6">
+        <v>30</v>
       </c>
       <c r="W48" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X48">
         <v>1</v>
@@ -5200,34 +4820,34 @@
         <v>283</v>
       </c>
       <c r="J49" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L49" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="M49" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="R49" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S49" t="s">
-        <v>654</v>
-      </c>
-      <c r="T49" t="s">
-        <v>715</v>
-      </c>
-      <c r="U49" t="s">
-        <v>772</v>
-      </c>
-      <c r="V49" t="s">
-        <v>798</v>
+        <v>653</v>
+      </c>
+      <c r="T49" s="6">
+        <v>89</v>
+      </c>
+      <c r="U49" s="6">
+        <v>75</v>
+      </c>
+      <c r="V49" s="6">
+        <v>35</v>
       </c>
       <c r="W49" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X49">
         <v>1</v>
@@ -5253,31 +4873,31 @@
         <v>283</v>
       </c>
       <c r="J50" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M50" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="R50" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S50" t="s">
-        <v>656</v>
-      </c>
-      <c r="T50" t="s">
-        <v>716</v>
-      </c>
-      <c r="U50" t="s">
-        <v>773</v>
-      </c>
-      <c r="V50" t="s">
-        <v>796</v>
+        <v>655</v>
+      </c>
+      <c r="T50" s="6">
+        <v>60</v>
+      </c>
+      <c r="U50" s="6">
+        <v>68</v>
+      </c>
+      <c r="V50" s="6">
+        <v>34</v>
       </c>
       <c r="W50" t="s">
-        <v>814</v>
+        <v>679</v>
       </c>
       <c r="X50">
         <v>1</v>
@@ -5303,25 +4923,25 @@
         <v>283</v>
       </c>
       <c r="J51" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M51" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="R51" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="S51" t="s">
-        <v>655</v>
-      </c>
-      <c r="T51" t="s">
-        <v>717</v>
+        <v>654</v>
+      </c>
+      <c r="T51" s="6">
+        <v>400</v>
       </c>
       <c r="W51" t="s">
-        <v>814</v>
+        <v>679</v>
       </c>
       <c r="X51">
         <v>1</v>
@@ -5347,34 +4967,34 @@
         <v>283</v>
       </c>
       <c r="J52" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L52" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="M52" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="R52" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S52" t="s">
-        <v>654</v>
-      </c>
-      <c r="T52" t="s">
-        <v>718</v>
-      </c>
-      <c r="U52" t="s">
-        <v>774</v>
-      </c>
-      <c r="V52" t="s">
-        <v>799</v>
+        <v>653</v>
+      </c>
+      <c r="T52" s="6">
+        <v>315</v>
+      </c>
+      <c r="U52" s="6">
+        <v>291</v>
+      </c>
+      <c r="V52" s="6">
+        <v>128</v>
       </c>
       <c r="W52" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X52">
         <v>1</v>
@@ -5400,34 +5020,34 @@
         <v>283</v>
       </c>
       <c r="J53" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L53" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="M53" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="R53" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S53" t="s">
-        <v>654</v>
-      </c>
-      <c r="T53" t="s">
-        <v>718</v>
-      </c>
-      <c r="U53" t="s">
-        <v>774</v>
-      </c>
-      <c r="V53" t="s">
-        <v>799</v>
+        <v>653</v>
+      </c>
+      <c r="T53" s="6">
+        <v>315</v>
+      </c>
+      <c r="U53" s="6">
+        <v>291</v>
+      </c>
+      <c r="V53" s="6">
+        <v>128</v>
       </c>
       <c r="W53" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X53">
         <v>1</v>
@@ -5453,28 +5073,28 @@
         <v>291</v>
       </c>
       <c r="M54" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="R54" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S54" t="s">
-        <v>656</v>
-      </c>
-      <c r="T54" t="s">
-        <v>719</v>
-      </c>
-      <c r="U54" t="s">
-        <v>775</v>
-      </c>
-      <c r="V54" t="s">
-        <v>694</v>
+        <v>655</v>
+      </c>
+      <c r="T54" s="6">
+        <v>223</v>
+      </c>
+      <c r="U54" s="6">
+        <v>110</v>
+      </c>
+      <c r="V54" s="6">
+        <v>150</v>
       </c>
       <c r="W54" t="s">
-        <v>814</v>
+        <v>679</v>
       </c>
       <c r="X54">
         <v>3</v>
@@ -5500,25 +5120,25 @@
         <v>292</v>
       </c>
       <c r="J55" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="M55" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="R55" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="S55" t="s">
-        <v>654</v>
-      </c>
-      <c r="T55" t="s">
-        <v>720</v>
+        <v>653</v>
+      </c>
+      <c r="T55" s="6">
+        <v>765</v>
       </c>
       <c r="W55" t="s">
-        <v>814</v>
+        <v>679</v>
       </c>
       <c r="X55">
         <v>3</v>
@@ -5544,28 +5164,28 @@
         <v>288</v>
       </c>
       <c r="M56" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="R56" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="S56" t="s">
-        <v>666</v>
-      </c>
-      <c r="T56" t="s">
-        <v>721</v>
-      </c>
-      <c r="U56" t="s">
-        <v>691</v>
-      </c>
-      <c r="V56" t="s">
-        <v>800</v>
+        <v>665</v>
+      </c>
+      <c r="T56" s="6">
+        <v>130</v>
+      </c>
+      <c r="U56" s="6">
+        <v>350</v>
+      </c>
+      <c r="V56" s="6">
+        <v>171</v>
       </c>
       <c r="W56" t="s">
-        <v>814</v>
+        <v>679</v>
       </c>
       <c r="X56">
         <v>3</v>
@@ -5591,25 +5211,25 @@
         <v>293</v>
       </c>
       <c r="J57" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="M57" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="R57" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S57" t="s">
-        <v>664</v>
-      </c>
-      <c r="T57" t="s">
-        <v>689</v>
+        <v>663</v>
+      </c>
+      <c r="T57" s="6">
+        <v>83</v>
       </c>
       <c r="W57" t="s">
-        <v>812</v>
+        <v>677</v>
       </c>
       <c r="X57">
         <v>2</v>
@@ -5635,31 +5255,31 @@
         <v>294</v>
       </c>
       <c r="J58" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="M58" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="R58" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S58" t="s">
-        <v>664</v>
-      </c>
-      <c r="T58" t="s">
-        <v>722</v>
-      </c>
-      <c r="U58" t="s">
-        <v>776</v>
-      </c>
-      <c r="V58" t="s">
-        <v>801</v>
+        <v>663</v>
+      </c>
+      <c r="T58" s="6">
+        <v>165</v>
+      </c>
+      <c r="U58" s="6">
+        <v>55</v>
+      </c>
+      <c r="V58" s="6">
+        <v>97</v>
       </c>
       <c r="W58" t="s">
-        <v>812</v>
+        <v>677</v>
       </c>
       <c r="X58">
         <v>2</v>
@@ -5685,31 +5305,31 @@
         <v>294</v>
       </c>
       <c r="J59" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="M59" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="R59" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S59" t="s">
-        <v>664</v>
-      </c>
-      <c r="T59" t="s">
-        <v>723</v>
-      </c>
-      <c r="U59" t="s">
-        <v>777</v>
-      </c>
-      <c r="V59" t="s">
-        <v>798</v>
+        <v>663</v>
+      </c>
+      <c r="T59" s="6">
+        <v>65</v>
+      </c>
+      <c r="U59" s="6">
+        <v>38</v>
+      </c>
+      <c r="V59" s="6">
+        <v>35</v>
       </c>
       <c r="W59" t="s">
-        <v>812</v>
+        <v>677</v>
       </c>
       <c r="X59">
         <v>2</v>
@@ -5735,22 +5355,22 @@
         <v>295</v>
       </c>
       <c r="J60" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="M60" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="R60" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="S60" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="W60" t="s">
-        <v>812</v>
+        <v>677</v>
       </c>
       <c r="X60">
         <v>2</v>
@@ -5776,31 +5396,31 @@
         <v>294</v>
       </c>
       <c r="J61" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="M61" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="R61" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S61" t="s">
-        <v>664</v>
-      </c>
-      <c r="T61" t="s">
-        <v>724</v>
-      </c>
-      <c r="U61" t="s">
-        <v>746</v>
-      </c>
-      <c r="V61" t="s">
-        <v>802</v>
+        <v>663</v>
+      </c>
+      <c r="T61" s="6">
+        <v>47</v>
+      </c>
+      <c r="U61" s="6">
+        <v>50</v>
+      </c>
+      <c r="V61" s="6">
+        <v>28</v>
       </c>
       <c r="W61" t="s">
-        <v>812</v>
+        <v>677</v>
       </c>
       <c r="X61">
         <v>2</v>
@@ -5826,31 +5446,31 @@
         <v>283</v>
       </c>
       <c r="J62" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M62" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="R62" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="S62" t="s">
-        <v>654</v>
-      </c>
-      <c r="T62" t="s">
-        <v>710</v>
-      </c>
-      <c r="U62" t="s">
-        <v>778</v>
-      </c>
-      <c r="V62" t="s">
-        <v>723</v>
+        <v>653</v>
+      </c>
+      <c r="T62" s="6">
+        <v>242</v>
+      </c>
+      <c r="U62" s="6">
+        <v>184</v>
+      </c>
+      <c r="V62" s="6">
+        <v>65</v>
       </c>
       <c r="W62" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X62">
         <v>2</v>
@@ -5876,28 +5496,28 @@
         <v>283</v>
       </c>
       <c r="J63" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M63" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="R63" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S63" t="s">
-        <v>656</v>
-      </c>
-      <c r="T63" t="s">
-        <v>706</v>
-      </c>
-      <c r="U63" t="s">
-        <v>695</v>
+        <v>655</v>
+      </c>
+      <c r="T63" s="6">
+        <v>220</v>
+      </c>
+      <c r="U63" s="6">
+        <v>200</v>
       </c>
       <c r="W63" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X63">
         <v>2</v>
@@ -5923,25 +5543,25 @@
         <v>281</v>
       </c>
       <c r="J64" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M64" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="R64" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S64" t="s">
-        <v>654</v>
-      </c>
-      <c r="T64" t="s">
-        <v>725</v>
+        <v>653</v>
+      </c>
+      <c r="T64" s="6">
+        <v>230</v>
       </c>
       <c r="W64" t="s">
-        <v>815</v>
+        <v>680</v>
       </c>
       <c r="X64">
         <v>1</v>
@@ -5967,28 +5587,28 @@
         <v>281</v>
       </c>
       <c r="J65" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="M65" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="R65" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="S65" t="s">
-        <v>654</v>
-      </c>
-      <c r="T65" t="s">
-        <v>707</v>
-      </c>
-      <c r="U65" t="s">
-        <v>698</v>
+        <v>653</v>
+      </c>
+      <c r="T65" s="6">
+        <v>175</v>
+      </c>
+      <c r="U65" s="6">
+        <v>105</v>
       </c>
       <c r="W65" t="s">
-        <v>815</v>
+        <v>680</v>
       </c>
       <c r="X65">
         <v>1</v>
@@ -6014,25 +5634,25 @@
         <v>281</v>
       </c>
       <c r="J66" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M66" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="R66" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S66" t="s">
-        <v>654</v>
-      </c>
-      <c r="T66" t="s">
-        <v>726</v>
+        <v>653</v>
+      </c>
+      <c r="T66" s="6">
+        <v>468</v>
       </c>
       <c r="W66" t="s">
-        <v>815</v>
+        <v>680</v>
       </c>
       <c r="X66">
         <v>1</v>
@@ -6058,22 +5678,22 @@
         <v>296</v>
       </c>
       <c r="M67" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="R67" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S67" t="s">
-        <v>656</v>
-      </c>
-      <c r="T67" t="s">
-        <v>727</v>
+        <v>655</v>
+      </c>
+      <c r="T67" s="6">
+        <v>61</v>
       </c>
       <c r="W67" t="s">
-        <v>815</v>
+        <v>680</v>
       </c>
       <c r="X67">
         <v>3</v>
@@ -6099,25 +5719,25 @@
         <v>297</v>
       </c>
       <c r="J68" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M68" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="R68" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="S68" t="s">
-        <v>654</v>
-      </c>
-      <c r="T68" t="s">
-        <v>677</v>
+        <v>653</v>
+      </c>
+      <c r="T68" s="6">
+        <v>750</v>
       </c>
       <c r="W68" t="s">
-        <v>815</v>
+        <v>680</v>
       </c>
       <c r="X68">
         <v>3</v>
@@ -6143,25 +5763,25 @@
         <v>281</v>
       </c>
       <c r="J69" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="M69" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="R69" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S69" t="s">
-        <v>654</v>
-      </c>
-      <c r="T69" t="s">
-        <v>728</v>
+        <v>653</v>
+      </c>
+      <c r="T69" s="6">
+        <v>290</v>
       </c>
       <c r="W69" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X69">
         <v>3</v>
@@ -6187,28 +5807,28 @@
         <v>281</v>
       </c>
       <c r="J70" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L70" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="M70" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="R70" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="S70" t="s">
-        <v>657</v>
-      </c>
-      <c r="T70" t="s">
-        <v>729</v>
+        <v>656</v>
+      </c>
+      <c r="T70" s="6">
+        <v>550</v>
       </c>
       <c r="W70" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X70">
         <v>3</v>
@@ -6234,25 +5854,25 @@
         <v>289</v>
       </c>
       <c r="J71" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M71" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="R71" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S71" t="s">
-        <v>654</v>
-      </c>
-      <c r="T71" t="s">
-        <v>730</v>
+        <v>653</v>
+      </c>
+      <c r="T71" s="6">
+        <v>120</v>
       </c>
       <c r="W71" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X71">
         <v>3</v>
@@ -6278,22 +5898,22 @@
         <v>298</v>
       </c>
       <c r="J72" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M72" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="R72" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="S72" t="s">
         <v>57</v>
       </c>
       <c r="W72" t="s">
-        <v>815</v>
+        <v>680</v>
       </c>
       <c r="X72">
         <v>3</v>
@@ -6319,25 +5939,25 @@
         <v>298</v>
       </c>
       <c r="J73" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="M73" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="R73" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="S73" t="s">
-        <v>654</v>
-      </c>
-      <c r="T73" t="s">
-        <v>731</v>
+        <v>653</v>
+      </c>
+      <c r="T73" s="6">
+        <v>1500</v>
       </c>
       <c r="W73" t="s">
-        <v>815</v>
+        <v>680</v>
       </c>
       <c r="X73">
         <v>3</v>
@@ -6363,31 +5983,31 @@
         <v>294</v>
       </c>
       <c r="J74" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="M74" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="R74" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S74" t="s">
-        <v>664</v>
-      </c>
-      <c r="T74" t="s">
-        <v>707</v>
-      </c>
-      <c r="U74" t="s">
-        <v>779</v>
-      </c>
-      <c r="V74" t="s">
-        <v>783</v>
+        <v>663</v>
+      </c>
+      <c r="T74" s="6">
+        <v>175</v>
+      </c>
+      <c r="U74" s="6">
+        <v>218</v>
+      </c>
+      <c r="V74" s="6">
+        <v>140</v>
       </c>
       <c r="W74" t="s">
-        <v>812</v>
+        <v>677</v>
       </c>
       <c r="X74">
         <v>2</v>
@@ -6413,34 +6033,34 @@
         <v>294</v>
       </c>
       <c r="J75" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="M75" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="N75" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="Q75" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="R75" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S75" t="s">
-        <v>664</v>
-      </c>
-      <c r="T75" t="s">
-        <v>732</v>
-      </c>
-      <c r="U75" t="s">
-        <v>780</v>
-      </c>
-      <c r="V75" t="s">
-        <v>803</v>
+        <v>663</v>
+      </c>
+      <c r="T75" s="6">
+        <v>51</v>
+      </c>
+      <c r="U75" s="6">
+        <v>192</v>
+      </c>
+      <c r="V75" s="6">
+        <v>76</v>
       </c>
       <c r="W75" t="s">
-        <v>812</v>
+        <v>677</v>
       </c>
       <c r="X75">
         <v>2</v>
@@ -6466,31 +6086,31 @@
         <v>299</v>
       </c>
       <c r="J76" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M76" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="R76" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S76" t="s">
-        <v>664</v>
-      </c>
-      <c r="T76" t="s">
-        <v>733</v>
-      </c>
-      <c r="U76" t="s">
-        <v>781</v>
-      </c>
-      <c r="V76" t="s">
-        <v>772</v>
+        <v>663</v>
+      </c>
+      <c r="T76" s="6">
+        <v>40</v>
+      </c>
+      <c r="U76" s="6">
+        <v>191</v>
+      </c>
+      <c r="V76" s="6">
+        <v>75</v>
       </c>
       <c r="W76" t="s">
-        <v>812</v>
+        <v>677</v>
       </c>
       <c r="X76">
         <v>2</v>
@@ -6516,19 +6136,19 @@
         <v>281</v>
       </c>
       <c r="M77" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="N77" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="R77" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S77" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="W77" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X77">
         <v>2</v>
@@ -6554,25 +6174,25 @@
         <v>281</v>
       </c>
       <c r="J78" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="M78" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="R78" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="S78" t="s">
-        <v>654</v>
-      </c>
-      <c r="T78" t="s">
-        <v>734</v>
+        <v>653</v>
+      </c>
+      <c r="T78" s="6">
+        <v>310</v>
       </c>
       <c r="W78" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X78">
         <v>2</v>
@@ -6598,25 +6218,25 @@
         <v>283</v>
       </c>
       <c r="J79" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M79" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="R79" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S79" t="s">
-        <v>654</v>
-      </c>
-      <c r="T79" t="s">
-        <v>735</v>
+        <v>653</v>
+      </c>
+      <c r="T79" s="6">
+        <v>70</v>
       </c>
       <c r="W79" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X79">
         <v>2</v>
@@ -6642,25 +6262,25 @@
         <v>286</v>
       </c>
       <c r="J80" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="M80" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="N80" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="R80" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S80" t="s">
-        <v>654</v>
-      </c>
-      <c r="T80" t="s">
-        <v>736</v>
+        <v>653</v>
+      </c>
+      <c r="T80" s="6">
+        <v>87</v>
       </c>
       <c r="W80" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X80">
         <v>2</v>
@@ -6686,28 +6306,28 @@
         <v>286</v>
       </c>
       <c r="J81" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L81" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="M81" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="N81" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="R81" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S81" t="s">
-        <v>654</v>
-      </c>
-      <c r="T81" t="s">
-        <v>717</v>
+        <v>653</v>
+      </c>
+      <c r="T81" s="6">
+        <v>400</v>
       </c>
       <c r="W81" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X81">
         <v>3</v>
@@ -6733,22 +6353,22 @@
         <v>285</v>
       </c>
       <c r="J82" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="M82" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="R82" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="S82" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="W82" t="s">
-        <v>816</v>
+        <v>681</v>
       </c>
       <c r="X82">
         <v>3</v>
@@ -6774,62 +6394,71 @@
         <v>283</v>
       </c>
       <c r="M83" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="N83" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="R83" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S83" t="s">
-        <v>654</v>
-      </c>
-      <c r="T83" t="s">
-        <v>706</v>
+        <v>653</v>
+      </c>
+      <c r="T83" s="6">
+        <v>220</v>
       </c>
       <c r="W83" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X83">
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+    <row r="84" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F84" t="s">
+      <c r="F84" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="G84">
+      <c r="G84" s="2">
         <v>1715</v>
       </c>
-      <c r="H84" t="s">
+      <c r="H84" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="J84" t="s">
-        <v>332</v>
-      </c>
-      <c r="M84" t="s">
-        <v>474</v>
-      </c>
-      <c r="N84" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="R84" t="s">
-        <v>641</v>
-      </c>
-      <c r="S84" t="s">
-        <v>666</v>
-      </c>
-      <c r="W84" t="s">
-        <v>809</v>
-      </c>
-      <c r="X84">
+      <c r="J84" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="N84" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="R84" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="S84" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="T84" s="7">
+        <v>132</v>
+      </c>
+      <c r="U84" s="7">
+        <v>605</v>
+      </c>
+      <c r="V84" s="7">
+        <v>255</v>
+      </c>
+      <c r="W84" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="X84" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6853,31 +6482,31 @@
         <v>283</v>
       </c>
       <c r="J85" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="M85" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="R85" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="S85" t="s">
-        <v>654</v>
-      </c>
-      <c r="T85" t="s">
-        <v>737</v>
-      </c>
-      <c r="U85" t="s">
-        <v>782</v>
-      </c>
-      <c r="V85" t="s">
-        <v>685</v>
+        <v>653</v>
+      </c>
+      <c r="T85" s="6">
+        <v>205</v>
+      </c>
+      <c r="U85" s="6">
+        <v>460</v>
+      </c>
+      <c r="V85" s="6">
+        <v>170</v>
       </c>
       <c r="W85" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X85">
         <v>1</v>
@@ -6900,34 +6529,34 @@
         <v>251</v>
       </c>
       <c r="J86" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L86" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="M86" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="R86" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S86" t="s">
-        <v>654</v>
-      </c>
-      <c r="T86" t="s">
-        <v>738</v>
-      </c>
-      <c r="U86" t="s">
-        <v>703</v>
-      </c>
-      <c r="V86" t="s">
-        <v>679</v>
+        <v>653</v>
+      </c>
+      <c r="T86" s="6">
+        <v>288</v>
+      </c>
+      <c r="U86" s="6">
+        <v>138</v>
+      </c>
+      <c r="V86" s="6">
+        <v>146</v>
       </c>
       <c r="W86" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X86">
         <v>1</v>
@@ -6950,34 +6579,34 @@
         <v>252</v>
       </c>
       <c r="J87" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L87" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="M87" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="R87" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S87" t="s">
-        <v>666</v>
-      </c>
-      <c r="T87" t="s">
-        <v>739</v>
-      </c>
-      <c r="U87" t="s">
-        <v>762</v>
-      </c>
-      <c r="V87" t="s">
-        <v>689</v>
+        <v>665</v>
+      </c>
+      <c r="T87" s="6">
+        <v>228</v>
+      </c>
+      <c r="U87" s="6">
+        <v>98</v>
+      </c>
+      <c r="V87" s="6">
+        <v>83</v>
       </c>
       <c r="W87" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X87">
         <v>1</v>
@@ -7003,22 +6632,22 @@
         <v>281</v>
       </c>
       <c r="J88" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="M88" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="R88" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S88" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="W88" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X88">
         <v>2</v>
@@ -7041,31 +6670,31 @@
         <v>1677</v>
       </c>
       <c r="J89" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="M89" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="R89" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S89" t="s">
-        <v>654</v>
-      </c>
-      <c r="T89" t="s">
-        <v>740</v>
-      </c>
-      <c r="U89" t="s">
-        <v>707</v>
-      </c>
-      <c r="V89" t="s">
-        <v>758</v>
+        <v>653</v>
+      </c>
+      <c r="T89" s="6">
+        <v>292</v>
+      </c>
+      <c r="U89" s="6">
+        <v>175</v>
+      </c>
+      <c r="V89" s="6">
+        <v>109</v>
       </c>
       <c r="W89" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X89">
         <v>3</v>
@@ -7091,25 +6720,25 @@
         <v>283</v>
       </c>
       <c r="J90" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M90" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="N90" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="R90" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S90" t="s">
-        <v>656</v>
-      </c>
-      <c r="T90" t="s">
-        <v>695</v>
+        <v>655</v>
+      </c>
+      <c r="T90" s="6">
+        <v>200</v>
       </c>
       <c r="W90" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X90">
         <v>3</v>
@@ -7132,25 +6761,25 @@
         <v>254</v>
       </c>
       <c r="J91" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="M91" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="N91" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="R91" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="S91" t="s">
-        <v>669</v>
-      </c>
-      <c r="T91" t="s">
-        <v>695</v>
+        <v>668</v>
+      </c>
+      <c r="T91" s="6">
+        <v>200</v>
       </c>
       <c r="W91" t="s">
-        <v>817</v>
+        <v>682</v>
       </c>
       <c r="X91">
         <v>3</v>
@@ -7176,65 +6805,67 @@
         <v>300</v>
       </c>
       <c r="J92" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="M92" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R92" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="S92" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="W92" t="s">
-        <v>814</v>
+        <v>679</v>
       </c>
       <c r="X92">
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+    <row r="93" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="F93" t="s">
+      <c r="F93" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="G93">
+      <c r="G93" s="4">
         <v>1690</v>
       </c>
-      <c r="H93" t="s">
+      <c r="H93" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="J93" t="s">
-        <v>332</v>
-      </c>
-      <c r="M93" t="s">
-        <v>482</v>
-      </c>
-      <c r="N93" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="R93" t="s">
-        <v>641</v>
-      </c>
-      <c r="S93" t="s">
-        <v>656</v>
-      </c>
-      <c r="T93" t="s">
-        <v>695</v>
-      </c>
-      <c r="W93" t="s">
-        <v>809</v>
-      </c>
-      <c r="X93">
+      <c r="J93" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="M93" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="N93" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="R93" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="S93" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="T93" s="8">
+        <v>200</v>
+      </c>
+      <c r="U93" s="8"/>
+      <c r="V93" s="8"/>
+      <c r="W93" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="X93" s="4">
         <v>3</v>
       </c>
     </row>
@@ -7258,22 +6889,22 @@
         <v>285</v>
       </c>
       <c r="J94" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="M94" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="R94" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S94" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="W94" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X94">
         <v>3</v>
@@ -7296,25 +6927,25 @@
         <v>258</v>
       </c>
       <c r="J95" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="M95" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="R95" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S95" t="s">
-        <v>654</v>
-      </c>
-      <c r="T95" t="s">
-        <v>706</v>
+        <v>653</v>
+      </c>
+      <c r="T95" s="6">
+        <v>220</v>
       </c>
       <c r="W95" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X95">
         <v>3</v>
@@ -7340,22 +6971,22 @@
         <v>281</v>
       </c>
       <c r="J96" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="M96" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="R96" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S96" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="W96" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X96">
         <v>2</v>
@@ -7381,25 +7012,25 @@
         <v>281</v>
       </c>
       <c r="J97" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="M97" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="N97" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="R97" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S97" t="s">
-        <v>654</v>
-      </c>
-      <c r="T97" t="s">
-        <v>741</v>
+        <v>653</v>
+      </c>
+      <c r="T97" s="6">
+        <v>145</v>
       </c>
       <c r="W97" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X97">
         <v>2</v>
@@ -7425,25 +7056,25 @@
         <v>281</v>
       </c>
       <c r="J98" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="M98" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="N98" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="R98" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S98" t="s">
-        <v>665</v>
-      </c>
-      <c r="T98" t="s">
-        <v>691</v>
+        <v>664</v>
+      </c>
+      <c r="T98" s="6">
+        <v>350</v>
       </c>
       <c r="W98" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X98">
         <v>3</v>
@@ -7466,25 +7097,25 @@
         <v>249</v>
       </c>
       <c r="J99" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="M99" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="N99" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="R99" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="S99" t="s">
-        <v>670</v>
-      </c>
-      <c r="T99" t="s">
-        <v>742</v>
+        <v>669</v>
+      </c>
+      <c r="T99" s="6">
+        <v>204</v>
       </c>
       <c r="W99" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X99">
         <v>1</v>
@@ -7507,28 +7138,28 @@
         <v>261</v>
       </c>
       <c r="J100" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="M100" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="N100" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q100" t="s">
+        <v>639</v>
+      </c>
+      <c r="R100" t="s">
         <v>640</v>
       </c>
-      <c r="R100" t="s">
-        <v>641</v>
-      </c>
       <c r="S100" t="s">
-        <v>664</v>
-      </c>
-      <c r="T100" t="s">
-        <v>743</v>
+        <v>663</v>
+      </c>
+      <c r="T100" s="6">
+        <v>195</v>
       </c>
       <c r="W100" t="s">
-        <v>812</v>
+        <v>677</v>
       </c>
       <c r="X100">
         <v>3</v>
@@ -7554,22 +7185,22 @@
         <v>301</v>
       </c>
       <c r="M101" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="N101" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="R101" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S101" t="s">
-        <v>654</v>
-      </c>
-      <c r="T101" t="s">
-        <v>744</v>
+        <v>653</v>
+      </c>
+      <c r="T101" s="6">
+        <v>250</v>
       </c>
       <c r="W101" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X101">
         <v>3</v>
@@ -7595,25 +7226,25 @@
         <v>281</v>
       </c>
       <c r="J102" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M102" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="N102" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="R102" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S102" t="s">
-        <v>654</v>
-      </c>
-      <c r="T102" t="s">
-        <v>745</v>
+        <v>653</v>
+      </c>
+      <c r="T102" s="6">
+        <v>500</v>
       </c>
       <c r="W102" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X102">
         <v>3</v>
@@ -7639,25 +7270,25 @@
         <v>290</v>
       </c>
       <c r="J103" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="M103" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="N103" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="R103" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S103" t="s">
-        <v>664</v>
-      </c>
-      <c r="T103" t="s">
-        <v>746</v>
+        <v>663</v>
+      </c>
+      <c r="T103" s="6">
+        <v>50</v>
       </c>
       <c r="W103" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X103">
         <v>3</v>
@@ -7683,22 +7314,22 @@
         <v>302</v>
       </c>
       <c r="J104" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M104" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="N104" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="R104" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="S104" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="W104" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X104">
         <v>3</v>
@@ -7724,25 +7355,25 @@
         <v>303</v>
       </c>
       <c r="J105" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="M105" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="N105" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="R105" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S105" t="s">
-        <v>654</v>
-      </c>
-      <c r="T105" t="s">
-        <v>695</v>
+        <v>653</v>
+      </c>
+      <c r="T105" s="6">
+        <v>200</v>
       </c>
       <c r="W105" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X105">
         <v>3</v>
@@ -7768,22 +7399,22 @@
         <v>304</v>
       </c>
       <c r="J106" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="M106" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="N106" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="R106" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S106" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="W106" t="s">
-        <v>817</v>
+        <v>682</v>
       </c>
       <c r="X106">
         <v>3</v>
@@ -7809,22 +7440,22 @@
         <v>305</v>
       </c>
       <c r="J107" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="M107" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="N107" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="R107" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S107" t="s">
         <v>57</v>
       </c>
       <c r="W107" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X107">
         <v>1</v>
@@ -7850,31 +7481,31 @@
         <v>283</v>
       </c>
       <c r="J108" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M108" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="N108" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="R108" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S108" t="s">
-        <v>654</v>
-      </c>
-      <c r="T108" t="s">
-        <v>747</v>
-      </c>
-      <c r="U108" t="s">
-        <v>783</v>
-      </c>
-      <c r="V108" t="s">
-        <v>804</v>
+        <v>653</v>
+      </c>
+      <c r="T108" s="6">
+        <v>270</v>
+      </c>
+      <c r="U108" s="6">
+        <v>140</v>
+      </c>
+      <c r="V108" s="6">
+        <v>80</v>
       </c>
       <c r="W108" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X108">
         <v>1</v>
@@ -7897,34 +7528,34 @@
         <v>267</v>
       </c>
       <c r="I109" t="s">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="J109" t="s">
+        <v>319</v>
+      </c>
+      <c r="M109" t="s">
+        <v>496</v>
+      </c>
+      <c r="N109" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="R109" t="s">
+        <v>640</v>
+      </c>
+      <c r="S109" t="s">
+        <v>653</v>
+      </c>
+      <c r="T109" s="6">
         <v>320</v>
       </c>
-      <c r="M109" t="s">
-        <v>497</v>
-      </c>
-      <c r="N109" s="1" t="s">
-        <v>620</v>
-      </c>
-      <c r="R109" t="s">
-        <v>641</v>
-      </c>
-      <c r="S109" t="s">
-        <v>654</v>
-      </c>
-      <c r="T109" t="s">
-        <v>748</v>
-      </c>
-      <c r="U109" t="s">
-        <v>693</v>
-      </c>
-      <c r="V109" t="s">
-        <v>805</v>
+      <c r="U109" s="6">
+        <v>106</v>
+      </c>
+      <c r="V109" s="6">
+        <v>114</v>
       </c>
       <c r="W109" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X109">
         <v>1</v>
@@ -7950,31 +7581,31 @@
         <v>283</v>
       </c>
       <c r="J110" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M110" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="N110" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="R110" t="s">
+        <v>652</v>
+      </c>
+      <c r="S110" t="s">
         <v>653</v>
       </c>
-      <c r="S110" t="s">
-        <v>654</v>
-      </c>
-      <c r="T110" t="s">
-        <v>749</v>
-      </c>
-      <c r="U110" t="s">
-        <v>784</v>
-      </c>
-      <c r="V110" t="s">
-        <v>806</v>
+      <c r="T110" s="6">
+        <v>332</v>
+      </c>
+      <c r="U110" s="6">
+        <v>296</v>
+      </c>
+      <c r="V110" s="6">
+        <v>44</v>
       </c>
       <c r="W110" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X110">
         <v>1</v>
@@ -7997,28 +7628,28 @@
         <v>268</v>
       </c>
       <c r="I111" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J111" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="M111" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="N111" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="R111" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="S111" t="s">
-        <v>654</v>
-      </c>
-      <c r="T111" t="s">
-        <v>750</v>
+        <v>653</v>
+      </c>
+      <c r="T111" s="6">
+        <v>66</v>
       </c>
       <c r="W111" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X111">
         <v>1</v>
@@ -8041,25 +7672,25 @@
         <v>269</v>
       </c>
       <c r="J112" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="M112" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="N112" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="R112" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S112" t="s">
-        <v>654</v>
-      </c>
-      <c r="T112" t="s">
-        <v>695</v>
+        <v>653</v>
+      </c>
+      <c r="T112" s="6">
+        <v>200</v>
       </c>
       <c r="W112" t="s">
-        <v>815</v>
+        <v>680</v>
       </c>
       <c r="X112">
         <v>3</v>
@@ -8085,25 +7716,25 @@
         <v>281</v>
       </c>
       <c r="J113" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="M113" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="N113" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="R113" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S113" t="s">
-        <v>654</v>
-      </c>
-      <c r="T113" t="s">
-        <v>691</v>
+        <v>653</v>
+      </c>
+      <c r="T113" s="6">
+        <v>350</v>
       </c>
       <c r="W113" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X113">
         <v>3</v>
@@ -8126,25 +7757,25 @@
         <v>270</v>
       </c>
       <c r="I114" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J114" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M114" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="N114" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="R114" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S114" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="W114" t="s">
-        <v>817</v>
+        <v>682</v>
       </c>
       <c r="X114">
         <v>3</v>
@@ -8167,22 +7798,22 @@
         <v>271</v>
       </c>
       <c r="J115" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="M115" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="N115" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="R115" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S115" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="W115" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X115">
         <v>3</v>
@@ -8205,28 +7836,28 @@
         <v>272</v>
       </c>
       <c r="I116" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J116" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="M116" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="N116" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="R116" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S116" t="s">
-        <v>656</v>
-      </c>
-      <c r="T116" t="s">
-        <v>695</v>
+        <v>655</v>
+      </c>
+      <c r="T116" s="6">
+        <v>200</v>
       </c>
       <c r="W116" t="s">
-        <v>817</v>
+        <v>682</v>
       </c>
       <c r="X116">
         <v>3</v>
@@ -8255,28 +7886,28 @@
         <v>273</v>
       </c>
       <c r="I117" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J117" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="M117" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="N117" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="R117" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S117" t="s">
-        <v>664</v>
-      </c>
-      <c r="T117" t="s">
-        <v>751</v>
+        <v>663</v>
+      </c>
+      <c r="T117" s="6">
+        <v>226</v>
       </c>
       <c r="W117" t="s">
-        <v>812</v>
+        <v>677</v>
       </c>
       <c r="X117">
         <v>3</v>
@@ -8299,28 +7930,28 @@
         <v>274</v>
       </c>
       <c r="I118" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J118" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="M118" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="N118" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="R118" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S118" t="s">
-        <v>664</v>
-      </c>
-      <c r="T118" t="s">
-        <v>752</v>
+        <v>663</v>
+      </c>
+      <c r="T118" s="6">
+        <v>180</v>
       </c>
       <c r="W118" t="s">
-        <v>812</v>
+        <v>677</v>
       </c>
       <c r="X118">
         <v>3</v>
@@ -8346,22 +7977,22 @@
         <v>283</v>
       </c>
       <c r="J119" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="M119" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="N119" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="R119" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S119" t="s">
         <v>57</v>
       </c>
       <c r="W119" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X119">
         <v>2</v>
@@ -8384,25 +8015,25 @@
         <v>268</v>
       </c>
       <c r="I120" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J120" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="M120" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="N120" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R120" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S120" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="W120" t="s">
-        <v>808</v>
+        <v>673</v>
       </c>
       <c r="X120">
         <v>3</v>
@@ -8425,25 +8056,25 @@
         <v>276</v>
       </c>
       <c r="I121" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J121" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="M121" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="N121" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="R121" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="S121" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="W121" t="s">
-        <v>810</v>
+        <v>675</v>
       </c>
       <c r="X121">
         <v>3</v>
@@ -8466,34 +8097,34 @@
         <v>277</v>
       </c>
       <c r="J122" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L122" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="M122" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="N122" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="R122" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S122" t="s">
-        <v>666</v>
-      </c>
-      <c r="T122" t="s">
-        <v>709</v>
-      </c>
-      <c r="U122" t="s">
-        <v>785</v>
-      </c>
-      <c r="V122" t="s">
-        <v>807</v>
+        <v>665</v>
+      </c>
+      <c r="T122" s="6">
+        <v>240</v>
+      </c>
+      <c r="U122" s="6">
+        <v>1350</v>
+      </c>
+      <c r="V122" s="6">
+        <v>1370</v>
       </c>
       <c r="W122" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X122">
         <v>3</v>
@@ -8516,25 +8147,25 @@
         <v>278</v>
       </c>
       <c r="I123" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J123" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="M123" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="N123" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="R123" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="S123" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="W123" t="s">
-        <v>815</v>
+        <v>680</v>
       </c>
       <c r="X123">
         <v>3</v>
@@ -8557,31 +8188,31 @@
         <v>279</v>
       </c>
       <c r="J124" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="M124" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="N124" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="R124" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S124" t="s">
-        <v>654</v>
-      </c>
-      <c r="T124" t="s">
-        <v>693</v>
-      </c>
-      <c r="U124" t="s">
-        <v>708</v>
-      </c>
-      <c r="V124" t="s">
-        <v>746</v>
+        <v>653</v>
+      </c>
+      <c r="T124" s="6">
+        <v>106</v>
+      </c>
+      <c r="U124" s="6">
+        <v>85</v>
+      </c>
+      <c r="V124" s="6">
+        <v>50</v>
       </c>
       <c r="W124" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="X124">
         <v>3</v>
@@ -8604,31 +8235,31 @@
         <v>280</v>
       </c>
       <c r="I125" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J125" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="M125" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="N125" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="R125" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="S125" t="s">
-        <v>673</v>
-      </c>
-      <c r="T125" t="s">
-        <v>753</v>
-      </c>
-      <c r="U125" t="s">
-        <v>745</v>
+        <v>672</v>
+      </c>
+      <c r="T125" s="6">
+        <v>1000</v>
+      </c>
+      <c r="U125" s="6">
+        <v>500</v>
       </c>
       <c r="W125" t="s">
-        <v>817</v>
+        <v>682</v>
       </c>
       <c r="X125">
         <v>3</v>

--- a/quizzes/sculpture-17e.xlsx
+++ b/quizzes/sculpture-17e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{903C7751-2725-4D6C-9F21-12A64929018C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2DA695-F762-4E67-82BF-D3A5E52DAC78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1900" uniqueCount="944">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1978" uniqueCount="964">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -2513,9 +2513,6 @@
     <t>Basilique de Carignano</t>
   </si>
   <si>
-    <t>"Saint Jean-Baptiste"</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c1/Filippo_parodi%2C_san_giovanni_battista%2C_1667.JPG/1280px-Filippo_parodi%2C_san_giovanni_battista%2C_1667.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -2570,301 +2567,364 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/6/60/Pierre_Puget_-_Louis_XIV.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>QUELLINUS L'ANCIEN</t>
+  </si>
+  <si>
+    <t>1650-1665</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9d/Mercurius.jpg/1280px-Mercurius.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>Antonio</t>
+  </si>
+  <si>
+    <t>RAGGI</t>
+  </si>
+  <si>
+    <t>Fontaine des Quatre-Fleuves, Piazza Navona</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/ae/The_Danube_in_the_fontana_dei_quattro_fiumi.jpg/1280px-The_Danube_in_the_fontana_dei_quattro_fiumi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Madrid</t>
+  </si>
+  <si>
+    <t>TACCA</t>
+  </si>
+  <si>
+    <t>Place de la Santissima Annunziata</t>
+  </si>
+  <si>
+    <t>Statue équestre de Ferdinand Ier de Médicis</t>
+  </si>
+  <si>
+    <t>Monumento a Ferdinando I de' Medici</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/ce/FerdinandodeMedici.jpg/960px-FerdinandodeMedici.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>Livourne</t>
+  </si>
+  <si>
+    <t>Piazza Micheli</t>
+  </si>
+  <si>
+    <t>Monument des Quatre Maures</t>
+  </si>
+  <si>
+    <t>Monumento dei Quattro mori</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/93/Livorno%2C_Monumento_dei_quattro_mori_a_Ferdinando_II_%281626%29_-_Foto_Giovanni_Dall%27Orto%2C_13-4-2006_12.jpg/1280px-Livorno%2C_Monumento_dei_quattro_mori_a_Ferdinando_II_%281626%29_-_Foto_Giovanni_Dall%27Orto%2C_13-4-2006_12.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Groupe de quatre rondes-bosses</t>
+  </si>
+  <si>
+    <t>Bronze et marbre</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>Place de l'Orient</t>
+  </si>
+  <si>
+    <t>Statue équestre de Philippe IV</t>
+  </si>
+  <si>
+    <t>Monumento a Felipe IV</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/PIETRO_TACCA_FELIPE_IV_DE_ESPA%C3%91A.JPG/1280px-PIETRO_TACCA_FELIPE_IV_DE_ESPA%C3%91A.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Monument avec rondes-bosses</t>
+  </si>
+  <si>
+    <t>420</t>
+  </si>
+  <si>
+    <t>Marché du Porcellino</t>
+  </si>
+  <si>
+    <t>Fontaine du Porcellino</t>
+  </si>
+  <si>
+    <t>Il Porcellino</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/e/ee/Firenze-cinghiale.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Fontaines des monstres marins</t>
+  </si>
+  <si>
+    <t>Fontane des mostri marini</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Fontana_in_Santissima_Annunziata.JPG/960px-Fontana_in_Santissima_Annunziata.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>1610-1620</t>
+  </si>
+  <si>
+    <t>Carrare</t>
+  </si>
+  <si>
+    <t>Cathédrale Saint-André</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crucifix </t>
+  </si>
+  <si>
+    <t>Crocifisso bronzeo</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/58/Carrara%2C_duomo%2C_interno%2C_altare_dell%27annunziata%2C_crocifisso_in_gesso_attr._a_pietro_tacca_01.jpg/960px-Carrara%2C_duomo%2C_interno%2C_altare_dell%27annunziata%2C_crocifisso_in_gesso_attr._a_pietro_tacca_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>Objet liturgique</t>
+  </si>
+  <si>
+    <t>Plâtre peint</t>
+  </si>
+  <si>
+    <t>Jean-Baptiste</t>
+  </si>
+  <si>
+    <t>TUBY</t>
+  </si>
+  <si>
+    <t>1668-1671</t>
+  </si>
+  <si>
+    <t>Bassin d'Apollon</t>
+  </si>
+  <si>
+    <t>"Le Char d'Apollon"</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f5/Versailles_Bassin_d%27Apollon_001.jpg/1280px-Versailles_Bassin_d%27Apollon_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1680</t>
+  </si>
+  <si>
+    <t>Palais royal de Gênes</t>
+  </si>
+  <si>
+    <t>Vénus</t>
+  </si>
+  <si>
+    <t>Venere</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/e/ec/Palazzo_Reale_%28Genova%29_07.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>Adonis</t>
+  </si>
+  <si>
+    <t>Adone</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Palazzo_Reale_%28Genova%29_06.jpg/960px-Palazzo_Reale_%28Genova%29_06.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1689</t>
+  </si>
+  <si>
+    <t>Padoue</t>
+  </si>
+  <si>
+    <t>Basilique de Santa Giustina</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3c/Padova_Basilica_di_Santa_Giustina_Innen_Kapelle_der_Piet%C3%A0_1.jpg/960px-Padova_Basilica_di_Santa_Giustina_Innen_Kapelle_der_Piet%C3%A0_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Pieta</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Santa_Giustina_%28Padua%29_-_Chapel_of_La_Pieta_-_Pieta_by_Filippo_Parodi.jpg/1280px-Santa_Giustina_%28Padua%29_-_Chapel_of_La_Pieta_-_Pieta_by_Filippo_Parodi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Element architectural</t>
+  </si>
+  <si>
+    <t>1659</t>
+  </si>
+  <si>
+    <t>Basilique Santa Maria di Carignano</t>
+  </si>
+  <si>
+    <t>Saint Sébastien</t>
+  </si>
+  <si>
+    <t>San Sebastiano</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a9/Pierre_puget%2C_san_sebastiano%2C_1668%2C_02.JPG/500px-Pierre_puget%2C_san_sebastiano%2C_1668%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1664-1668</t>
+  </si>
+  <si>
+    <t>Le Bienheureux Alexandre Sauli</t>
+  </si>
+  <si>
+    <t>Beato Alessandro Sauli</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Pierre_puget%2C_sant%27alessandro_sauli%2C_1668%2C_02.JPG/960px-Pierre_puget%2C_sant%27alessandro_sauli%2C_1668%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Hercule Gaulois</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a9/Hercule_au_repos_-_Pierre_Puget_-_Mus%C3%A9e_du_Louvre_Sculptures_N_15345.jpg/1280px-Hercule_au_repos_-_Pierre_Puget_-_Mus%C3%A9e_du_Louvre_Sculptures_N_15345.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Amsterdam</t>
+  </si>
+  <si>
+    <t>Palais royal</t>
+  </si>
+  <si>
     <t>Artus</t>
   </si>
   <si>
-    <t>QUELLINUS L'ANCIEN</t>
-  </si>
-  <si>
-    <t>1650-1665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palais royal d'Amsterdam </t>
-  </si>
-  <si>
-    <t>"Mercure "</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9d/Mercurius.jpg/1280px-Mercurius.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Antonio</t>
-  </si>
-  <si>
-    <t>RAGGI</t>
-  </si>
-  <si>
-    <t>Fontaine des Quatre-Fleuves, Piazza Navona</t>
-  </si>
-  <si>
-    <t>"Statue du Danube"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/ae/The_Danube_in_the_fontana_dei_quattro_fiumi.jpg/1280px-The_Danube_in_the_fontana_dei_quattro_fiumi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>Matthias</t>
-  </si>
-  <si>
-    <t>RAUCHMILLER</t>
-  </si>
-  <si>
-    <t>1679-1694</t>
-  </si>
-  <si>
-    <t>Graben</t>
-  </si>
-  <si>
-    <t>"Colonne de la Peste "</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/56/Wien_-_Dreifaltigkeits-_bzw._Pests%C3%A4ule.JPG/1280px-Wien_-_Dreifaltigkeits-_bzw._Pests%C3%A4ule.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Thomas</t>
-  </si>
-  <si>
-    <t>REGNAUDIN</t>
-  </si>
-  <si>
-    <t>1672-1679</t>
-  </si>
-  <si>
-    <t>"Bassin de Cérès"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0a/Le_chateau_de_versailles_le_jardin_41.JPG/1280px-Le_chateau_de_versailles_le_jardin_41.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>Plomb doré et marbre</t>
-  </si>
-  <si>
-    <t>Hans</t>
-  </si>
-  <si>
-    <t>REICHLE</t>
-  </si>
-  <si>
-    <t>1605-1607</t>
-  </si>
-  <si>
-    <t>Augsbourg</t>
-  </si>
-  <si>
-    <t>Arsenal</t>
-  </si>
-  <si>
-    <t>"L'Archange saint Michel terrassant Satan"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e4/Erzengel-Michael-Augsburg-1.jpg/1280px-Erzengel-Michael-Augsburg-1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Luisa</t>
-  </si>
-  <si>
-    <t>ROLDÁN</t>
-  </si>
-  <si>
-    <t>Madrid</t>
-  </si>
-  <si>
-    <t>Galería de las Colecciones Reales</t>
-  </si>
-  <si>
-    <t>"Saint Michel Archange terrassant le démon"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/37/El_arc%C3%A1ngel_San_Miguel_venciendo_al_demonio%2C_Luisa_Rold%C3%A1n.jpg/1280px-El_arc%C3%A1ngel_San_Miguel_venciendo_al_demonio%2C_Luisa_Rold%C3%A1n.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Iglesia del Hospital de los Venerables</t>
-  </si>
-  <si>
-    <t>"San Fernando"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3e/San_Fernando%2C_Pedro_Rold%C3%A1n.jpg/1280px-San_Fernando%2C_Pedro_Rold%C3%A1n.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Jacques</t>
-  </si>
-  <si>
-    <t>SARRAZIN</t>
-  </si>
-  <si>
-    <t>1636-1642</t>
-  </si>
-  <si>
-    <t>Cour Carrée, Musée du Louvre</t>
-  </si>
-  <si>
-    <t>"Cariatides du pavillon de l'Horloge"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3e/Left_caryatids_Pavillon_Horloge_Louvre.jpg/1280px-Left_caryatids_Pavillon_Horloge_Louvre.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Giacomo</t>
-  </si>
-  <si>
-    <t>SERPOTTA</t>
-  </si>
-  <si>
-    <t>Palerme</t>
-  </si>
-  <si>
-    <t>Oratorio del Rosario di Santa Cita</t>
-  </si>
-  <si>
-    <t>"Décors de l'Oratoire du Rosaire"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8b/Fd.4.8_Giacomo_Serpotta%2C_Oratorio_di_S._Cita_Palermo%2C_statua_allegorica_-FG.jpg/1280px-Fd.4.8_Giacomo_Serpotta%2C_Oratorio_di_S._Cita_Palermo%2C_statua_allegorica_-FG.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>TACCA</t>
-  </si>
-  <si>
-    <t>Place de la Santissima Annunziata</t>
-  </si>
-  <si>
-    <t>Statue équestre de Ferdinand Ier de Médicis</t>
-  </si>
-  <si>
-    <t>Monumento a Ferdinando I de' Medici</t>
-  </si>
-  <si>
-    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/ce/FerdinandodeMedici.jpg/960px-FerdinandodeMedici.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
-  </si>
-  <si>
-    <t>400</t>
-  </si>
-  <si>
-    <t>Livourne</t>
-  </si>
-  <si>
-    <t>Piazza Micheli</t>
-  </si>
-  <si>
-    <t>Monument des Quatre Maures</t>
-  </si>
-  <si>
-    <t>Monumento dei Quattro mori</t>
-  </si>
-  <si>
-    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/93/Livorno%2C_Monumento_dei_quattro_mori_a_Ferdinando_II_%281626%29_-_Foto_Giovanni_Dall%27Orto%2C_13-4-2006_12.jpg/1280px-Livorno%2C_Monumento_dei_quattro_mori_a_Ferdinando_II_%281626%29_-_Foto_Giovanni_Dall%27Orto%2C_13-4-2006_12.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>Groupe de quatre rondes-bosses</t>
-  </si>
-  <si>
-    <t>Bronze et marbre</t>
-  </si>
-  <si>
-    <t>250</t>
-  </si>
-  <si>
-    <t>Place de l'Orient</t>
-  </si>
-  <si>
-    <t>Statue équestre de Philippe IV</t>
-  </si>
-  <si>
-    <t>Monumento a Felipe IV</t>
-  </si>
-  <si>
-    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/PIETRO_TACCA_FELIPE_IV_DE_ESPA%C3%91A.JPG/1280px-PIETRO_TACCA_FELIPE_IV_DE_ESPA%C3%91A.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>Monument avec rondes-bosses</t>
-  </si>
-  <si>
-    <t>420</t>
-  </si>
-  <si>
-    <t>Marché du Porcellino</t>
-  </si>
-  <si>
-    <t>Fontaine du Porcellino</t>
-  </si>
-  <si>
-    <t>Il Porcellino</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/e/ee/Firenze-cinghiale.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>Fontaines des monstres marins</t>
-  </si>
-  <si>
-    <t>Fontane des mostri marini</t>
-  </si>
-  <si>
-    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Fontana_in_Santissima_Annunziata.JPG/960px-Fontana_in_Santissima_Annunziata.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>210</t>
-  </si>
-  <si>
-    <t>1610-1620</t>
-  </si>
-  <si>
-    <t>Carrare</t>
-  </si>
-  <si>
-    <t>Cathédrale Saint-André</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crucifix </t>
-  </si>
-  <si>
-    <t>Crocifisso bronzeo</t>
-  </si>
-  <si>
-    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/58/Carrara%2C_duomo%2C_interno%2C_altare_dell%27annunziata%2C_crocifisso_in_gesso_attr._a_pietro_tacca_01.jpg/960px-Carrara%2C_duomo%2C_interno%2C_altare_dell%27annunziata%2C_crocifisso_in_gesso_attr._a_pietro_tacca_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
-  </si>
-  <si>
-    <t>Objet liturgique</t>
-  </si>
-  <si>
-    <t>Plâtre peint</t>
-  </si>
-  <si>
-    <t>Jean-Baptiste</t>
-  </si>
-  <si>
-    <t>TUBY</t>
-  </si>
-  <si>
-    <t>1668-1671</t>
-  </si>
-  <si>
-    <t>Bassin d'Apollon</t>
-  </si>
-  <si>
-    <t>"Le Char d'Apollon"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f5/Versailles_Bassin_d%27Apollon_001.jpg/1280px-Versailles_Bassin_d%27Apollon_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>Jean</t>
-  </si>
-  <si>
-    <t>WARIN</t>
-  </si>
-  <si>
-    <t>1665-1666</t>
-  </si>
-  <si>
-    <t>"Buste de Louis XIV"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/17/Jean_Warin_%28Lie%C4%9Do%2C_1607_-_Parizo%2C_1672%29._Portreto_de_Ludoviko_XIV%2C_re%C4%9Do_de_Francio_%281638-1715%29._1665-1666._Busto%2C_marmoro._Versajlo%2C_Nacia_Muzeo_de_la_kasteloj_de_Versajlo_kaj_Trianon%2C_MV_494.jpg/1280px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+    <t>Mercure</t>
+  </si>
+  <si>
+    <t>1650-1655</t>
+  </si>
+  <si>
+    <t>Salle des Bourgeois</t>
+  </si>
+  <si>
+    <t>Atlas supportant le globe céleste</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Royal_Palace_of_Amsterdam_71.jpg/960px-Royal_Palace_of_Amsterdam_71.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Statue monumentale</t>
+  </si>
+  <si>
+    <t>Rijksmuseum</t>
+  </si>
+  <si>
+    <t>Galerie d'honneur</t>
+  </si>
+  <si>
+    <t>Buste de Johan de Witt</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/68/Buste_Johan_de_Witt_Artus_Quellinus_%28I%29_1665.jpg/960px-Buste_Johan_de_Witt_Artus_Quellinus_%28I%29_1665.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1661</t>
+  </si>
+  <si>
+    <t>Buste d'Andries de Graeff</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2f/Andries_de_Graeff_1661_door_Artur_Quellinus.JPG/960px-Andries_de_Graeff_1661_door_Artur_Quellinus.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1650-1654</t>
+  </si>
+  <si>
+    <t>Le Jugement de Salomon (Relief)</t>
+  </si>
+  <si>
+    <t>ttps://upload.wikimedia.org/wikipedia/commons/0/08/Artus_Quellinus_-_Paleis-op-de-Dam_vierschaar_-_salomos_oordeel.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>1658</t>
+  </si>
+  <si>
+    <t>Anvers</t>
+  </si>
+  <si>
+    <t>Église Saint-Paul</t>
+  </si>
+  <si>
+    <t>Nef principale</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/f/f2/Artus_Quellinus_I_-_Saint_Peter_%28cropped%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>Statue du Danube</t>
+  </si>
+  <si>
+    <t>Il Lombardo</t>
+  </si>
+  <si>
+    <t>1665-1667</t>
+  </si>
+  <si>
+    <t>Église San Giovanni dei Fiorentini</t>
+  </si>
+  <si>
+    <t>Chœur</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0b/Antonio_raggi%2C_battesimo_di_cristo%2C_1669%2C_in_altare_del_borromini%2C_1640%2C_02.jpg/960px-Antonio_raggi%2C_battesimo_di_cristo%2C_1669%2C_in_altare_del_borromini%2C_1640%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1667-1669</t>
+  </si>
+  <si>
+    <t>Parapet</t>
+  </si>
+  <si>
+    <t>Ange avec la Colonne</t>
+  </si>
+  <si>
+    <t>Angelo avec la Colonna</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9e/Antonio_Raggi-Angel_bearing_a_column-Ponte_Sant_Angelo.jpg/960px-Antonio_Raggi-Angel_bearing_a_column-Ponte_Sant_Angelo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Anges de la Passion</t>
+  </si>
+  <si>
+    <t>1675</t>
+  </si>
+  <si>
+    <t>Basilique Sant'Agnese in Agone</t>
+  </si>
+  <si>
+    <t>Autel principal</t>
+  </si>
+  <si>
+    <t>Martyre de sainte Agnès</t>
+  </si>
+  <si>
+    <t>Martirio di Sant'Agnese</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1a/Sant-agnese-erroma-0608.jpg/960px-Sant-agnese-erroma-0608.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tribunal </t>
   </si>
 </sst>
 </file>
@@ -3414,7 +3474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W218"/>
+  <dimension ref="A1:W192"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="18" customWidth="1"/>
@@ -3424,12 +3484,12 @@
     <col min="7" max="7" width="5.85546875" customWidth="1"/>
     <col min="8" max="8" width="13.7109375" customWidth="1"/>
     <col min="9" max="9" width="20.28515625" customWidth="1"/>
-    <col min="10" max="10" width="36" customWidth="1"/>
+    <col min="10" max="10" width="18.5703125" customWidth="1"/>
     <col min="13" max="13" width="4.7109375" customWidth="1"/>
     <col min="14" max="14" width="4.140625" customWidth="1"/>
     <col min="15" max="15" width="9.42578125" customWidth="1"/>
-    <col min="16" max="16" width="6.28515625" customWidth="1"/>
-    <col min="17" max="17" width="14.140625" customWidth="1"/>
+    <col min="16" max="16" width="4.140625" customWidth="1"/>
+    <col min="17" max="17" width="14.140625" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="19.42578125" customWidth="1"/>
     <col min="19" max="19" width="24.5703125" customWidth="1"/>
     <col min="20" max="23" width="9.140625" style="24" customWidth="1"/>
@@ -11903,8 +11963,8 @@
       <c r="B164" s="2" t="s">
         <v>823</v>
       </c>
-      <c r="C164" s="2"/>
-      <c r="D164" s="5" t="s">
+      <c r="C164" s="29"/>
+      <c r="D164" s="2" t="s">
         <v>190</v>
       </c>
       <c r="E164" s="2" t="s">
@@ -11917,11 +11977,11 @@
       <c r="H164" s="2"/>
       <c r="I164" s="2"/>
       <c r="J164" s="2" t="s">
-        <v>826</v>
+        <v>277</v>
       </c>
       <c r="K164" s="2"/>
       <c r="L164" s="7" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="M164" s="2"/>
       <c r="N164" s="2"/>
@@ -11934,116 +11994,204 @@
       <c r="S164" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="T164" s="21">
-        <v>200</v>
-      </c>
-      <c r="U164" s="21"/>
-      <c r="V164" s="21"/>
-      <c r="W164" s="21">
+      <c r="T164" s="5">
+        <v>450</v>
+      </c>
+      <c r="U164" s="5">
+        <v>160</v>
+      </c>
+      <c r="V164" s="5">
+        <v>110</v>
+      </c>
+      <c r="W164" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="165" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A165" s="2"/>
-      <c r="B165" s="2"/>
-      <c r="C165" s="2"/>
-      <c r="D165" s="5"/>
-      <c r="E165" s="2"/>
-      <c r="F165" s="2"/>
+      <c r="A165" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="C165" s="29"/>
+      <c r="D165" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>896</v>
+      </c>
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
       <c r="I165" s="2"/>
-      <c r="J165" s="2"/>
-      <c r="K165" s="2"/>
-      <c r="L165" s="7"/>
+      <c r="J165" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="K165" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="L165" s="7" t="s">
+        <v>899</v>
+      </c>
       <c r="M165" s="2"/>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
       <c r="P165" s="2"/>
       <c r="Q165" s="2"/>
-      <c r="R165" s="2"/>
-      <c r="S165" s="2"/>
-      <c r="T165" s="21"/>
-      <c r="U165" s="21"/>
-      <c r="V165" s="21"/>
-      <c r="W165" s="21"/>
+      <c r="R165" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S165" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="T165" s="5">
+        <v>102</v>
+      </c>
+      <c r="U165" s="5">
+        <v>68</v>
+      </c>
+      <c r="V165" s="5">
+        <v>55</v>
+      </c>
+      <c r="W165" s="5">
+        <v>3</v>
+      </c>
     </row>
     <row r="166" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A166" s="2"/>
-      <c r="B166" s="2"/>
-      <c r="C166" s="2"/>
-      <c r="D166" s="5"/>
-      <c r="E166" s="2"/>
-      <c r="F166" s="2"/>
+      <c r="A166" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="C166" s="29"/>
+      <c r="D166" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>896</v>
+      </c>
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
       <c r="I166" s="2"/>
-      <c r="J166" s="2"/>
-      <c r="K166" s="2"/>
-      <c r="L166" s="7"/>
+      <c r="J166" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="K166" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="L166" s="7" t="s">
+        <v>902</v>
+      </c>
       <c r="M166" s="2"/>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
       <c r="P166" s="2"/>
       <c r="Q166" s="2"/>
-      <c r="R166" s="2"/>
-      <c r="S166" s="2"/>
-      <c r="T166" s="21"/>
-      <c r="U166" s="21"/>
-      <c r="V166" s="21"/>
-      <c r="W166" s="21"/>
+      <c r="R166" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S166" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="T166" s="5">
+        <v>102</v>
+      </c>
+      <c r="U166" s="5">
+        <v>68</v>
+      </c>
+      <c r="V166" s="5">
+        <v>55</v>
+      </c>
+      <c r="W166" s="5">
+        <v>3</v>
+      </c>
     </row>
     <row r="167" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A167" s="2"/>
-      <c r="B167" s="2"/>
-      <c r="C167" s="2"/>
-      <c r="D167" s="5"/>
-      <c r="E167" s="2"/>
-      <c r="F167" s="2"/>
+      <c r="A167" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="C167" s="29"/>
+      <c r="D167" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>905</v>
+      </c>
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
-      <c r="I167" s="2"/>
-      <c r="J167" s="2"/>
+      <c r="I167" s="7" t="s">
+        <v>906</v>
+      </c>
+      <c r="J167" s="2" t="s">
+        <v>907</v>
+      </c>
       <c r="K167" s="2"/>
-      <c r="L167" s="7"/>
+      <c r="L167" s="7" t="s">
+        <v>908</v>
+      </c>
       <c r="M167" s="2"/>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
       <c r="P167" s="2"/>
       <c r="Q167" s="2"/>
-      <c r="R167" s="2"/>
-      <c r="S167" s="2"/>
-      <c r="T167" s="21"/>
-      <c r="U167" s="21"/>
-      <c r="V167" s="21"/>
-      <c r="W167" s="21"/>
+      <c r="R167" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="S167" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="T167" s="5">
+        <v>180</v>
+      </c>
+      <c r="U167" s="5">
+        <v>500</v>
+      </c>
+      <c r="V167" s="5">
+        <v>120</v>
+      </c>
+      <c r="W167" s="5">
+        <v>3</v>
+      </c>
     </row>
     <row r="168" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>96</v>
       </c>
       <c r="B168" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="C168" s="2"/>
+      <c r="D168" s="2" t="s">
         <v>828</v>
       </c>
-      <c r="C168" s="2"/>
-      <c r="D168" s="5" t="s">
+      <c r="E168" s="2" t="s">
         <v>829</v>
       </c>
-      <c r="E168" s="2" t="s">
+      <c r="F168" s="2" t="s">
         <v>830</v>
-      </c>
-      <c r="F168" s="2" t="s">
-        <v>831</v>
       </c>
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
       <c r="I168" s="2"/>
       <c r="J168" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="K168" s="2"/>
       <c r="L168" s="7" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="M168" s="2"/>
       <c r="N168" s="2"/>
@@ -12051,26 +12199,34 @@
       <c r="P168" s="2"/>
       <c r="Q168" s="2"/>
       <c r="R168" s="2" t="s">
-        <v>30</v>
+        <v>909</v>
       </c>
       <c r="S168" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="T168" s="21"/>
-      <c r="U168" s="21"/>
-      <c r="V168" s="21"/>
-      <c r="W168" s="21"/>
+      <c r="T168" s="5">
+        <v>250</v>
+      </c>
+      <c r="U168" s="5">
+        <v>80</v>
+      </c>
+      <c r="V168" s="5">
+        <v>200</v>
+      </c>
+      <c r="W168" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="169" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>96</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C169" s="2"/>
-      <c r="D169" s="5" t="s">
-        <v>834</v>
+      <c r="D169" s="2" t="s">
+        <v>833</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>73</v>
@@ -12082,11 +12238,11 @@
       <c r="H169" s="2"/>
       <c r="I169" s="2"/>
       <c r="J169" s="2" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="K169" s="2"/>
       <c r="L169" s="7" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="M169" s="2"/>
       <c r="N169" s="2"/>
@@ -12099,16 +12255,16 @@
       <c r="S169" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="T169" s="21">
+      <c r="T169" s="5">
         <v>270</v>
       </c>
-      <c r="U169" s="21">
+      <c r="U169" s="5">
         <v>140</v>
       </c>
-      <c r="V169" s="21">
+      <c r="V169" s="5">
         <v>80</v>
       </c>
-      <c r="W169" s="21">
+      <c r="W169" s="5">
         <v>1</v>
       </c>
     </row>
@@ -12117,11 +12273,11 @@
         <v>96</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C170" s="2"/>
-      <c r="D170" s="5" t="s">
-        <v>837</v>
+      <c r="D170" s="2" t="s">
+        <v>836</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>73</v>
@@ -12133,11 +12289,11 @@
       <c r="H170" s="2"/>
       <c r="I170" s="2"/>
       <c r="J170" s="2" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="K170" s="2"/>
       <c r="L170" s="7" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="M170" s="2"/>
       <c r="N170" s="2"/>
@@ -12150,16 +12306,16 @@
       <c r="S170" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="T170" s="21">
+      <c r="T170" s="5">
         <v>320</v>
       </c>
-      <c r="U170" s="21">
+      <c r="U170" s="5">
         <v>106</v>
       </c>
-      <c r="V170" s="21">
+      <c r="V170" s="5">
         <v>114</v>
       </c>
-      <c r="W170" s="21">
+      <c r="W170" s="5">
         <v>1</v>
       </c>
     </row>
@@ -12168,10 +12324,10 @@
         <v>96</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C171" s="2"/>
-      <c r="D171" s="5" t="s">
+      <c r="D171" s="2" t="s">
         <v>333</v>
       </c>
       <c r="E171" s="2" t="s">
@@ -12184,11 +12340,11 @@
       <c r="H171" s="2"/>
       <c r="I171" s="2"/>
       <c r="J171" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="K171" s="2"/>
       <c r="L171" s="7" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="M171" s="2"/>
       <c r="N171" s="2"/>
@@ -12201,16 +12357,16 @@
       <c r="S171" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="T171" s="21">
+      <c r="T171" s="5">
         <v>332</v>
       </c>
-      <c r="U171" s="21">
+      <c r="U171" s="5">
         <v>296</v>
       </c>
-      <c r="V171" s="21">
+      <c r="V171" s="5">
         <v>44</v>
       </c>
-      <c r="W171" s="21">
+      <c r="W171" s="5">
         <v>1</v>
       </c>
     </row>
@@ -12219,14 +12375,14 @@
         <v>96</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C172" s="2"/>
-      <c r="D172" s="5" t="s">
+      <c r="D172" s="2" t="s">
         <v>649</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>282</v>
@@ -12235,11 +12391,11 @@
       <c r="H172" s="2"/>
       <c r="I172" s="2"/>
       <c r="J172" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="K172" s="2"/>
       <c r="L172" s="7" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="M172" s="2"/>
       <c r="N172" s="2"/>
@@ -12252,114 +12408,202 @@
       <c r="S172" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="T172" s="21">
+      <c r="T172" s="5">
         <v>66</v>
       </c>
-      <c r="U172" s="21"/>
-      <c r="V172" s="21"/>
-      <c r="W172" s="21">
+      <c r="U172" s="5">
+        <v>66</v>
+      </c>
+      <c r="V172" s="5">
+        <v>8</v>
+      </c>
+      <c r="W172" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="173" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A173" s="2"/>
-      <c r="B173" s="2"/>
+      <c r="A173" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>827</v>
+      </c>
       <c r="C173" s="2"/>
-      <c r="D173" s="5"/>
-      <c r="E173" s="2"/>
-      <c r="F173" s="2"/>
+      <c r="D173" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>911</v>
+      </c>
       <c r="G173" s="2"/>
       <c r="H173" s="2"/>
       <c r="I173" s="2"/>
-      <c r="J173" s="2"/>
-      <c r="K173" s="2"/>
-      <c r="L173" s="7"/>
+      <c r="J173" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="K173" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="L173" s="7" t="s">
+        <v>914</v>
+      </c>
       <c r="M173" s="2"/>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
       <c r="P173" s="2"/>
       <c r="Q173" s="2"/>
-      <c r="R173" s="2"/>
-      <c r="S173" s="2"/>
-      <c r="T173" s="21"/>
-      <c r="U173" s="21"/>
-      <c r="V173" s="21"/>
-      <c r="W173" s="21"/>
+      <c r="R173" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S173" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="T173" s="5">
+        <v>400</v>
+      </c>
+      <c r="U173" s="5">
+        <v>160</v>
+      </c>
+      <c r="V173" s="5">
+        <v>110</v>
+      </c>
+      <c r="W173" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="174" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A174" s="2"/>
-      <c r="B174" s="2"/>
+      <c r="A174" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>827</v>
+      </c>
       <c r="C174" s="2"/>
-      <c r="D174" s="5"/>
-      <c r="E174" s="2"/>
-      <c r="F174" s="2"/>
+      <c r="D174" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>911</v>
+      </c>
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
       <c r="I174" s="2"/>
-      <c r="J174" s="2"/>
-      <c r="K174" s="2"/>
-      <c r="L174" s="7"/>
+      <c r="J174" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="K174" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="L174" s="7" t="s">
+        <v>918</v>
+      </c>
       <c r="M174" s="2"/>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
       <c r="P174" s="2"/>
       <c r="Q174" s="2"/>
-      <c r="R174" s="2"/>
-      <c r="S174" s="2"/>
-      <c r="T174" s="21"/>
-      <c r="U174" s="21"/>
-      <c r="V174" s="21"/>
-      <c r="W174" s="21"/>
+      <c r="R174" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S174" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="T174" s="5">
+        <v>350</v>
+      </c>
+      <c r="U174" s="5">
+        <v>160</v>
+      </c>
+      <c r="V174" s="5">
+        <v>110</v>
+      </c>
+      <c r="W174" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="175" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A175" s="2"/>
-      <c r="B175" s="2"/>
+      <c r="A175" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>827</v>
+      </c>
       <c r="C175" s="2"/>
-      <c r="D175" s="5"/>
-      <c r="E175" s="2"/>
-      <c r="F175" s="2"/>
+      <c r="D175" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F175" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="G175" s="2"/>
       <c r="H175" s="2"/>
       <c r="I175" s="2"/>
-      <c r="J175" s="2"/>
+      <c r="J175" s="2" t="s">
+        <v>919</v>
+      </c>
       <c r="K175" s="2"/>
-      <c r="L175" s="7"/>
+      <c r="L175" s="7" t="s">
+        <v>920</v>
+      </c>
       <c r="M175" s="2"/>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
       <c r="P175" s="2"/>
       <c r="Q175" s="2"/>
-      <c r="R175" s="2"/>
-      <c r="S175" s="2"/>
-      <c r="T175" s="21"/>
-      <c r="U175" s="21"/>
-      <c r="V175" s="21"/>
-      <c r="W175" s="21"/>
+      <c r="R175" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S175" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="T175" s="5">
+        <v>180</v>
+      </c>
+      <c r="U175" s="5">
+        <v>140</v>
+      </c>
+      <c r="V175" s="5">
+        <v>80</v>
+      </c>
+      <c r="W175" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="176" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="C176" s="2"/>
+      <c r="D176" s="2" t="s">
         <v>845</v>
       </c>
-      <c r="B176" s="2" t="s">
-        <v>846</v>
-      </c>
-      <c r="C176" s="2"/>
-      <c r="D176" s="5" t="s">
-        <v>847</v>
-      </c>
-      <c r="E176" s="2"/>
+      <c r="E176" s="2" t="s">
+        <v>921</v>
+      </c>
       <c r="F176" s="2" t="s">
-        <v>848</v>
+        <v>922</v>
       </c>
       <c r="G176" s="2"/>
       <c r="H176" s="2"/>
       <c r="I176" s="2"/>
       <c r="J176" s="2" t="s">
-        <v>849</v>
+        <v>924</v>
       </c>
       <c r="K176" s="2"/>
       <c r="L176" s="7" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="M176" s="2"/>
       <c r="N176" s="2"/>
@@ -12372,166 +12616,310 @@
       <c r="S176" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="T176" s="21">
+      <c r="T176" s="5">
         <v>200</v>
       </c>
-      <c r="U176" s="21"/>
-      <c r="V176" s="21"/>
-      <c r="W176" s="21">
+      <c r="U176" s="5">
+        <v>80</v>
+      </c>
+      <c r="V176" s="5">
+        <v>40</v>
+      </c>
+      <c r="W176" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="177" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A177" s="2"/>
-      <c r="B177" s="2"/>
+      <c r="A177" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>844</v>
+      </c>
       <c r="C177" s="2"/>
-      <c r="D177" s="5"/>
-      <c r="E177" s="2"/>
-      <c r="F177" s="2"/>
+      <c r="D177" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="F177" s="2" t="s">
+        <v>922</v>
+      </c>
       <c r="G177" s="2"/>
-      <c r="H177" s="2"/>
+      <c r="H177" s="2" t="s">
+        <v>926</v>
+      </c>
       <c r="I177" s="2"/>
-      <c r="J177" s="2"/>
+      <c r="J177" s="2" t="s">
+        <v>927</v>
+      </c>
       <c r="K177" s="2"/>
-      <c r="L177" s="7"/>
+      <c r="L177" s="7" t="s">
+        <v>928</v>
+      </c>
       <c r="M177" s="2"/>
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
       <c r="P177" s="2"/>
       <c r="Q177" s="2"/>
-      <c r="R177" s="2"/>
-      <c r="S177" s="2"/>
-      <c r="T177" s="21"/>
-      <c r="U177" s="21"/>
-      <c r="V177" s="21"/>
-      <c r="W177" s="21"/>
+      <c r="R177" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="S177" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="T177" s="5">
+        <v>350</v>
+      </c>
+      <c r="U177" s="5">
+        <v>200</v>
+      </c>
+      <c r="V177" s="5">
+        <v>200</v>
+      </c>
+      <c r="W177" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="178" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A178" s="2"/>
-      <c r="B178" s="2"/>
+      <c r="A178" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>844</v>
+      </c>
       <c r="C178" s="2"/>
-      <c r="D178" s="5"/>
-      <c r="E178" s="2"/>
-      <c r="F178" s="2"/>
+      <c r="D178" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="F178" s="2" t="s">
+        <v>930</v>
+      </c>
       <c r="G178" s="2"/>
-      <c r="H178" s="2"/>
+      <c r="H178" s="2" t="s">
+        <v>931</v>
+      </c>
       <c r="I178" s="2"/>
-      <c r="J178" s="2"/>
+      <c r="J178" s="2" t="s">
+        <v>932</v>
+      </c>
       <c r="K178" s="2"/>
-      <c r="L178" s="7"/>
+      <c r="L178" s="7" t="s">
+        <v>933</v>
+      </c>
       <c r="M178" s="2"/>
       <c r="N178" s="2"/>
       <c r="O178" s="2"/>
       <c r="P178" s="2"/>
       <c r="Q178" s="2"/>
-      <c r="R178" s="2"/>
-      <c r="S178" s="2"/>
-      <c r="T178" s="21"/>
-      <c r="U178" s="21"/>
-      <c r="V178" s="21"/>
-      <c r="W178" s="21"/>
+      <c r="R178" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="S178" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="T178" s="5">
+        <v>81</v>
+      </c>
+      <c r="U178" s="5">
+        <v>72</v>
+      </c>
+      <c r="V178" s="5">
+        <v>42</v>
+      </c>
+      <c r="W178" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="179" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A179" s="2"/>
-      <c r="B179" s="2"/>
+      <c r="A179" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>844</v>
+      </c>
       <c r="C179" s="2"/>
-      <c r="D179" s="5"/>
-      <c r="E179" s="2"/>
-      <c r="F179" s="2"/>
+      <c r="D179" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>930</v>
+      </c>
       <c r="G179" s="2"/>
-      <c r="H179" s="2"/>
+      <c r="H179" s="2" t="s">
+        <v>931</v>
+      </c>
       <c r="I179" s="2"/>
-      <c r="J179" s="2"/>
+      <c r="J179" s="2" t="s">
+        <v>935</v>
+      </c>
       <c r="K179" s="2"/>
-      <c r="L179" s="7"/>
+      <c r="L179" s="7" t="s">
+        <v>936</v>
+      </c>
       <c r="M179" s="2"/>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
       <c r="P179" s="2"/>
       <c r="Q179" s="2"/>
-      <c r="R179" s="2"/>
-      <c r="S179" s="2"/>
-      <c r="T179" s="21"/>
-      <c r="U179" s="21"/>
-      <c r="V179" s="21"/>
-      <c r="W179" s="21"/>
+      <c r="R179" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="S179" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="T179" s="5">
+        <v>76</v>
+      </c>
+      <c r="U179" s="5">
+        <v>68</v>
+      </c>
+      <c r="V179" s="5">
+        <v>38</v>
+      </c>
+      <c r="W179" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="180" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A180" s="2"/>
-      <c r="B180" s="2"/>
+      <c r="A180" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>844</v>
+      </c>
       <c r="C180" s="2"/>
-      <c r="D180" s="5"/>
-      <c r="E180" s="2"/>
-      <c r="F180" s="2"/>
+      <c r="D180" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>922</v>
+      </c>
       <c r="G180" s="2"/>
-      <c r="H180" s="2"/>
+      <c r="H180" s="2" t="s">
+        <v>963</v>
+      </c>
       <c r="I180" s="2"/>
-      <c r="J180" s="2"/>
+      <c r="J180" s="2" t="s">
+        <v>938</v>
+      </c>
       <c r="K180" s="2"/>
-      <c r="L180" s="7"/>
+      <c r="L180" s="7" t="s">
+        <v>939</v>
+      </c>
       <c r="M180" s="2"/>
       <c r="N180" s="2"/>
       <c r="O180" s="2"/>
       <c r="P180" s="2"/>
       <c r="Q180" s="2"/>
-      <c r="R180" s="2"/>
-      <c r="S180" s="2"/>
-      <c r="T180" s="21"/>
-      <c r="U180" s="21"/>
-      <c r="V180" s="21"/>
-      <c r="W180" s="21"/>
+      <c r="R180" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="S180" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="T180" s="5">
+        <v>210</v>
+      </c>
+      <c r="U180" s="5">
+        <v>280</v>
+      </c>
+      <c r="V180" s="5">
+        <v>45</v>
+      </c>
+      <c r="W180" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="181" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A181" s="2"/>
-      <c r="B181" s="2"/>
+      <c r="A181" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>844</v>
+      </c>
       <c r="C181" s="2"/>
-      <c r="D181" s="5"/>
-      <c r="E181" s="2"/>
-      <c r="F181" s="2"/>
+      <c r="D181" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>942</v>
+      </c>
       <c r="G181" s="2"/>
-      <c r="H181" s="2"/>
+      <c r="H181" s="2" t="s">
+        <v>943</v>
+      </c>
       <c r="I181" s="2"/>
-      <c r="J181" s="2"/>
+      <c r="J181" s="2" t="s">
+        <v>814</v>
+      </c>
       <c r="K181" s="2"/>
-      <c r="L181" s="7"/>
+      <c r="L181" s="7" t="s">
+        <v>944</v>
+      </c>
       <c r="M181" s="2"/>
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
       <c r="P181" s="2"/>
       <c r="Q181" s="2"/>
-      <c r="R181" s="2"/>
-      <c r="S181" s="2"/>
-      <c r="T181" s="21"/>
-      <c r="U181" s="21"/>
-      <c r="V181" s="21"/>
-      <c r="W181" s="21"/>
+      <c r="R181" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S181" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="T181" s="5">
+        <v>215</v>
+      </c>
+      <c r="U181" s="5">
+        <v>85</v>
+      </c>
+      <c r="V181" s="5">
+        <v>55</v>
+      </c>
+      <c r="W181" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="182" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="C182" s="2"/>
-      <c r="D182" s="5" t="s">
+      <c r="D182" s="2" t="s">
         <v>161</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="G182" s="2"/>
       <c r="H182" s="2"/>
       <c r="I182" s="2"/>
       <c r="J182" s="2" t="s">
-        <v>854</v>
+        <v>945</v>
       </c>
       <c r="K182" s="2"/>
       <c r="L182" s="7" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="M182" s="2"/>
       <c r="N182" s="2"/>
@@ -12544,116 +12932,204 @@
       <c r="S182" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="T182" s="21">
+      <c r="T182" s="5">
         <v>350</v>
       </c>
-      <c r="U182" s="21"/>
-      <c r="V182" s="21"/>
-      <c r="W182" s="21">
+      <c r="U182" s="5"/>
+      <c r="V182" s="5"/>
+      <c r="W182" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="183" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A183" s="2"/>
-      <c r="B183" s="2"/>
-      <c r="C183" s="2"/>
-      <c r="D183" s="5"/>
-      <c r="E183" s="2"/>
-      <c r="F183" s="2"/>
+      <c r="A183" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F183" s="2" t="s">
+        <v>948</v>
+      </c>
       <c r="G183" s="2"/>
-      <c r="H183" s="2"/>
+      <c r="H183" s="2" t="s">
+        <v>949</v>
+      </c>
       <c r="I183" s="2"/>
-      <c r="J183" s="2"/>
-      <c r="K183" s="2"/>
-      <c r="L183" s="7"/>
+      <c r="J183" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="K183" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="L183" s="7" t="s">
+        <v>950</v>
+      </c>
       <c r="M183" s="2"/>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
       <c r="P183" s="2"/>
       <c r="Q183" s="2"/>
-      <c r="R183" s="2"/>
-      <c r="S183" s="2"/>
-      <c r="T183" s="21"/>
-      <c r="U183" s="21"/>
-      <c r="V183" s="21"/>
-      <c r="W183" s="21"/>
+      <c r="R183" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S183" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="T183" s="5">
+        <v>250</v>
+      </c>
+      <c r="U183" s="5"/>
+      <c r="V183" s="5"/>
+      <c r="W183" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="184" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A184" s="2"/>
-      <c r="B184" s="2"/>
-      <c r="C184" s="2"/>
-      <c r="D184" s="5"/>
-      <c r="E184" s="2"/>
-      <c r="F184" s="2"/>
+      <c r="A184" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F184" s="2" t="s">
+        <v>587</v>
+      </c>
       <c r="G184" s="2"/>
-      <c r="H184" s="2"/>
+      <c r="H184" s="2" t="s">
+        <v>952</v>
+      </c>
       <c r="I184" s="2"/>
-      <c r="J184" s="2"/>
-      <c r="K184" s="2"/>
-      <c r="L184" s="7"/>
-      <c r="M184" s="2"/>
+      <c r="J184" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="K184" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="L184" s="7" t="s">
+        <v>955</v>
+      </c>
+      <c r="M184" s="2" t="s">
+        <v>956</v>
+      </c>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
       <c r="P184" s="2"/>
       <c r="Q184" s="2"/>
-      <c r="R184" s="2"/>
-      <c r="S184" s="2"/>
-      <c r="T184" s="21"/>
-      <c r="U184" s="21"/>
-      <c r="V184" s="21"/>
-      <c r="W184" s="21"/>
+      <c r="R184" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S184" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="T184" s="5">
+        <v>300</v>
+      </c>
+      <c r="U184" s="5"/>
+      <c r="V184" s="5"/>
+      <c r="W184" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="185" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A185" s="2"/>
-      <c r="B185" s="2"/>
-      <c r="C185" s="2"/>
-      <c r="D185" s="5"/>
-      <c r="E185" s="2"/>
-      <c r="F185" s="2"/>
+      <c r="A185" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F185" s="2" t="s">
+        <v>958</v>
+      </c>
       <c r="G185" s="2"/>
-      <c r="H185" s="2"/>
+      <c r="H185" s="2" t="s">
+        <v>959</v>
+      </c>
       <c r="I185" s="2"/>
-      <c r="J185" s="2"/>
-      <c r="K185" s="2"/>
-      <c r="L185" s="7"/>
+      <c r="J185" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="K185" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="L185" s="7" t="s">
+        <v>962</v>
+      </c>
       <c r="M185" s="2"/>
       <c r="N185" s="2"/>
       <c r="O185" s="2"/>
       <c r="P185" s="2"/>
       <c r="Q185" s="2"/>
-      <c r="R185" s="2"/>
-      <c r="S185" s="2"/>
-      <c r="T185" s="21"/>
-      <c r="U185" s="21"/>
-      <c r="V185" s="21"/>
-      <c r="W185" s="21"/>
+      <c r="R185" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="S185" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="T185" s="5">
+        <v>280</v>
+      </c>
+      <c r="U185" s="5"/>
+      <c r="V185" s="5"/>
+      <c r="W185" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="186" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>856</v>
+        <v>213</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="C186" s="2"/>
-      <c r="D186" s="5" t="s">
-        <v>858</v>
+      <c r="D186" s="2" t="s">
+        <v>788</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>485</v>
+        <v>141</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="G186" s="2"/>
       <c r="H186" s="2"/>
       <c r="I186" s="2"/>
       <c r="J186" s="2" t="s">
-        <v>860</v>
-      </c>
-      <c r="K186" s="2"/>
+        <v>854</v>
+      </c>
+      <c r="K186" s="2" t="s">
+        <v>855</v>
+      </c>
       <c r="L186" s="7" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="M186" s="2"/>
       <c r="N186" s="2"/>
@@ -12661,40 +13137,48 @@
       <c r="P186" s="2"/>
       <c r="Q186" s="2"/>
       <c r="R186" s="2" t="s">
-        <v>30</v>
+        <v>152</v>
       </c>
       <c r="S186" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="T186" s="21"/>
-      <c r="U186" s="21"/>
-      <c r="V186" s="21"/>
-      <c r="W186" s="21"/>
+        <v>64</v>
+      </c>
+      <c r="T186" s="5" t="s">
+        <v>857</v>
+      </c>
+      <c r="U186" s="5"/>
+      <c r="V186" s="5"/>
+      <c r="W186" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="187" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>862</v>
+        <v>213</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>863</v>
+        <v>852</v>
       </c>
       <c r="C187" s="2"/>
-      <c r="D187" s="5" t="s">
-        <v>864</v>
-      </c>
-      <c r="E187" s="2"/>
+      <c r="D187" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>858</v>
+      </c>
       <c r="F187" s="2" t="s">
-        <v>108</v>
+        <v>859</v>
       </c>
       <c r="G187" s="2"/>
       <c r="H187" s="2"/>
       <c r="I187" s="2"/>
       <c r="J187" s="2" t="s">
-        <v>865</v>
-      </c>
-      <c r="K187" s="2"/>
+        <v>860</v>
+      </c>
+      <c r="K187" s="2" t="s">
+        <v>861</v>
+      </c>
       <c r="L187" s="7" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="M187" s="2"/>
       <c r="N187" s="2"/>
@@ -12702,44 +13186,48 @@
       <c r="P187" s="2"/>
       <c r="Q187" s="2"/>
       <c r="R187" s="2" t="s">
-        <v>30</v>
+        <v>863</v>
       </c>
       <c r="S187" s="2" t="s">
-        <v>867</v>
-      </c>
-      <c r="T187" s="21"/>
-      <c r="U187" s="21"/>
-      <c r="V187" s="21"/>
-      <c r="W187" s="21">
-        <v>3</v>
+        <v>864</v>
+      </c>
+      <c r="T187" s="5" t="s">
+        <v>865</v>
+      </c>
+      <c r="U187" s="5"/>
+      <c r="V187" s="5"/>
+      <c r="W187" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="188" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>868</v>
+        <v>213</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>869</v>
+        <v>852</v>
       </c>
       <c r="C188" s="2"/>
-      <c r="D188" s="5" t="s">
-        <v>870</v>
+      <c r="D188" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>871</v>
+        <v>851</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
       <c r="G188" s="2"/>
       <c r="H188" s="2"/>
       <c r="I188" s="2"/>
       <c r="J188" s="2" t="s">
-        <v>873</v>
-      </c>
-      <c r="K188" s="2"/>
+        <v>867</v>
+      </c>
+      <c r="K188" s="2" t="s">
+        <v>868</v>
+      </c>
       <c r="L188" s="7" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="M188" s="2"/>
       <c r="N188" s="2"/>
@@ -12747,46 +13235,48 @@
       <c r="P188" s="2"/>
       <c r="Q188" s="2"/>
       <c r="R188" s="2" t="s">
-        <v>30</v>
+        <v>870</v>
       </c>
       <c r="S188" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="T188" s="21">
-        <v>200</v>
-      </c>
-      <c r="U188" s="21"/>
-      <c r="V188" s="21"/>
-      <c r="W188" s="21">
-        <v>3</v>
+      <c r="T188" s="5" t="s">
+        <v>871</v>
+      </c>
+      <c r="U188" s="5"/>
+      <c r="V188" s="5"/>
+      <c r="W188" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="189" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>875</v>
+        <v>213</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>876</v>
+        <v>852</v>
       </c>
       <c r="C189" s="2"/>
-      <c r="D189" s="5" t="s">
-        <v>705</v>
+      <c r="D189" s="2" t="s">
+        <v>554</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>877</v>
+        <v>141</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
       <c r="G189" s="2"/>
       <c r="H189" s="2"/>
       <c r="I189" s="2"/>
       <c r="J189" s="2" t="s">
-        <v>879</v>
-      </c>
-      <c r="K189" s="2"/>
+        <v>873</v>
+      </c>
+      <c r="K189" s="2" t="s">
+        <v>874</v>
+      </c>
       <c r="L189" s="7" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="M189" s="2"/>
       <c r="N189" s="2"/>
@@ -12794,1000 +13284,168 @@
       <c r="P189" s="2"/>
       <c r="Q189" s="2"/>
       <c r="R189" s="2" t="s">
-        <v>30</v>
+        <v>152</v>
       </c>
       <c r="S189" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="T189" s="21">
-        <v>226</v>
-      </c>
-      <c r="U189" s="21"/>
-      <c r="V189" s="21"/>
-      <c r="W189" s="21">
-        <v>3</v>
+        <v>64</v>
+      </c>
+      <c r="T189" s="5" t="s">
+        <v>876</v>
+      </c>
+      <c r="U189" s="5"/>
+      <c r="V189" s="5"/>
+      <c r="W189" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="190" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A190" s="2"/>
-      <c r="B190" s="2"/>
+      <c r="A190" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>852</v>
+      </c>
       <c r="C190" s="2"/>
-      <c r="D190" s="5"/>
-      <c r="E190" s="2"/>
-      <c r="F190" s="2"/>
+      <c r="D190" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F190" s="2" t="s">
+        <v>853</v>
+      </c>
       <c r="G190" s="2"/>
       <c r="H190" s="2"/>
       <c r="I190" s="2"/>
-      <c r="J190" s="2"/>
-      <c r="K190" s="2"/>
-      <c r="L190" s="7"/>
+      <c r="J190" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="K190" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="L190" s="7" t="s">
+        <v>879</v>
+      </c>
       <c r="M190" s="2"/>
       <c r="N190" s="2"/>
       <c r="O190" s="2"/>
       <c r="P190" s="2"/>
       <c r="Q190" s="2"/>
-      <c r="R190" s="2"/>
-      <c r="S190" s="2"/>
-      <c r="T190" s="21"/>
-      <c r="U190" s="21"/>
-      <c r="V190" s="21"/>
-      <c r="W190" s="21"/>
+      <c r="R190" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="S190" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="T190" s="5" t="s">
+        <v>880</v>
+      </c>
+      <c r="U190" s="5"/>
+      <c r="V190" s="5"/>
+      <c r="W190" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="191" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A191" s="2"/>
-      <c r="B191" s="2"/>
+      <c r="A191" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>852</v>
+      </c>
       <c r="C191" s="2"/>
-      <c r="D191" s="5"/>
-      <c r="E191" s="2"/>
-      <c r="F191" s="2"/>
+      <c r="D191" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="F191" s="2" t="s">
+        <v>883</v>
+      </c>
       <c r="G191" s="2"/>
       <c r="H191" s="2"/>
       <c r="I191" s="2"/>
-      <c r="J191" s="2"/>
-      <c r="K191" s="2"/>
-      <c r="L191" s="7"/>
+      <c r="J191" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="K191" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="L191" s="7" t="s">
+        <v>886</v>
+      </c>
       <c r="M191" s="2"/>
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
       <c r="P191" s="2"/>
       <c r="Q191" s="2"/>
-      <c r="R191" s="2"/>
-      <c r="S191" s="2"/>
-      <c r="T191" s="21"/>
-      <c r="U191" s="21"/>
-      <c r="V191" s="21"/>
-      <c r="W191" s="21"/>
+      <c r="R191" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="S191" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="T191" s="5">
+        <v>85</v>
+      </c>
+      <c r="U191" s="5"/>
+      <c r="V191" s="5"/>
+      <c r="W191" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="192" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A192" s="2"/>
-      <c r="B192" s="2"/>
-      <c r="C192" s="2"/>
-      <c r="D192" s="5"/>
-      <c r="E192" s="2"/>
-      <c r="F192" s="2"/>
-      <c r="G192" s="2"/>
-      <c r="H192" s="2"/>
-      <c r="I192" s="2"/>
-      <c r="J192" s="2"/>
-      <c r="K192" s="2"/>
-      <c r="L192" s="7"/>
-      <c r="M192" s="2"/>
-      <c r="N192" s="2"/>
-      <c r="O192" s="2"/>
-      <c r="P192" s="2"/>
-      <c r="Q192" s="2"/>
-      <c r="R192" s="2"/>
-      <c r="S192" s="2"/>
-      <c r="T192" s="21"/>
-      <c r="U192" s="21"/>
-      <c r="V192" s="21"/>
-      <c r="W192" s="21"/>
-    </row>
-    <row r="193" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A193" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="B193" s="2" t="s">
-        <v>876</v>
-      </c>
-      <c r="C193" s="2"/>
-      <c r="D193" s="5">
-        <v>1698</v>
-      </c>
-      <c r="E193" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="F193" s="2" t="s">
-        <v>881</v>
-      </c>
-      <c r="G193" s="2"/>
-      <c r="H193" s="2"/>
-      <c r="I193" s="2"/>
-      <c r="J193" s="2" t="s">
-        <v>882</v>
-      </c>
-      <c r="K193" s="2"/>
-      <c r="L193" s="7" t="s">
-        <v>883</v>
-      </c>
-      <c r="M193" s="2"/>
-      <c r="N193" s="2"/>
-      <c r="O193" s="2"/>
-      <c r="P193" s="2"/>
-      <c r="Q193" s="2"/>
-      <c r="R193" s="2" t="s">
+      <c r="A192" s="10" t="s">
+        <v>889</v>
+      </c>
+      <c r="B192" s="10" t="s">
+        <v>890</v>
+      </c>
+      <c r="C192" s="10"/>
+      <c r="D192" s="14" t="s">
+        <v>891</v>
+      </c>
+      <c r="E192" s="10"/>
+      <c r="F192" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="G192" s="10"/>
+      <c r="H192" s="10" t="s">
+        <v>892</v>
+      </c>
+      <c r="I192" s="10"/>
+      <c r="J192" s="10" t="s">
+        <v>893</v>
+      </c>
+      <c r="K192" s="10"/>
+      <c r="L192" s="11" t="s">
+        <v>894</v>
+      </c>
+      <c r="M192" s="10"/>
+      <c r="N192" s="10"/>
+      <c r="O192" s="10"/>
+      <c r="P192" s="10"/>
+      <c r="Q192" s="10"/>
+      <c r="R192" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="S193" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="T193" s="21">
-        <v>180</v>
-      </c>
-      <c r="U193" s="21"/>
-      <c r="V193" s="21"/>
-      <c r="W193" s="21">
+      <c r="S192" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="T192" s="23">
+        <v>240</v>
+      </c>
+      <c r="U192" s="23">
+        <v>1350</v>
+      </c>
+      <c r="V192" s="23">
+        <v>1370</v>
+      </c>
+      <c r="W192" s="23">
         <v>3</v>
       </c>
-    </row>
-    <row r="194" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A194" s="2"/>
-      <c r="B194" s="2"/>
-      <c r="C194" s="2"/>
-      <c r="D194" s="5"/>
-      <c r="E194" s="2"/>
-      <c r="F194" s="2"/>
-      <c r="G194" s="2"/>
-      <c r="H194" s="2"/>
-      <c r="I194" s="2"/>
-      <c r="J194" s="2"/>
-      <c r="K194" s="2"/>
-      <c r="L194" s="7"/>
-      <c r="M194" s="2"/>
-      <c r="N194" s="2"/>
-      <c r="O194" s="2"/>
-      <c r="P194" s="2"/>
-      <c r="Q194" s="2"/>
-      <c r="R194" s="2"/>
-      <c r="S194" s="2"/>
-      <c r="T194" s="21"/>
-      <c r="U194" s="21"/>
-      <c r="V194" s="21"/>
-      <c r="W194" s="21"/>
-    </row>
-    <row r="195" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A195" s="2"/>
-      <c r="B195" s="2"/>
-      <c r="C195" s="2"/>
-      <c r="D195" s="5"/>
-      <c r="E195" s="2"/>
-      <c r="F195" s="2"/>
-      <c r="G195" s="2"/>
-      <c r="H195" s="2"/>
-      <c r="I195" s="2"/>
-      <c r="J195" s="2"/>
-      <c r="K195" s="2"/>
-      <c r="L195" s="7"/>
-      <c r="M195" s="2"/>
-      <c r="N195" s="2"/>
-      <c r="O195" s="2"/>
-      <c r="P195" s="2"/>
-      <c r="Q195" s="2"/>
-      <c r="R195" s="2"/>
-      <c r="S195" s="2"/>
-      <c r="T195" s="21"/>
-      <c r="U195" s="21"/>
-      <c r="V195" s="21"/>
-      <c r="W195" s="21"/>
-    </row>
-    <row r="196" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A196" s="2"/>
-      <c r="B196" s="2"/>
-      <c r="C196" s="2"/>
-      <c r="D196" s="5"/>
-      <c r="E196" s="2"/>
-      <c r="F196" s="2"/>
-      <c r="G196" s="2"/>
-      <c r="H196" s="2"/>
-      <c r="I196" s="2"/>
-      <c r="J196" s="2"/>
-      <c r="K196" s="2"/>
-      <c r="L196" s="7"/>
-      <c r="M196" s="2"/>
-      <c r="N196" s="2"/>
-      <c r="O196" s="2"/>
-      <c r="P196" s="2"/>
-      <c r="Q196" s="2"/>
-      <c r="R196" s="2"/>
-      <c r="S196" s="2"/>
-      <c r="T196" s="21"/>
-      <c r="U196" s="21"/>
-      <c r="V196" s="21"/>
-      <c r="W196" s="21"/>
-    </row>
-    <row r="197" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A197" s="2" t="s">
-        <v>884</v>
-      </c>
-      <c r="B197" s="2" t="s">
-        <v>885</v>
-      </c>
-      <c r="C197" s="2"/>
-      <c r="D197" s="5" t="s">
-        <v>886</v>
-      </c>
-      <c r="E197" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F197" s="2" t="s">
-        <v>887</v>
-      </c>
-      <c r="G197" s="2"/>
-      <c r="H197" s="2"/>
-      <c r="I197" s="2"/>
-      <c r="J197" s="2" t="s">
-        <v>888</v>
-      </c>
-      <c r="K197" s="2"/>
-      <c r="L197" s="7" t="s">
-        <v>889</v>
-      </c>
-      <c r="M197" s="2"/>
-      <c r="N197" s="2"/>
-      <c r="O197" s="2"/>
-      <c r="P197" s="2"/>
-      <c r="Q197" s="2"/>
-      <c r="R197" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S197" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="T197" s="21"/>
-      <c r="U197" s="21"/>
-      <c r="V197" s="21"/>
-      <c r="W197" s="21">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="198" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A198" s="2"/>
-      <c r="B198" s="2"/>
-      <c r="C198" s="2"/>
-      <c r="D198" s="5"/>
-      <c r="E198" s="2"/>
-      <c r="F198" s="2"/>
-      <c r="G198" s="2"/>
-      <c r="H198" s="2"/>
-      <c r="I198" s="2"/>
-      <c r="J198" s="2"/>
-      <c r="K198" s="2"/>
-      <c r="L198" s="7"/>
-      <c r="M198" s="2"/>
-      <c r="N198" s="2"/>
-      <c r="O198" s="2"/>
-      <c r="P198" s="2"/>
-      <c r="Q198" s="2"/>
-      <c r="R198" s="2"/>
-      <c r="S198" s="2"/>
-      <c r="T198" s="21"/>
-      <c r="U198" s="21"/>
-      <c r="V198" s="21"/>
-      <c r="W198" s="21"/>
-    </row>
-    <row r="199" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A199" s="2"/>
-      <c r="B199" s="2"/>
-      <c r="C199" s="2"/>
-      <c r="D199" s="5"/>
-      <c r="E199" s="2"/>
-      <c r="F199" s="2"/>
-      <c r="G199" s="2"/>
-      <c r="H199" s="2"/>
-      <c r="I199" s="2"/>
-      <c r="J199" s="2"/>
-      <c r="K199" s="2"/>
-      <c r="L199" s="7"/>
-      <c r="M199" s="2"/>
-      <c r="N199" s="2"/>
-      <c r="O199" s="2"/>
-      <c r="P199" s="2"/>
-      <c r="Q199" s="2"/>
-      <c r="R199" s="2"/>
-      <c r="S199" s="2"/>
-      <c r="T199" s="21"/>
-      <c r="U199" s="21"/>
-      <c r="V199" s="21"/>
-      <c r="W199" s="21"/>
-    </row>
-    <row r="200" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A200" s="2"/>
-      <c r="B200" s="2"/>
-      <c r="C200" s="2"/>
-      <c r="D200" s="5"/>
-      <c r="E200" s="2"/>
-      <c r="F200" s="2"/>
-      <c r="G200" s="2"/>
-      <c r="H200" s="2"/>
-      <c r="I200" s="2"/>
-      <c r="J200" s="2"/>
-      <c r="K200" s="2"/>
-      <c r="L200" s="7"/>
-      <c r="M200" s="2"/>
-      <c r="N200" s="2"/>
-      <c r="O200" s="2"/>
-      <c r="P200" s="2"/>
-      <c r="Q200" s="2"/>
-      <c r="R200" s="2"/>
-      <c r="S200" s="2"/>
-      <c r="T200" s="21"/>
-      <c r="U200" s="21"/>
-      <c r="V200" s="21"/>
-      <c r="W200" s="21"/>
-    </row>
-    <row r="201" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A201" s="2" t="s">
-        <v>890</v>
-      </c>
-      <c r="B201" s="2" t="s">
-        <v>891</v>
-      </c>
-      <c r="C201" s="2"/>
-      <c r="D201" s="5" t="s">
-        <v>649</v>
-      </c>
-      <c r="E201" s="2" t="s">
-        <v>892</v>
-      </c>
-      <c r="F201" s="2" t="s">
-        <v>893</v>
-      </c>
-      <c r="G201" s="2"/>
-      <c r="H201" s="2"/>
-      <c r="I201" s="2"/>
-      <c r="J201" s="2" t="s">
-        <v>894</v>
-      </c>
-      <c r="K201" s="2"/>
-      <c r="L201" s="7" t="s">
-        <v>895</v>
-      </c>
-      <c r="M201" s="2"/>
-      <c r="N201" s="2"/>
-      <c r="O201" s="2"/>
-      <c r="P201" s="2"/>
-      <c r="Q201" s="2"/>
-      <c r="R201" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S201" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="T201" s="21"/>
-      <c r="U201" s="21"/>
-      <c r="V201" s="21"/>
-      <c r="W201" s="21">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="202" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A202" s="2"/>
-      <c r="B202" s="2"/>
-      <c r="C202" s="2"/>
-      <c r="D202" s="5"/>
-      <c r="E202" s="2"/>
-      <c r="F202" s="2"/>
-      <c r="G202" s="2"/>
-      <c r="H202" s="2"/>
-      <c r="I202" s="2"/>
-      <c r="J202" s="2"/>
-      <c r="K202" s="2"/>
-      <c r="L202" s="7"/>
-      <c r="M202" s="2"/>
-      <c r="N202" s="2"/>
-      <c r="O202" s="2"/>
-      <c r="P202" s="2"/>
-      <c r="Q202" s="2"/>
-      <c r="R202" s="2"/>
-      <c r="S202" s="2"/>
-      <c r="T202" s="21"/>
-      <c r="U202" s="21"/>
-      <c r="V202" s="21"/>
-      <c r="W202" s="21"/>
-    </row>
-    <row r="203" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A203" s="2"/>
-      <c r="B203" s="2"/>
-      <c r="C203" s="2"/>
-      <c r="D203" s="5"/>
-      <c r="E203" s="2"/>
-      <c r="F203" s="2"/>
-      <c r="G203" s="2"/>
-      <c r="H203" s="2"/>
-      <c r="I203" s="2"/>
-      <c r="J203" s="2"/>
-      <c r="K203" s="2"/>
-      <c r="L203" s="7"/>
-      <c r="M203" s="2"/>
-      <c r="N203" s="2"/>
-      <c r="O203" s="2"/>
-      <c r="P203" s="2"/>
-      <c r="Q203" s="2"/>
-      <c r="R203" s="2"/>
-      <c r="S203" s="2"/>
-      <c r="T203" s="21"/>
-      <c r="U203" s="21"/>
-      <c r="V203" s="21"/>
-      <c r="W203" s="21"/>
-    </row>
-    <row r="204" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A204" s="8"/>
-      <c r="B204" s="8"/>
-      <c r="C204" s="8"/>
-      <c r="D204" s="13"/>
-      <c r="E204" s="8"/>
-      <c r="F204" s="8"/>
-      <c r="G204" s="8"/>
-      <c r="H204" s="8"/>
-      <c r="I204" s="8"/>
-      <c r="J204" s="8"/>
-      <c r="K204" s="8"/>
-      <c r="L204" s="9"/>
-      <c r="M204" s="8"/>
-      <c r="N204" s="8"/>
-      <c r="O204" s="8"/>
-      <c r="P204" s="8"/>
-      <c r="Q204" s="8"/>
-      <c r="R204" s="8"/>
-      <c r="S204" s="8"/>
-      <c r="T204" s="22"/>
-      <c r="U204" s="22"/>
-      <c r="V204" s="22"/>
-      <c r="W204" s="22"/>
-    </row>
-    <row r="205" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A205" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>896</v>
-      </c>
-      <c r="C205" s="2"/>
-      <c r="D205" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="E205" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="F205" s="2" t="s">
-        <v>897</v>
-      </c>
-      <c r="G205" s="2"/>
-      <c r="H205" s="2"/>
-      <c r="I205" s="2"/>
-      <c r="J205" s="2" t="s">
-        <v>898</v>
-      </c>
-      <c r="K205" s="2" t="s">
-        <v>899</v>
-      </c>
-      <c r="L205" s="7" t="s">
-        <v>900</v>
-      </c>
-      <c r="M205" s="2"/>
-      <c r="N205" s="2"/>
-      <c r="O205" s="2"/>
-      <c r="P205" s="2"/>
-      <c r="Q205" s="2"/>
-      <c r="R205" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="S205" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="T205" s="5" t="s">
-        <v>901</v>
-      </c>
-      <c r="U205" s="5"/>
-      <c r="V205" s="5"/>
-      <c r="W205" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="206" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A206" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B206" s="2" t="s">
-        <v>896</v>
-      </c>
-      <c r="C206" s="2"/>
-      <c r="D206" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="E206" s="2" t="s">
-        <v>902</v>
-      </c>
-      <c r="F206" s="2" t="s">
-        <v>903</v>
-      </c>
-      <c r="G206" s="2"/>
-      <c r="H206" s="2"/>
-      <c r="I206" s="2"/>
-      <c r="J206" s="2" t="s">
-        <v>904</v>
-      </c>
-      <c r="K206" s="2" t="s">
-        <v>905</v>
-      </c>
-      <c r="L206" s="7" t="s">
-        <v>906</v>
-      </c>
-      <c r="M206" s="2"/>
-      <c r="N206" s="2"/>
-      <c r="O206" s="2"/>
-      <c r="P206" s="2"/>
-      <c r="Q206" s="2"/>
-      <c r="R206" s="2" t="s">
-        <v>907</v>
-      </c>
-      <c r="S206" s="2" t="s">
-        <v>908</v>
-      </c>
-      <c r="T206" s="5" t="s">
-        <v>909</v>
-      </c>
-      <c r="U206" s="5"/>
-      <c r="V206" s="5"/>
-      <c r="W206" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="207" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A207" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B207" s="2" t="s">
-        <v>896</v>
-      </c>
-      <c r="C207" s="2"/>
-      <c r="D207" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E207" s="2" t="s">
-        <v>877</v>
-      </c>
-      <c r="F207" s="2" t="s">
-        <v>910</v>
-      </c>
-      <c r="G207" s="2"/>
-      <c r="H207" s="2"/>
-      <c r="I207" s="2"/>
-      <c r="J207" s="2" t="s">
-        <v>911</v>
-      </c>
-      <c r="K207" s="2" t="s">
-        <v>912</v>
-      </c>
-      <c r="L207" s="7" t="s">
-        <v>913</v>
-      </c>
-      <c r="M207" s="2"/>
-      <c r="N207" s="2"/>
-      <c r="O207" s="2"/>
-      <c r="P207" s="2"/>
-      <c r="Q207" s="2"/>
-      <c r="R207" s="2" t="s">
-        <v>914</v>
-      </c>
-      <c r="S207" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="T207" s="5" t="s">
-        <v>915</v>
-      </c>
-      <c r="U207" s="5"/>
-      <c r="V207" s="5"/>
-      <c r="W207" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="208" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A208" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B208" s="2" t="s">
-        <v>896</v>
-      </c>
-      <c r="C208" s="2"/>
-      <c r="D208" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="E208" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="F208" s="2" t="s">
-        <v>916</v>
-      </c>
-      <c r="G208" s="2"/>
-      <c r="H208" s="2"/>
-      <c r="I208" s="2"/>
-      <c r="J208" s="2" t="s">
-        <v>917</v>
-      </c>
-      <c r="K208" s="2" t="s">
-        <v>918</v>
-      </c>
-      <c r="L208" s="7" t="s">
-        <v>919</v>
-      </c>
-      <c r="M208" s="2"/>
-      <c r="N208" s="2"/>
-      <c r="O208" s="2"/>
-      <c r="P208" s="2"/>
-      <c r="Q208" s="2"/>
-      <c r="R208" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="S208" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="T208" s="5" t="s">
-        <v>920</v>
-      </c>
-      <c r="U208" s="5"/>
-      <c r="V208" s="5"/>
-      <c r="W208" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="209" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A209" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B209" s="2" t="s">
-        <v>896</v>
-      </c>
-      <c r="C209" s="2"/>
-      <c r="D209" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="E209" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="F209" s="2" t="s">
-        <v>897</v>
-      </c>
-      <c r="G209" s="2"/>
-      <c r="H209" s="2"/>
-      <c r="I209" s="2"/>
-      <c r="J209" s="2" t="s">
-        <v>921</v>
-      </c>
-      <c r="K209" s="2" t="s">
-        <v>922</v>
-      </c>
-      <c r="L209" s="7" t="s">
-        <v>923</v>
-      </c>
-      <c r="M209" s="2"/>
-      <c r="N209" s="2"/>
-      <c r="O209" s="2"/>
-      <c r="P209" s="2"/>
-      <c r="Q209" s="2"/>
-      <c r="R209" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="S209" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="T209" s="5" t="s">
-        <v>924</v>
-      </c>
-      <c r="U209" s="5"/>
-      <c r="V209" s="5"/>
-      <c r="W209" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="210" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A210" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B210" s="2" t="s">
-        <v>896</v>
-      </c>
-      <c r="C210" s="2"/>
-      <c r="D210" s="2" t="s">
-        <v>925</v>
-      </c>
-      <c r="E210" s="2" t="s">
-        <v>926</v>
-      </c>
-      <c r="F210" s="2" t="s">
-        <v>927</v>
-      </c>
-      <c r="G210" s="2"/>
-      <c r="H210" s="2"/>
-      <c r="I210" s="2"/>
-      <c r="J210" s="2" t="s">
-        <v>928</v>
-      </c>
-      <c r="K210" s="2" t="s">
-        <v>929</v>
-      </c>
-      <c r="L210" s="7" t="s">
-        <v>930</v>
-      </c>
-      <c r="M210" s="2"/>
-      <c r="N210" s="2"/>
-      <c r="O210" s="2"/>
-      <c r="P210" s="2"/>
-      <c r="Q210" s="2"/>
-      <c r="R210" s="2" t="s">
-        <v>931</v>
-      </c>
-      <c r="S210" s="2" t="s">
-        <v>932</v>
-      </c>
-      <c r="T210" s="5">
-        <v>85</v>
-      </c>
-      <c r="U210" s="5"/>
-      <c r="V210" s="5"/>
-      <c r="W210" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="211" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A211" s="10" t="s">
-        <v>933</v>
-      </c>
-      <c r="B211" s="10" t="s">
-        <v>934</v>
-      </c>
-      <c r="C211" s="10"/>
-      <c r="D211" s="14" t="s">
-        <v>935</v>
-      </c>
-      <c r="E211" s="10"/>
-      <c r="F211" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="G211" s="10"/>
-      <c r="H211" s="10" t="s">
-        <v>936</v>
-      </c>
-      <c r="I211" s="10"/>
-      <c r="J211" s="10" t="s">
-        <v>937</v>
-      </c>
-      <c r="K211" s="10"/>
-      <c r="L211" s="11" t="s">
-        <v>938</v>
-      </c>
-      <c r="M211" s="10"/>
-      <c r="N211" s="10"/>
-      <c r="O211" s="10"/>
-      <c r="P211" s="10"/>
-      <c r="Q211" s="10"/>
-      <c r="R211" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="S211" s="10" t="s">
-        <v>681</v>
-      </c>
-      <c r="T211" s="23">
-        <v>240</v>
-      </c>
-      <c r="U211" s="23">
-        <v>1350</v>
-      </c>
-      <c r="V211" s="23">
-        <v>1370</v>
-      </c>
-      <c r="W211" s="23">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="212" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A212" s="2"/>
-      <c r="B212" s="2"/>
-      <c r="C212" s="2"/>
-      <c r="D212" s="5"/>
-      <c r="E212" s="2"/>
-      <c r="F212" s="2"/>
-      <c r="G212" s="2"/>
-      <c r="H212" s="2"/>
-      <c r="I212" s="2"/>
-      <c r="J212" s="2"/>
-      <c r="K212" s="2"/>
-      <c r="L212" s="7"/>
-      <c r="M212" s="2"/>
-      <c r="N212" s="2"/>
-      <c r="O212" s="2"/>
-      <c r="P212" s="2"/>
-      <c r="Q212" s="2"/>
-      <c r="R212" s="2"/>
-      <c r="S212" s="2"/>
-      <c r="T212" s="21"/>
-      <c r="U212" s="21"/>
-      <c r="V212" s="21"/>
-      <c r="W212" s="21"/>
-    </row>
-    <row r="213" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A213" s="2"/>
-      <c r="B213" s="2"/>
-      <c r="C213" s="2"/>
-      <c r="D213" s="5"/>
-      <c r="E213" s="2"/>
-      <c r="F213" s="2"/>
-      <c r="G213" s="2"/>
-      <c r="H213" s="2"/>
-      <c r="I213" s="2"/>
-      <c r="J213" s="2"/>
-      <c r="K213" s="2"/>
-      <c r="L213" s="7"/>
-      <c r="M213" s="2"/>
-      <c r="N213" s="2"/>
-      <c r="O213" s="2"/>
-      <c r="P213" s="2"/>
-      <c r="Q213" s="2"/>
-      <c r="R213" s="2"/>
-      <c r="S213" s="2"/>
-      <c r="T213" s="21"/>
-      <c r="U213" s="21"/>
-      <c r="V213" s="21"/>
-      <c r="W213" s="21"/>
-    </row>
-    <row r="214" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="2"/>
-      <c r="B214" s="2"/>
-      <c r="C214" s="2"/>
-      <c r="D214" s="5"/>
-      <c r="E214" s="2"/>
-      <c r="F214" s="2"/>
-      <c r="G214" s="2"/>
-      <c r="H214" s="2"/>
-      <c r="I214" s="2"/>
-      <c r="J214" s="2"/>
-      <c r="K214" s="2"/>
-      <c r="L214" s="7"/>
-      <c r="M214" s="2"/>
-      <c r="N214" s="2"/>
-      <c r="O214" s="2"/>
-      <c r="P214" s="2"/>
-      <c r="Q214" s="2"/>
-      <c r="R214" s="2"/>
-      <c r="S214" s="2"/>
-      <c r="T214" s="21"/>
-      <c r="U214" s="21"/>
-      <c r="V214" s="21"/>
-      <c r="W214" s="21"/>
-    </row>
-    <row r="215" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="2" t="s">
-        <v>939</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>940</v>
-      </c>
-      <c r="C215" s="2"/>
-      <c r="D215" s="5" t="s">
-        <v>941</v>
-      </c>
-      <c r="E215" s="2"/>
-      <c r="F215" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G215" s="2"/>
-      <c r="H215" s="2"/>
-      <c r="I215" s="2"/>
-      <c r="J215" s="2" t="s">
-        <v>942</v>
-      </c>
-      <c r="K215" s="2"/>
-      <c r="L215" s="7" t="s">
-        <v>943</v>
-      </c>
-      <c r="M215" s="2"/>
-      <c r="N215" s="2"/>
-      <c r="O215" s="2"/>
-      <c r="P215" s="2"/>
-      <c r="Q215" s="2"/>
-      <c r="R215" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S215" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="T215" s="21">
-        <v>106</v>
-      </c>
-      <c r="U215" s="21">
-        <v>85</v>
-      </c>
-      <c r="V215" s="21">
-        <v>50</v>
-      </c>
-      <c r="W215" s="21">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="216" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A216" s="2"/>
-      <c r="B216" s="2"/>
-      <c r="C216" s="2"/>
-      <c r="D216" s="5"/>
-      <c r="E216" s="2"/>
-      <c r="F216" s="2"/>
-      <c r="G216" s="2"/>
-      <c r="H216" s="2"/>
-      <c r="I216" s="2"/>
-      <c r="J216" s="2"/>
-      <c r="K216" s="2"/>
-      <c r="L216" s="7"/>
-      <c r="M216" s="2"/>
-      <c r="N216" s="2"/>
-      <c r="O216" s="2"/>
-      <c r="P216" s="2"/>
-      <c r="Q216" s="2"/>
-      <c r="R216" s="2"/>
-      <c r="S216" s="2"/>
-      <c r="T216" s="21"/>
-      <c r="U216" s="21"/>
-      <c r="V216" s="21"/>
-      <c r="W216" s="21"/>
-    </row>
-    <row r="217" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A217" s="2"/>
-      <c r="B217" s="2"/>
-      <c r="C217" s="2"/>
-      <c r="D217" s="5"/>
-      <c r="E217" s="2"/>
-      <c r="F217" s="2"/>
-      <c r="G217" s="2"/>
-      <c r="H217" s="2"/>
-      <c r="I217" s="2"/>
-      <c r="J217" s="2"/>
-      <c r="K217" s="2"/>
-      <c r="L217" s="7"/>
-      <c r="M217" s="2"/>
-      <c r="N217" s="2"/>
-      <c r="O217" s="2"/>
-      <c r="P217" s="2"/>
-      <c r="Q217" s="2"/>
-      <c r="R217" s="2"/>
-      <c r="S217" s="2"/>
-      <c r="T217" s="21"/>
-      <c r="U217" s="21"/>
-      <c r="V217" s="21"/>
-      <c r="W217" s="21"/>
-    </row>
-    <row r="218" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A218" s="2"/>
-      <c r="B218" s="2"/>
-      <c r="C218" s="2"/>
-      <c r="D218" s="5"/>
-      <c r="E218" s="2"/>
-      <c r="F218" s="2"/>
-      <c r="G218" s="2"/>
-      <c r="H218" s="2"/>
-      <c r="I218" s="2"/>
-      <c r="J218" s="2"/>
-      <c r="K218" s="2"/>
-      <c r="L218" s="7"/>
-      <c r="M218" s="2"/>
-      <c r="N218" s="2"/>
-      <c r="O218" s="2"/>
-      <c r="P218" s="2"/>
-      <c r="Q218" s="2"/>
-      <c r="R218" s="2"/>
-      <c r="S218" s="2"/>
-      <c r="T218" s="21"/>
-      <c r="U218" s="21"/>
-      <c r="V218" s="21"/>
-      <c r="W218" s="21"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -13966,29 +13624,36 @@
     <hyperlink ref="L161" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
     <hyperlink ref="L162" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
     <hyperlink ref="L163" r:id="rId175" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/12/Baptism_of_Christ_by_Francesco_Mochi_in_San_Giovanni_Battista_dei_Fiorentini.jpg/1280px-Baptism_of_Christ_by_Francesco_Mochi_in_San_Giovanni_Battista_dei_Fiorentini.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="L164" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="L168" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="L169" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="L170" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="L171" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="L172" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="L176" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="L182" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="L186" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="L187" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="L188" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="L189" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="L193" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="L197" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="L201" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="L205" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="L206" r:id="rId192" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/93/Livorno%2C_Monumento_dei_quattro_mori_a_Ferdinando_II_%281626%29_-_Foto_Giovanni_Dall%27Orto%2C_13-4-2006_12.jpg/1280px-Livorno%2C_Monumento_dei_quattro_mori_a_Ferdinando_II_%281626%29_-_Foto_Giovanni_Dall%27Orto%2C_13-4-2006_12.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="L207" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="L208" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="L209" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="L210" r:id="rId196" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/58/Carrara%2C_duomo%2C_interno%2C_altare_dell%27annunziata%2C_crocifisso_in_gesso_attr._a_pietro_tacca_01.jpg/960px-Carrara%2C_duomo%2C_interno%2C_altare_dell%27annunziata%2C_crocifisso_in_gesso_attr._a_pietro_tacca_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="L211" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="L215" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="L186" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="L187" r:id="rId177" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/93/Livorno%2C_Monumento_dei_quattro_mori_a_Ferdinando_II_%281626%29_-_Foto_Giovanni_Dall%27Orto%2C_13-4-2006_12.jpg/1280px-Livorno%2C_Monumento_dei_quattro_mori_a_Ferdinando_II_%281626%29_-_Foto_Giovanni_Dall%27Orto%2C_13-4-2006_12.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="L188" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="L189" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="L190" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="L191" r:id="rId181" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/58/Carrara%2C_duomo%2C_interno%2C_altare_dell%27annunziata%2C_crocifisso_in_gesso_attr._a_pietro_tacca_01.jpg/960px-Carrara%2C_duomo%2C_interno%2C_altare_dell%27annunziata%2C_crocifisso_in_gesso_attr._a_pietro_tacca_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="L192" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="L164" r:id="rId183" xr:uid="{B62212A5-401B-487A-B487-A16DD88E7CDA}"/>
+    <hyperlink ref="L167" r:id="rId184" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Santa_Giustina_%28Padua%29_-_Chapel_of_La_Pieta_-_Pieta_by_Filippo_Parodi.jpg/1280px-Santa_Giustina_%28Padua%29_-_Chapel_of_La_Pieta_-_Pieta_by_Filippo_Parodi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6252DED4-96BF-429F-A381-A245EAE0ED69}"/>
+    <hyperlink ref="I167" r:id="rId185" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3c/Padova_Basilica_di_Santa_Giustina_Innen_Kapelle_der_Piet%C3%A0_1.jpg/960px-Padova_Basilica_di_Santa_Giustina_Innen_Kapelle_der_Piet%C3%A0_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F568C684-A209-4F04-8F8C-17A6AAC5DC37}"/>
+    <hyperlink ref="L166" r:id="rId186" xr:uid="{6C291A7F-648F-443A-8E59-55DB0E1370C4}"/>
+    <hyperlink ref="L165" r:id="rId187" xr:uid="{E248900C-FA54-4FC1-9EB8-C0D95189B6A7}"/>
+    <hyperlink ref="L168" r:id="rId188" xr:uid="{7139457B-BD20-4B96-B180-FEF00BB941BC}"/>
+    <hyperlink ref="L169" r:id="rId189" xr:uid="{9E94E8FE-E5A9-40A3-8558-E71E74125907}"/>
+    <hyperlink ref="L170" r:id="rId190" xr:uid="{5EA024E5-EFD5-4945-BC89-45DE7F114AFA}"/>
+    <hyperlink ref="L171" r:id="rId191" xr:uid="{F29ADA93-FFCA-4FE5-B9DC-696434C0D505}"/>
+    <hyperlink ref="L172" r:id="rId192" xr:uid="{4EE773E4-3861-4F95-817F-046CE1BE3215}"/>
+    <hyperlink ref="L175" r:id="rId193" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a9/Hercule_au_repos_-_Pierre_Puget_-_Mus%C3%A9e_du_Louvre_Sculptures_N_15345.jpg/1280px-Hercule_au_repos_-_Pierre_Puget_-_Mus%C3%A9e_du_Louvre_Sculptures_N_15345.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E462B9F0-8815-42D8-85D1-4D16E1151E43}"/>
+    <hyperlink ref="L173" r:id="rId194" xr:uid="{6EEEF935-FB38-4228-8AFC-EC2DE8AA6CE5}"/>
+    <hyperlink ref="L174" r:id="rId195" xr:uid="{E43D01AA-B03A-4F60-B893-BAD30B08C99D}"/>
+    <hyperlink ref="L176" r:id="rId196" xr:uid="{50D248BC-1ABE-4869-86AE-3903AED1BF33}"/>
+    <hyperlink ref="L181" r:id="rId197" xr:uid="{97EC60B5-E7B4-494F-8FC1-A71E07FD1866}"/>
+    <hyperlink ref="L177" r:id="rId198" xr:uid="{C81BE4E0-B911-411D-A62F-D3461FE0199D}"/>
+    <hyperlink ref="L178" r:id="rId199" xr:uid="{8C6E1BC7-D507-43AD-9539-E497DF951F49}"/>
+    <hyperlink ref="L179" r:id="rId200" xr:uid="{49636437-1A28-4A23-812B-E21A73D95FC6}"/>
+    <hyperlink ref="L180" r:id="rId201" xr:uid="{29C894BA-2DBA-435D-8DA2-15C79207E0D4}"/>
+    <hyperlink ref="L182" r:id="rId202" xr:uid="{A9F8AACF-DD60-4E09-9D03-EB99FFC90C87}"/>
+    <hyperlink ref="L184" r:id="rId203" xr:uid="{A06D195A-0D35-436B-B5ED-E84040B80563}"/>
+    <hyperlink ref="L183" r:id="rId204" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0b/Antonio_raggi%2C_battesimo_di_cristo%2C_1669%2C_in_altare_del_borromini%2C_1640%2C_02.jpg/960px-Antonio_raggi%2C_battesimo_di_cristo%2C_1669%2C_in_altare_del_borromini%2C_1640%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B226CB10-B7E3-45BC-AD92-696AA2BACC78}"/>
+    <hyperlink ref="L185" r:id="rId205" xr:uid="{646C88F8-6572-433F-8D7C-7F229CB8B67A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-17e.xlsx
+++ b/quizzes/sculpture-17e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2DA695-F762-4E67-82BF-D3A5E52DAC78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF38271-51DC-439A-89EA-7B66573E132E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1978" uniqueCount="964">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1972" uniqueCount="959">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -650,12 +650,6 @@
     <t>1671-1674</t>
   </si>
   <si>
-    <t>San Francesco a Ripa</t>
-  </si>
-  <si>
-    <t>Chapelle Altieri</t>
-  </si>
-  <si>
     <t>La Bienheureuse Ludovica Albertoni</t>
   </si>
   <si>
@@ -2813,9 +2807,6 @@
     <t>1650-1655</t>
   </si>
   <si>
-    <t>Salle des Bourgeois</t>
-  </si>
-  <si>
     <t>Atlas supportant le globe céleste</t>
   </si>
   <si>
@@ -2828,9 +2819,6 @@
     <t>Rijksmuseum</t>
   </si>
   <si>
-    <t>Galerie d'honneur</t>
-  </si>
-  <si>
     <t>Buste de Johan de Witt</t>
   </si>
   <si>
@@ -2861,12 +2849,6 @@
     <t>Anvers</t>
   </si>
   <si>
-    <t>Église Saint-Paul</t>
-  </si>
-  <si>
-    <t>Nef principale</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/f/f2/Artus_Quellinus_I_-_Saint_Peter_%28cropped%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
@@ -2924,7 +2906,10 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1a/Sant-agnese-erroma-0608.jpg/960px-Sant-agnese-erroma-0608.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t xml:space="preserve">Tribunal </t>
+    <t>Église Saint-André</t>
+  </si>
+  <si>
+    <t>Basilique San Francesco a Ripa</t>
   </si>
 </sst>
 </file>
@@ -2951,6 +2936,7 @@
       <sz val="11"/>
       <color rgb="FF0563C1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -5619,19 +5605,17 @@
         <v>26</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>205</v>
+        <v>958</v>
       </c>
       <c r="G42" s="2"/>
-      <c r="H42" s="2" t="s">
-        <v>206</v>
-      </c>
+      <c r="H42" s="2"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="K42" s="2"/>
       <c r="L42" s="7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
@@ -5666,23 +5650,23 @@
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K43" s="2"/>
       <c r="L43" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
@@ -5710,30 +5694,30 @@
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>216</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K44" s="2"/>
       <c r="L44" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
@@ -5761,10 +5745,10 @@
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="5" t="s">
@@ -5774,17 +5758,17 @@
         <v>26</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K45" s="2"/>
       <c r="L45" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
@@ -5795,7 +5779,7 @@
         <v>53</v>
       </c>
       <c r="S45" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="T45" s="21">
         <v>350</v>
@@ -5812,32 +5796,32 @@
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="L46" s="7" t="s">
         <v>227</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="L46" s="7" t="s">
-        <v>229</v>
       </c>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
@@ -5865,32 +5849,32 @@
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F47" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>232</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="L47" s="7" t="s">
         <v>233</v>
-      </c>
-      <c r="K47" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="L47" s="7" t="s">
-        <v>235</v>
       </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
@@ -5918,36 +5902,36 @@
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I48" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="J48" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="I48" s="7" t="s">
+      <c r="K48" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="J48" s="2" t="s">
+      <c r="L48" s="7" t="s">
         <v>240</v>
-      </c>
-      <c r="K48" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="L48" s="7" t="s">
-        <v>242</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -5975,10 +5959,10 @@
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="5" t="s">
@@ -5988,19 +5972,19 @@
         <v>26</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
       <c r="J49" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="L49" s="7" t="s">
         <v>244</v>
-      </c>
-      <c r="K49" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="L49" s="7" t="s">
-        <v>246</v>
       </c>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
@@ -6011,7 +5995,7 @@
         <v>30</v>
       </c>
       <c r="S49" s="6" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="T49" s="21">
         <v>80</v>
@@ -6028,32 +6012,32 @@
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="L50" s="7" t="s">
         <v>250</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="L50" s="7" t="s">
-        <v>252</v>
       </c>
       <c r="M50" s="2"/>
       <c r="N50" s="2"/>
@@ -6081,34 +6065,34 @@
     </row>
     <row r="51" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="G51" s="2"/>
       <c r="H51" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I51" s="2"/>
       <c r="J51" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="L51" s="7" t="s">
         <v>259</v>
-      </c>
-      <c r="K51" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="L51" s="7" t="s">
-        <v>261</v>
       </c>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
@@ -6119,7 +6103,7 @@
         <v>30</v>
       </c>
       <c r="S51" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T51" s="21">
         <v>55</v>
@@ -6131,41 +6115,41 @@
         <v>20</v>
       </c>
       <c r="W51" s="21" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="52" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="F52" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>266</v>
       </c>
       <c r="G52" s="2"/>
       <c r="H52" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I52" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="J52" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="I52" s="7" t="s">
+      <c r="K52" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="J52" s="2" t="s">
+      <c r="L52" s="7" t="s">
         <v>269</v>
-      </c>
-      <c r="K52" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="L52" s="7" t="s">
-        <v>271</v>
       </c>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
@@ -6176,10 +6160,10 @@
         <v>30</v>
       </c>
       <c r="S52" s="6" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="T52" s="21" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="U52" s="21">
         <v>80</v>
@@ -6188,37 +6172,37 @@
         <v>60</v>
       </c>
       <c r="W52" s="21" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="53" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F53" s="2" t="s">
         <v>274</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>276</v>
       </c>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="L53" s="7" t="s">
         <v>277</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="L53" s="7" t="s">
-        <v>279</v>
       </c>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
@@ -6229,10 +6213,10 @@
         <v>30</v>
       </c>
       <c r="S53" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T53" s="21" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="U53" s="21">
         <v>79</v>
@@ -6241,37 +6225,37 @@
         <v>89</v>
       </c>
       <c r="W53" s="21" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="54" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L54" s="7" t="s">
         <v>283</v>
-      </c>
-      <c r="K54" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="L54" s="7" t="s">
-        <v>285</v>
       </c>
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
@@ -6282,10 +6266,10 @@
         <v>30</v>
       </c>
       <c r="S54" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T54" s="21" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="U54" s="21">
         <v>72</v>
@@ -6294,35 +6278,35 @@
         <v>98</v>
       </c>
       <c r="W54" s="21" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="55" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="K55" s="2"/>
       <c r="L55" s="7" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="M55" s="2"/>
       <c r="N55" s="2"/>
@@ -6333,7 +6317,7 @@
         <v>30</v>
       </c>
       <c r="S55" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T55" s="21">
         <v>30</v>
@@ -6345,35 +6329,35 @@
         <v>21</v>
       </c>
       <c r="W55" s="21" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="56" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="K56" s="2"/>
       <c r="L56" s="15" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
@@ -6384,7 +6368,7 @@
         <v>30</v>
       </c>
       <c r="S56" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T56" s="21">
         <v>203</v>
@@ -6401,34 +6385,34 @@
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B57" t="s">
+        <v>252</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="E57" t="s">
         <v>254</v>
       </c>
-      <c r="D57" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="E57" t="s">
-        <v>256</v>
-      </c>
       <c r="F57" t="s">
+        <v>291</v>
+      </c>
+      <c r="J57" t="s">
+        <v>292</v>
+      </c>
+      <c r="K57" t="s">
         <v>293</v>
       </c>
-      <c r="J57" t="s">
+      <c r="L57" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="K57" t="s">
-        <v>295</v>
-      </c>
-      <c r="L57" s="1" t="s">
-        <v>296</v>
       </c>
       <c r="R57" s="2" t="s">
         <v>30</v>
       </c>
       <c r="S57" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T57" s="24">
         <v>197</v>
@@ -6440,35 +6424,35 @@
         <v>79</v>
       </c>
       <c r="W57" s="24" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="58" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C58" s="8"/>
       <c r="D58" s="13" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G58" s="8"/>
       <c r="H58" s="8"/>
       <c r="I58" s="8"/>
       <c r="J58" s="8" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="K58" s="8"/>
       <c r="L58" s="9" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="M58" s="8"/>
       <c r="N58" s="8"/>
@@ -6479,7 +6463,7 @@
         <v>30</v>
       </c>
       <c r="S58" s="19" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T58" s="22">
         <v>47</v>
@@ -6491,25 +6475,25 @@
         <v>28</v>
       </c>
       <c r="W58" s="22" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="59" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
@@ -6519,7 +6503,7 @@
       </c>
       <c r="K59" s="2"/>
       <c r="L59" s="7" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -6547,32 +6531,32 @@
     </row>
     <row r="60" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="L60" s="7" t="s">
         <v>307</v>
-      </c>
-      <c r="K60" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="L60" s="7" t="s">
-        <v>309</v>
       </c>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
@@ -6586,7 +6570,7 @@
         <v>64</v>
       </c>
       <c r="T60" s="21" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="U60" s="21">
         <v>120</v>
@@ -6600,32 +6584,32 @@
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
       <c r="J61" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="L61" s="7" t="s">
         <v>312</v>
-      </c>
-      <c r="K61" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="L61" s="7" t="s">
-        <v>314</v>
       </c>
       <c r="M61" s="2"/>
       <c r="N61" s="2"/>
@@ -6653,32 +6637,32 @@
     </row>
     <row r="62" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
       <c r="J62" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="L62" s="7" t="s">
         <v>317</v>
-      </c>
-      <c r="K62" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="L62" s="7" t="s">
-        <v>319</v>
       </c>
       <c r="M62" s="2"/>
       <c r="N62" s="2"/>
@@ -6689,7 +6673,7 @@
         <v>30</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="T62" s="21">
         <v>183</v>
@@ -6706,14 +6690,14 @@
     </row>
     <row r="63" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="14" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>73</v>
@@ -6725,11 +6709,11 @@
       <c r="H63" s="10"/>
       <c r="I63" s="10"/>
       <c r="J63" s="10" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="K63" s="10"/>
       <c r="L63" s="11" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M63" s="10"/>
       <c r="N63" s="10"/>
@@ -6757,13 +6741,13 @@
     </row>
     <row r="64" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B64" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E64" t="s">
         <v>73</v>
@@ -6772,13 +6756,13 @@
         <v>74</v>
       </c>
       <c r="J64" t="s">
+        <v>324</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="R64" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="L64" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="R64" s="2" t="s">
-        <v>328</v>
       </c>
       <c r="S64" s="2" t="s">
         <v>31</v>
@@ -6798,10 +6782,10 @@
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="5">
@@ -6817,11 +6801,11 @@
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
       <c r="J65" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="K65" s="2"/>
       <c r="L65" s="7" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
@@ -6849,14 +6833,14 @@
     </row>
     <row r="66" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="5" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="2" t="s">
@@ -6866,11 +6850,11 @@
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
       <c r="J66" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="K66" s="2"/>
       <c r="L66" s="7" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
@@ -6898,14 +6882,14 @@
     </row>
     <row r="67" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="5" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="2" t="s">
@@ -6915,11 +6899,11 @@
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
       <c r="J67" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="K67" s="2"/>
       <c r="L67" s="7" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
@@ -6947,14 +6931,14 @@
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="5" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="2" t="s">
@@ -6962,15 +6946,15 @@
       </c>
       <c r="G68" s="2"/>
       <c r="H68" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="I68" s="2"/>
       <c r="J68" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="K68" s="2"/>
       <c r="L68" s="7" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
@@ -6978,10 +6962,10 @@
       <c r="P68" s="2"/>
       <c r="Q68" s="2"/>
       <c r="R68" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="S68" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="T68" s="21">
         <v>390</v>
@@ -6998,14 +6982,14 @@
     </row>
     <row r="69" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="5" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>73</v>
@@ -7015,7 +6999,7 @@
       </c>
       <c r="G69" s="2"/>
       <c r="H69" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="I69" s="2"/>
       <c r="J69" s="2" t="s">
@@ -7023,7 +7007,7 @@
       </c>
       <c r="K69" s="2"/>
       <c r="L69" s="7" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
@@ -7051,14 +7035,14 @@
     </row>
     <row r="70" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>73</v>
@@ -7070,11 +7054,11 @@
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
       <c r="J70" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="K70" s="2"/>
       <c r="L70" s="7" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
@@ -7102,30 +7086,30 @@
     </row>
     <row r="71" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>73</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
       <c r="J71" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="K71" s="2"/>
       <c r="L71" s="7" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
@@ -7153,14 +7137,14 @@
     </row>
     <row r="72" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" s="5" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>73</v>
@@ -7170,15 +7154,15 @@
       </c>
       <c r="G72" s="2"/>
       <c r="H72" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="I72" s="2"/>
       <c r="J72" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="K72" s="2"/>
       <c r="L72" s="7" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
@@ -7206,14 +7190,14 @@
     </row>
     <row r="73" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" s="5" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>73</v>
@@ -7223,15 +7207,15 @@
       </c>
       <c r="G73" s="2"/>
       <c r="H73" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="I73" s="2"/>
       <c r="J73" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="K73" s="2"/>
       <c r="L73" s="7" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="M73" s="2"/>
       <c r="N73" s="2"/>
@@ -7259,28 +7243,28 @@
     </row>
     <row r="74" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="5" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
       <c r="J74" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="K74" s="2"/>
       <c r="L74" s="7" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
@@ -7294,44 +7278,44 @@
         <v>64</v>
       </c>
       <c r="T74" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="U74" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="V74" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="U74" s="5" t="s">
+      <c r="W74" s="5" t="s">
         <v>368</v>
-      </c>
-      <c r="V74" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="W74" s="5" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="75" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F75" s="2" t="s">
         <v>371</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>373</v>
       </c>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
       <c r="J75" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="K75" s="2"/>
       <c r="L75" s="7" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
@@ -7345,7 +7329,7 @@
         <v>31</v>
       </c>
       <c r="T75" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="U75" s="5">
         <v>566</v>
@@ -7354,39 +7338,39 @@
         <v>426</v>
       </c>
       <c r="W75" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F76" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="F76" s="2" t="s">
+      <c r="G76" s="7" t="s">
         <v>373</v>
-      </c>
-      <c r="G76" s="7" t="s">
-        <v>375</v>
       </c>
       <c r="H76" s="2"/>
       <c r="I76" s="2"/>
       <c r="J76" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="L76" s="7" t="s">
         <v>377</v>
-      </c>
-      <c r="K76" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="L76" s="7" t="s">
-        <v>379</v>
       </c>
       <c r="M76" s="2"/>
       <c r="N76" s="2"/>
@@ -7409,39 +7393,39 @@
         <v>55</v>
       </c>
       <c r="W76" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="77" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F77" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="E77" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="F77" s="2" t="s">
+      <c r="G77" s="7" t="s">
         <v>373</v>
-      </c>
-      <c r="G77" s="7" t="s">
-        <v>375</v>
       </c>
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
       <c r="J77" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="L77" s="7" t="s">
         <v>380</v>
-      </c>
-      <c r="K77" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="L77" s="7" t="s">
-        <v>382</v>
       </c>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
@@ -7464,37 +7448,37 @@
         <v>140</v>
       </c>
       <c r="W77" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="78" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" s="5" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
       <c r="J78" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="L78" s="7" t="s">
         <v>385</v>
-      </c>
-      <c r="K78" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="L78" s="7" t="s">
-        <v>387</v>
       </c>
       <c r="M78" s="2"/>
       <c r="N78" s="2"/>
@@ -7505,7 +7489,7 @@
         <v>30</v>
       </c>
       <c r="S78" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="T78" s="5">
         <v>175</v>
@@ -7517,35 +7501,35 @@
         <v>50</v>
       </c>
       <c r="W78" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="79" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="F79" s="2" t="s">
         <v>389</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>391</v>
       </c>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
       <c r="J79" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="K79" s="2"/>
       <c r="L79" s="7" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="M79" s="2"/>
       <c r="N79" s="2"/>
@@ -7568,35 +7552,35 @@
         <v>12</v>
       </c>
       <c r="W79" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" s="5" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
       <c r="J80" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="K80" s="2"/>
       <c r="L80" s="7" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
@@ -7607,47 +7591,47 @@
         <v>30</v>
       </c>
       <c r="S80" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T80" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="U80" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="V80" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="U80" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="V80" s="5" t="s">
-        <v>401</v>
-      </c>
       <c r="W80" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="81" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" s="5" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
       <c r="J81" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="K81" s="2"/>
       <c r="L81" s="7" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
@@ -7658,47 +7642,47 @@
         <v>133</v>
       </c>
       <c r="S81" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="T81" s="5">
         <v>124</v>
       </c>
       <c r="U81" s="5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="V81" s="5"/>
       <c r="W81" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="82" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" s="5" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
       <c r="J82" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="L82" s="7" t="s">
         <v>409</v>
-      </c>
-      <c r="K82" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="L82" s="7" t="s">
-        <v>411</v>
       </c>
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
@@ -7709,49 +7693,49 @@
         <v>30</v>
       </c>
       <c r="S82" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T82" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="U82" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="V82" s="5" t="s">
         <v>412</v>
       </c>
-      <c r="U82" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="V82" s="5" t="s">
-        <v>414</v>
-      </c>
       <c r="W82" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="83" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="F83" s="2" t="s">
         <v>415</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>417</v>
       </c>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
       <c r="J83" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="L83" s="7" t="s">
         <v>418</v>
-      </c>
-      <c r="K83" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="L83" s="7" t="s">
-        <v>420</v>
       </c>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
@@ -7762,7 +7746,7 @@
         <v>30</v>
       </c>
       <c r="S83" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T83" s="5">
         <v>167</v>
@@ -7774,37 +7758,37 @@
         <v>57</v>
       </c>
       <c r="W83" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" s="5">
         <v>1670</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
       <c r="J84" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="L84" s="7" t="s">
         <v>423</v>
-      </c>
-      <c r="K84" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="L84" s="7" t="s">
-        <v>425</v>
       </c>
       <c r="M84" s="2"/>
       <c r="N84" s="2"/>
@@ -7815,7 +7799,7 @@
         <v>30</v>
       </c>
       <c r="S84" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T84" s="5">
         <v>58</v>
@@ -7827,37 +7811,37 @@
         <v>18</v>
       </c>
       <c r="W84" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="85" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" s="5">
         <v>1675</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
       <c r="J85" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="L85" s="7" t="s">
         <v>427</v>
-      </c>
-      <c r="K85" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="L85" s="7" t="s">
-        <v>429</v>
       </c>
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
@@ -7868,7 +7852,7 @@
         <v>30</v>
       </c>
       <c r="S85" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T85" s="5">
         <v>60</v>
@@ -7880,19 +7864,19 @@
         <v>25</v>
       </c>
       <c r="W85" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="86" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" s="5" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>113</v>
@@ -7904,13 +7888,13 @@
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
       <c r="J86" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="L86" s="7" t="s">
         <v>431</v>
-      </c>
-      <c r="K86" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="L86" s="7" t="s">
-        <v>433</v>
       </c>
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
@@ -7921,7 +7905,7 @@
         <v>43</v>
       </c>
       <c r="S86" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T86" s="5">
         <v>24</v>
@@ -7933,37 +7917,37 @@
         <v>18</v>
       </c>
       <c r="W86" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="87" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C87" s="8"/>
       <c r="D87" s="13">
         <v>1663</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="G87" s="8"/>
       <c r="H87" s="8"/>
       <c r="I87" s="8"/>
       <c r="J87" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="K87" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="L87" s="9" t="s">
         <v>436</v>
-      </c>
-      <c r="K87" s="8" t="s">
-        <v>437</v>
-      </c>
-      <c r="L87" s="9" t="s">
-        <v>438</v>
       </c>
       <c r="M87" s="8"/>
       <c r="N87" s="8"/>
@@ -7974,10 +7958,10 @@
         <v>30</v>
       </c>
       <c r="S87" s="8" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T87" s="13" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="U87" s="13">
         <v>40</v>
@@ -7986,35 +7970,35 @@
         <v>36</v>
       </c>
       <c r="W87" s="13" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="88" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
       <c r="I88" s="2"/>
       <c r="J88" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="K88" s="2"/>
       <c r="L88" s="7" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="M88" s="2"/>
       <c r="N88" s="2"/>
@@ -8025,16 +8009,16 @@
         <v>30</v>
       </c>
       <c r="S88" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T88" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="U88" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="V88" s="5" t="s">
         <v>445</v>
-      </c>
-      <c r="U88" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="V88" s="5" t="s">
-        <v>447</v>
       </c>
       <c r="W88" s="5" t="s">
         <v>107</v>
@@ -8042,32 +8026,32 @@
     </row>
     <row r="89" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
       <c r="I89" s="2"/>
       <c r="J89" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="L89" s="7" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
@@ -8078,7 +8062,7 @@
         <v>30</v>
       </c>
       <c r="S89" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T89" s="5">
         <v>60</v>
@@ -8095,10 +8079,10 @@
     </row>
     <row r="90" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" s="2">
@@ -8114,13 +8098,13 @@
       <c r="H90" s="2"/>
       <c r="I90" s="2"/>
       <c r="J90" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="K90" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="L90" s="7" t="s">
         <v>451</v>
-      </c>
-      <c r="K90" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="L90" s="7" t="s">
-        <v>453</v>
       </c>
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
@@ -8131,16 +8115,16 @@
         <v>30</v>
       </c>
       <c r="S90" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="T90" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="U90" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="T90" s="5" t="s">
+      <c r="V90" s="5" t="s">
         <v>455</v>
-      </c>
-      <c r="U90" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="V90" s="5" t="s">
-        <v>457</v>
       </c>
       <c r="W90" s="5" t="s">
         <v>107</v>
@@ -8148,32 +8132,32 @@
     </row>
     <row r="91" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
       <c r="I91" s="2"/>
       <c r="J91" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="K91" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="L91" s="7" t="s">
         <v>460</v>
-      </c>
-      <c r="K91" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="L91" s="7" t="s">
-        <v>462</v>
       </c>
       <c r="M91" s="2"/>
       <c r="N91" s="2"/>
@@ -8184,7 +8168,7 @@
         <v>30</v>
       </c>
       <c r="S91" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T91" s="5">
         <v>58</v>
@@ -8201,14 +8185,14 @@
     </row>
     <row r="92" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>73</v>
@@ -8220,11 +8204,11 @@
       <c r="H92" s="2"/>
       <c r="I92" s="2"/>
       <c r="J92" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="K92" s="2"/>
       <c r="L92" s="7" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="M92" s="2"/>
       <c r="N92" s="2"/>
@@ -8238,13 +8222,13 @@
         <v>31</v>
       </c>
       <c r="T92" s="5" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="U92" s="5" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="V92" s="5" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="W92" s="5" t="s">
         <v>107</v>
@@ -8252,14 +8236,14 @@
     </row>
     <row r="93" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>73</v>
@@ -8271,11 +8255,11 @@
       <c r="H93" s="2"/>
       <c r="I93" s="2"/>
       <c r="J93" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K93" s="2"/>
       <c r="L93" s="7" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
@@ -8289,10 +8273,10 @@
         <v>64</v>
       </c>
       <c r="T93" s="5" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="U93" s="5" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="V93" s="5"/>
       <c r="W93" s="5" t="s">
@@ -8301,30 +8285,30 @@
     </row>
     <row r="94" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="F94" s="2" t="s">
         <v>473</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>475</v>
       </c>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
       <c r="I94" s="2"/>
       <c r="J94" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K94" s="2"/>
       <c r="L94" s="7" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
@@ -8352,14 +8336,14 @@
     </row>
     <row r="95" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>73</v>
@@ -8371,11 +8355,11 @@
       <c r="H95" s="2"/>
       <c r="I95" s="2"/>
       <c r="J95" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="K95" s="2"/>
       <c r="L95" s="7" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="M95" s="2"/>
       <c r="N95" s="2"/>
@@ -8383,19 +8367,19 @@
       <c r="P95" s="2"/>
       <c r="Q95" s="2"/>
       <c r="R95" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="S95" s="2" t="s">
         <v>31</v>
       </c>
       <c r="T95" s="5" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="U95" s="5" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="V95" s="5" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="W95" s="5" t="s">
         <v>107</v>
@@ -8403,32 +8387,32 @@
     </row>
     <row r="96" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="F96" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>486</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
       <c r="J96" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="K96" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="L96" s="3" t="s">
         <v>487</v>
-      </c>
-      <c r="K96" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="L96" s="3" t="s">
-        <v>489</v>
       </c>
       <c r="M96" s="2"/>
       <c r="N96" s="4"/>
@@ -8442,7 +8426,7 @@
         <v>64</v>
       </c>
       <c r="T96" s="21" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="U96" s="21">
         <v>70</v>
@@ -8459,27 +8443,27 @@
         <v>70</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
       <c r="J97" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="K97" s="2"/>
       <c r="L97" s="7" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="M97" s="2"/>
       <c r="N97" s="2"/>
@@ -8510,27 +8494,27 @@
         <v>70</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
       <c r="I98" s="2"/>
       <c r="J98" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="K98" s="2"/>
       <c r="L98" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="M98" s="2"/>
       <c r="N98" s="2"/>
@@ -8559,11 +8543,11 @@
         <v>70</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>26</v>
@@ -8575,11 +8559,11 @@
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
       <c r="J99" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="K99" s="2"/>
       <c r="L99" s="7" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="M99" s="2"/>
       <c r="N99" s="2"/>
@@ -8610,27 +8594,27 @@
         <v>70</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
       <c r="I100" s="2"/>
       <c r="J100" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="K100" s="2"/>
       <c r="L100" s="7" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="M100" s="2"/>
       <c r="N100" s="2"/>
@@ -8659,27 +8643,27 @@
         <v>70</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
       <c r="J101" s="2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="K101" s="2"/>
       <c r="L101" s="7" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="M101" s="2"/>
       <c r="N101" s="2"/>
@@ -8687,7 +8671,7 @@
       <c r="P101" s="2"/>
       <c r="Q101" s="2"/>
       <c r="R101" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="S101" s="2" t="s">
         <v>31</v>
@@ -8710,31 +8694,31 @@
         <v>70</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G102" s="2"/>
       <c r="H102" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="I102" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="J102" s="2" t="s">
         <v>512</v>
-      </c>
-      <c r="I102" s="7" t="s">
-        <v>513</v>
-      </c>
-      <c r="J102" s="2" t="s">
-        <v>514</v>
       </c>
       <c r="K102" s="2"/>
       <c r="L102" s="7" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="M102" s="2"/>
       <c r="N102" s="2"/>
@@ -8762,30 +8746,30 @@
     </row>
     <row r="103" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
       <c r="I103" s="2"/>
       <c r="J103" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="K103" s="2"/>
       <c r="L103" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="M103" s="2"/>
       <c r="N103" s="2"/>
@@ -8809,36 +8793,36 @@
     </row>
     <row r="104" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="G104" s="2"/>
       <c r="H104" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="I104" s="26" t="s">
+        <v>522</v>
+      </c>
+      <c r="J104" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="I104" s="26" t="s">
+      <c r="K104" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="J104" s="2" t="s">
+      <c r="L104" s="7" t="s">
         <v>525</v>
-      </c>
-      <c r="K104" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="L104" s="7" t="s">
-        <v>527</v>
       </c>
       <c r="M104" s="2"/>
       <c r="N104" s="2"/>
@@ -8866,30 +8850,30 @@
     </row>
     <row r="105" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
       <c r="I105" s="2"/>
       <c r="J105" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="K105" s="2"/>
       <c r="L105" s="26" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="M105" s="2"/>
       <c r="N105" s="2"/>
@@ -8906,10 +8890,10 @@
         <v>2400</v>
       </c>
       <c r="U105" s="5" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="V105" s="5" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="W105" s="5">
         <v>3</v>
@@ -8917,36 +8901,36 @@
     </row>
     <row r="106" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="G106" s="2"/>
       <c r="H106" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="I106" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="J106" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="I106" s="7" t="s">
+      <c r="K106" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="J106" s="2" t="s">
+      <c r="L106" s="7" t="s">
         <v>537</v>
-      </c>
-      <c r="K106" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="L106" s="7" t="s">
-        <v>539</v>
       </c>
       <c r="M106" s="2"/>
       <c r="N106" s="2"/>
@@ -8974,30 +8958,30 @@
     </row>
     <row r="107" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
       <c r="I107" s="2"/>
       <c r="J107" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="K107" s="2"/>
       <c r="L107" s="7" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
@@ -9008,7 +8992,7 @@
         <v>30</v>
       </c>
       <c r="S107" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T107" s="5">
         <v>175</v>
@@ -9025,32 +9009,32 @@
     </row>
     <row r="108" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
       <c r="I108" s="2"/>
       <c r="J108" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="K108" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="L108" s="7" t="s">
         <v>546</v>
-      </c>
-      <c r="K108" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="L108" s="7" t="s">
-        <v>548</v>
       </c>
       <c r="M108" s="2"/>
       <c r="N108" s="2"/>
@@ -9061,7 +9045,7 @@
         <v>30</v>
       </c>
       <c r="S108" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T108" s="5">
         <v>51</v>
@@ -9078,30 +9062,30 @@
     </row>
     <row r="109" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="F109" s="2" t="s">
         <v>549</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
       <c r="I109" s="2"/>
       <c r="J109" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="K109" s="2"/>
       <c r="L109" s="7" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="M109" s="2"/>
       <c r="N109" s="2"/>
@@ -9112,7 +9096,7 @@
         <v>30</v>
       </c>
       <c r="S109" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T109" s="5">
         <v>40</v>
@@ -9129,32 +9113,32 @@
     </row>
     <row r="110" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
       <c r="I110" s="2"/>
       <c r="J110" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="K110" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="L110" s="7" t="s">
         <v>556</v>
-      </c>
-      <c r="K110" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="L110" s="7" t="s">
-        <v>558</v>
       </c>
       <c r="M110" s="2"/>
       <c r="N110" s="2"/>
@@ -9165,7 +9149,7 @@
         <v>30</v>
       </c>
       <c r="S110" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T110" s="5">
         <v>186</v>
@@ -9182,32 +9166,32 @@
     </row>
     <row r="111" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
       <c r="I111" s="2"/>
       <c r="J111" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="L111" s="7" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="M111" s="2"/>
       <c r="N111" s="2"/>
@@ -9218,7 +9202,7 @@
         <v>53</v>
       </c>
       <c r="S111" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T111" s="5">
         <v>299</v>
@@ -9235,32 +9219,32 @@
     </row>
     <row r="112" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
       <c r="I112" s="2"/>
       <c r="J112" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="K112" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="L112" s="7" t="s">
         <v>563</v>
-      </c>
-      <c r="K112" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="L112" s="7" t="s">
-        <v>565</v>
       </c>
       <c r="M112" s="2"/>
       <c r="N112" s="2"/>
@@ -9268,10 +9252,10 @@
       <c r="P112" s="2"/>
       <c r="Q112" s="2"/>
       <c r="R112" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="S112" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T112" s="5">
         <v>600</v>
@@ -9284,32 +9268,32 @@
     </row>
     <row r="113" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
       <c r="I113" s="2"/>
       <c r="J113" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="K113" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="L113" s="7" t="s">
         <v>568</v>
-      </c>
-      <c r="K113" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="L113" s="7" t="s">
-        <v>570</v>
       </c>
       <c r="M113" s="2"/>
       <c r="N113" s="2"/>
@@ -9317,10 +9301,10 @@
       <c r="P113" s="2"/>
       <c r="Q113" s="2"/>
       <c r="R113" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="S113" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T113" s="5">
         <v>378</v>
@@ -9337,32 +9321,32 @@
     </row>
     <row r="114" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
       <c r="I114" s="2"/>
       <c r="J114" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="K114" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="L114" s="7" t="s">
         <v>573</v>
-      </c>
-      <c r="K114" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="L114" s="7" t="s">
-        <v>575</v>
       </c>
       <c r="M114" s="2"/>
       <c r="N114" s="2"/>
@@ -9373,7 +9357,7 @@
         <v>30</v>
       </c>
       <c r="S114" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T114" s="5">
         <v>187</v>
@@ -9390,32 +9374,32 @@
     </row>
     <row r="115" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
       <c r="I115" s="2"/>
       <c r="J115" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="K115" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="L115" s="7" t="s">
         <v>580</v>
-      </c>
-      <c r="K115" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="L115" s="7" t="s">
-        <v>582</v>
       </c>
       <c r="M115" s="2"/>
       <c r="N115" s="2"/>
@@ -9443,32 +9427,32 @@
     </row>
     <row r="116" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
       <c r="I116" s="2"/>
       <c r="J116" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="K116" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="L116" s="7" t="s">
         <v>584</v>
-      </c>
-      <c r="K116" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="L116" s="7" t="s">
-        <v>586</v>
       </c>
       <c r="M116" s="2"/>
       <c r="N116" s="2"/>
@@ -9496,10 +9480,10 @@
     </row>
     <row r="117" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" s="2" t="s">
@@ -9509,19 +9493,19 @@
         <v>26</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
       <c r="I117" s="2"/>
       <c r="J117" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="K117" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="L117" s="7" t="s">
         <v>588</v>
-      </c>
-      <c r="K117" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="L117" s="7" t="s">
-        <v>590</v>
       </c>
       <c r="M117" s="2"/>
       <c r="N117" s="2"/>
@@ -9549,10 +9533,10 @@
     </row>
     <row r="118" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" s="2" t="s">
@@ -9562,19 +9546,19 @@
         <v>26</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
       <c r="I118" s="2"/>
       <c r="J118" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="K118" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="L118" s="7" t="s">
         <v>592</v>
-      </c>
-      <c r="K118" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="L118" s="7" t="s">
-        <v>594</v>
       </c>
       <c r="M118" s="2"/>
       <c r="N118" s="2"/>
@@ -9602,34 +9586,34 @@
     </row>
     <row r="119" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="F119" s="2" t="s">
         <v>595</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="F119" s="2" t="s">
-        <v>597</v>
       </c>
       <c r="G119" s="2"/>
       <c r="H119" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="I119" s="2"/>
       <c r="J119" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="K119" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="L119" s="7" t="s">
         <v>599</v>
-      </c>
-      <c r="K119" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="L119" s="7" t="s">
-        <v>601</v>
       </c>
       <c r="M119" s="2"/>
       <c r="N119" s="2"/>
@@ -9657,34 +9641,34 @@
     </row>
     <row r="120" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="F120" s="2" t="s">
         <v>602</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="F120" s="2" t="s">
-        <v>604</v>
       </c>
       <c r="G120" s="2"/>
       <c r="H120" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="I120" s="2"/>
       <c r="J120" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="K120" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="L120" s="7" t="s">
         <v>606</v>
-      </c>
-      <c r="K120" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="L120" s="7" t="s">
-        <v>608</v>
       </c>
       <c r="M120" s="2"/>
       <c r="N120" s="2"/>
@@ -9712,14 +9696,14 @@
     </row>
     <row r="121" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>73</v>
@@ -9731,11 +9715,11 @@
       <c r="H121" s="2"/>
       <c r="I121" s="2"/>
       <c r="J121" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K121" s="2"/>
       <c r="L121" s="7" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="M121" s="2"/>
       <c r="N121" s="2"/>
@@ -9758,35 +9742,35 @@
         <v>30</v>
       </c>
       <c r="W121" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="122" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>141</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
       <c r="I122" s="2"/>
       <c r="J122" s="2" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="K122" s="2"/>
       <c r="L122" s="7" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="M122" s="2"/>
       <c r="N122" s="2"/>
@@ -9800,7 +9784,7 @@
         <v>31</v>
       </c>
       <c r="T122" s="5" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="U122" s="5">
         <v>65</v>
@@ -9809,19 +9793,19 @@
         <v>40</v>
       </c>
       <c r="W122" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="123" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>113</v>
@@ -9833,13 +9817,13 @@
       <c r="H123" s="2"/>
       <c r="I123" s="2"/>
       <c r="J123" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="K123" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="L123" s="7" t="s">
         <v>619</v>
-      </c>
-      <c r="K123" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="L123" s="7" t="s">
-        <v>621</v>
       </c>
       <c r="M123" s="2"/>
       <c r="N123" s="2"/>
@@ -9853,7 +9837,7 @@
         <v>31</v>
       </c>
       <c r="T123" s="5" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="U123" s="5">
         <v>78</v>
@@ -9862,19 +9846,19 @@
         <v>41</v>
       </c>
       <c r="W123" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="124" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>123</v>
@@ -9886,13 +9870,13 @@
       <c r="H124" s="2"/>
       <c r="I124" s="2"/>
       <c r="J124" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="K124" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="L124" s="7" t="s">
         <v>624</v>
-      </c>
-      <c r="K124" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="L124" s="7" t="s">
-        <v>626</v>
       </c>
       <c r="M124" s="2"/>
       <c r="N124" s="2"/>
@@ -9915,37 +9899,37 @@
         <v>39</v>
       </c>
       <c r="W124" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="125" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" s="2" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
       <c r="I125" s="2"/>
       <c r="J125" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="K125" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="L125" s="7" t="s">
         <v>629</v>
-      </c>
-      <c r="K125" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="L125" s="7" t="s">
-        <v>631</v>
       </c>
       <c r="M125" s="2"/>
       <c r="N125" s="2"/>
@@ -9968,37 +9952,37 @@
         <v>29</v>
       </c>
       <c r="W125" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="126" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
       <c r="I126" s="2"/>
       <c r="J126" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="K126" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="L126" s="7" t="s">
         <v>634</v>
-      </c>
-      <c r="K126" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="L126" s="7" t="s">
-        <v>636</v>
       </c>
       <c r="M126" s="2"/>
       <c r="N126" s="2"/>
@@ -10021,37 +10005,37 @@
         <v>35</v>
       </c>
       <c r="W126" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="127" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>141</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G127" s="2"/>
       <c r="H127" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="I127" s="2"/>
       <c r="J127" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="K127" s="2"/>
       <c r="L127" s="7" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="M127" s="2"/>
       <c r="N127" s="2"/>
@@ -10079,32 +10063,32 @@
     </row>
     <row r="128" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>141</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
       <c r="I128" s="2"/>
       <c r="J128" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="K128" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="L128" s="7" t="s">
         <v>646</v>
-      </c>
-      <c r="K128" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="L128" s="7" t="s">
-        <v>648</v>
       </c>
       <c r="M128" s="2"/>
       <c r="N128" s="2"/>
@@ -10132,14 +10116,14 @@
     </row>
     <row r="129" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>123</v>
@@ -10151,13 +10135,13 @@
       <c r="H129" s="2"/>
       <c r="I129" s="2"/>
       <c r="J129" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="K129" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="L129" s="7" t="s">
         <v>650</v>
-      </c>
-      <c r="K129" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="L129" s="7" t="s">
-        <v>652</v>
       </c>
       <c r="M129" s="2"/>
       <c r="N129" s="2"/>
@@ -10185,34 +10169,34 @@
     </row>
     <row r="130" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>141</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G130" s="2"/>
       <c r="H130" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="I130" s="2"/>
       <c r="J130" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="K130" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="L130" s="7" t="s">
         <v>653</v>
-      </c>
-      <c r="K130" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="L130" s="7" t="s">
-        <v>655</v>
       </c>
       <c r="M130" s="2"/>
       <c r="N130" s="2"/>
@@ -10240,36 +10224,36 @@
     </row>
     <row r="131" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" s="5" t="s">
+        <v>656</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="F131" s="2" t="s">
         <v>658</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>660</v>
       </c>
       <c r="G131" s="2"/>
       <c r="H131" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="I131" s="7" t="s">
+        <v>660</v>
+      </c>
+      <c r="J131" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="I131" s="7" t="s">
+      <c r="K131" s="4" t="s">
         <v>662</v>
       </c>
-      <c r="J131" s="2" t="s">
+      <c r="L131" s="7" t="s">
         <v>663</v>
-      </c>
-      <c r="K131" s="4" t="s">
-        <v>664</v>
-      </c>
-      <c r="L131" s="7" t="s">
-        <v>665</v>
       </c>
       <c r="M131" s="2"/>
       <c r="N131" s="2"/>
@@ -10297,14 +10281,14 @@
     </row>
     <row r="132" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="8" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B132" s="8" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C132" s="8"/>
       <c r="D132" s="13" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E132" s="8" t="s">
         <v>113</v>
@@ -10316,13 +10300,13 @@
       <c r="H132" s="8"/>
       <c r="I132" s="8"/>
       <c r="J132" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="K132" s="27" t="s">
+        <v>666</v>
+      </c>
+      <c r="L132" s="26" t="s">
         <v>667</v>
-      </c>
-      <c r="K132" s="27" t="s">
-        <v>668</v>
-      </c>
-      <c r="L132" s="26" t="s">
-        <v>669</v>
       </c>
       <c r="M132" s="8"/>
       <c r="N132" s="8"/>
@@ -10353,11 +10337,11 @@
         <v>70</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>73</v>
@@ -10367,36 +10351,36 @@
       <c r="H133" s="2"/>
       <c r="I133" s="2"/>
       <c r="J133" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="K133" s="2"/>
       <c r="L133" s="28" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
       <c r="P133" s="2"/>
       <c r="Q133" s="2"/>
       <c r="R133" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="S133" s="2" t="s">
         <v>31</v>
       </c>
       <c r="T133" s="5" t="s">
+        <v>673</v>
+      </c>
+      <c r="U133" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="V133" s="5" t="s">
         <v>675</v>
       </c>
-      <c r="U133" s="5" t="s">
-        <v>676</v>
-      </c>
-      <c r="V133" s="5" t="s">
-        <v>677</v>
-      </c>
       <c r="W133" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="134" spans="1:23" x14ac:dyDescent="0.25">
@@ -10404,11 +10388,11 @@
         <v>70</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" s="2" t="s">
@@ -10418,11 +10402,11 @@
       <c r="H134" s="2"/>
       <c r="I134" s="2"/>
       <c r="J134" s="2" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="K134" s="2"/>
       <c r="L134" s="28" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="M134" s="2"/>
       <c r="N134" s="2"/>
@@ -10430,22 +10414,22 @@
       <c r="P134" s="2"/>
       <c r="Q134" s="2"/>
       <c r="R134" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="S134" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="T134" s="5" t="s">
+        <v>680</v>
+      </c>
+      <c r="U134" s="5" t="s">
         <v>681</v>
       </c>
-      <c r="T134" s="5" t="s">
+      <c r="V134" s="5" t="s">
         <v>682</v>
       </c>
-      <c r="U134" s="5" t="s">
-        <v>683</v>
-      </c>
-      <c r="V134" s="5" t="s">
-        <v>684</v>
-      </c>
       <c r="W134" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="135" spans="1:23" x14ac:dyDescent="0.25">
@@ -10453,27 +10437,27 @@
         <v>70</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>73</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
       <c r="I135" s="2"/>
       <c r="J135" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="K135" s="2"/>
       <c r="L135" s="28" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="M135" s="2"/>
       <c r="N135" s="2"/>
@@ -10487,16 +10471,16 @@
         <v>31</v>
       </c>
       <c r="T135" s="5" t="s">
+        <v>687</v>
+      </c>
+      <c r="U135" s="5" t="s">
+        <v>688</v>
+      </c>
+      <c r="V135" s="5" t="s">
         <v>689</v>
       </c>
-      <c r="U135" s="5" t="s">
-        <v>690</v>
-      </c>
-      <c r="V135" s="5" t="s">
-        <v>691</v>
-      </c>
       <c r="W135" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="136" spans="1:23" x14ac:dyDescent="0.25">
@@ -10504,11 +10488,11 @@
         <v>70</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" s="2" t="s">
@@ -10516,15 +10500,15 @@
       </c>
       <c r="G136" s="2"/>
       <c r="H136" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="I136" s="2"/>
       <c r="J136" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="K136" s="2"/>
       <c r="L136" s="28" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="M136" s="2"/>
       <c r="N136" s="2"/>
@@ -10538,16 +10522,16 @@
         <v>31</v>
       </c>
       <c r="T136" s="5" t="s">
+        <v>694</v>
+      </c>
+      <c r="U136" s="5" t="s">
+        <v>695</v>
+      </c>
+      <c r="V136" s="5" t="s">
         <v>696</v>
       </c>
-      <c r="U136" s="5" t="s">
-        <v>697</v>
-      </c>
-      <c r="V136" s="5" t="s">
-        <v>698</v>
-      </c>
       <c r="W136" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="137" spans="1:23" x14ac:dyDescent="0.25">
@@ -10555,11 +10539,11 @@
         <v>70</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" s="2" t="s">
@@ -10567,15 +10551,15 @@
       </c>
       <c r="G137" s="2"/>
       <c r="H137" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="I137" s="2"/>
       <c r="J137" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="K137" s="2"/>
       <c r="L137" s="28" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="M137" s="2"/>
       <c r="N137" s="2"/>
@@ -10586,19 +10570,19 @@
         <v>30</v>
       </c>
       <c r="S137" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="T137" s="5" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="U137" s="5" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="V137" s="5" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="W137" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="138" spans="1:23" x14ac:dyDescent="0.25">
@@ -10606,11 +10590,11 @@
         <v>70</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>73</v>
@@ -10622,13 +10606,13 @@
       <c r="H138" s="2"/>
       <c r="I138" s="2"/>
       <c r="J138" s="2" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="K138" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="L138" s="7" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="M138" s="2"/>
       <c r="N138" s="2"/>
@@ -10636,22 +10620,22 @@
       <c r="P138" s="2"/>
       <c r="Q138" s="2"/>
       <c r="R138" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="S138" s="2" t="s">
         <v>64</v>
       </c>
       <c r="T138" s="5" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="U138" s="5" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="V138" s="5" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="W138" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="139" spans="1:23" x14ac:dyDescent="0.25">
@@ -10659,11 +10643,11 @@
         <v>70</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" s="2" t="s">
@@ -10671,15 +10655,15 @@
       </c>
       <c r="G139" s="2"/>
       <c r="H139" s="2" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="I139" s="2"/>
       <c r="J139" s="2" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="K139" s="2"/>
       <c r="L139" s="7" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="M139" s="2"/>
       <c r="N139" s="2"/>
@@ -10693,16 +10677,16 @@
         <v>31</v>
       </c>
       <c r="T139" s="5" t="s">
+        <v>712</v>
+      </c>
+      <c r="U139" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="V139" s="5" t="s">
         <v>714</v>
       </c>
-      <c r="U139" s="5" t="s">
-        <v>715</v>
-      </c>
-      <c r="V139" s="5" t="s">
-        <v>716</v>
-      </c>
       <c r="W139" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="140" spans="1:23" x14ac:dyDescent="0.25">
@@ -10710,11 +10694,11 @@
         <v>70</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" s="2" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>73</v>
@@ -10726,11 +10710,11 @@
       <c r="H140" s="2"/>
       <c r="I140" s="2"/>
       <c r="J140" s="2" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="K140" s="2"/>
       <c r="L140" s="7" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="M140" s="2"/>
       <c r="N140" s="2"/>
@@ -10744,44 +10728,44 @@
         <v>31</v>
       </c>
       <c r="T140" s="5" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="U140" s="5" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="V140" s="5" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="W140" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="141" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" s="2" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
       <c r="I141" s="2"/>
       <c r="J141" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="K141" s="2"/>
       <c r="L141" s="7" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="M141" s="2"/>
       <c r="N141" s="2"/>
@@ -10809,28 +10793,28 @@
     </row>
     <row r="142" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" s="2" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
       <c r="I142" s="2"/>
       <c r="J142" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="K142" s="2"/>
       <c r="L142" s="7" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="M142" s="2"/>
       <c r="N142" s="2"/>
@@ -10844,13 +10828,13 @@
         <v>31</v>
       </c>
       <c r="T142" s="5" t="s">
+        <v>728</v>
+      </c>
+      <c r="U142" s="5" t="s">
+        <v>729</v>
+      </c>
+      <c r="V142" s="5" t="s">
         <v>730</v>
-      </c>
-      <c r="U142" s="5" t="s">
-        <v>731</v>
-      </c>
-      <c r="V142" s="5" t="s">
-        <v>732</v>
       </c>
       <c r="W142" s="5" t="s">
         <v>107</v>
@@ -10858,32 +10842,32 @@
     </row>
     <row r="143" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
       <c r="I143" s="2"/>
       <c r="J143" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="K143" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="L143" s="7" t="s">
         <v>734</v>
-      </c>
-      <c r="K143" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="L143" s="7" t="s">
-        <v>736</v>
       </c>
       <c r="M143" s="2"/>
       <c r="N143" s="2"/>
@@ -10911,34 +10895,34 @@
     </row>
     <row r="144" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" s="2" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="G144" s="2"/>
       <c r="H144" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="I144" s="2"/>
       <c r="J144" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="K144" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="L144" s="7" t="s">
         <v>739</v>
-      </c>
-      <c r="K144" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="L144" s="7" t="s">
-        <v>741</v>
       </c>
       <c r="M144" s="2"/>
       <c r="N144" s="2"/>
@@ -10966,30 +10950,30 @@
     </row>
     <row r="145" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" s="5" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
       <c r="I145" s="2"/>
       <c r="J145" s="2" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="K145" s="2"/>
       <c r="L145" s="7" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="M145" s="2"/>
       <c r="N145" s="2"/>
@@ -11017,28 +11001,28 @@
     </row>
     <row r="146" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A146" s="29" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B146" s="29" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C146" s="29"/>
       <c r="D146" s="29" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E146" s="29" t="s">
         <v>26</v>
       </c>
       <c r="F146" s="29" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="G146" s="30" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="H146" s="29"/>
       <c r="I146" s="29"/>
       <c r="J146" s="29" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="K146" s="29"/>
       <c r="L146" s="30" t="str">
@@ -11054,10 +11038,10 @@
         <v>30</v>
       </c>
       <c r="S146" s="29" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="T146" s="5" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="U146" s="5"/>
       <c r="V146" s="5"/>
@@ -11067,34 +11051,34 @@
     </row>
     <row r="147" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A147" s="29" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B147" s="29" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C147" s="29"/>
       <c r="D147" s="29" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="E147" s="29" t="s">
         <v>26</v>
       </c>
       <c r="F147" s="29" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="G147" s="30" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="H147" s="29"/>
       <c r="I147" s="29"/>
       <c r="J147" s="29" t="s">
+        <v>751</v>
+      </c>
+      <c r="K147" s="29" t="s">
+        <v>752</v>
+      </c>
+      <c r="L147" s="30" t="s">
         <v>753</v>
-      </c>
-      <c r="K147" s="29" t="s">
-        <v>754</v>
-      </c>
-      <c r="L147" s="30" t="s">
-        <v>755</v>
       </c>
       <c r="M147" s="29"/>
       <c r="N147" s="29"/>
@@ -11105,7 +11089,7 @@
         <v>30</v>
       </c>
       <c r="S147" s="29" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="T147" s="5">
         <v>350</v>
@@ -11118,32 +11102,32 @@
     </row>
     <row r="148" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A148" s="29" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B148" s="29" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C148" s="29"/>
       <c r="D148" s="29" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E148" s="29" t="s">
         <v>26</v>
       </c>
       <c r="F148" s="29" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="G148" s="30" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="H148" s="29"/>
       <c r="I148" s="29"/>
       <c r="J148" s="29" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="K148" s="29"/>
       <c r="L148" s="30" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="M148" s="29"/>
       <c r="N148" s="29"/>
@@ -11154,7 +11138,7 @@
         <v>30</v>
       </c>
       <c r="S148" s="29" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="T148" s="5">
         <v>350</v>
@@ -11167,32 +11151,32 @@
     </row>
     <row r="149" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A149" s="29" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B149" s="29" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C149" s="29"/>
       <c r="D149" s="29" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="E149" s="29" t="s">
         <v>26</v>
       </c>
       <c r="F149" s="29" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="G149" s="30" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="H149" s="29"/>
       <c r="I149" s="29"/>
       <c r="J149" s="29" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="K149" s="29"/>
       <c r="L149" s="30" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="M149" s="29"/>
       <c r="N149" s="29"/>
@@ -11203,7 +11187,7 @@
         <v>30</v>
       </c>
       <c r="S149" s="29" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="T149" s="5">
         <v>350</v>
@@ -11216,32 +11200,32 @@
     </row>
     <row r="150" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
       <c r="I150" s="2"/>
       <c r="J150" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="K150" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="L150" s="7" t="s">
         <v>765</v>
-      </c>
-      <c r="K150" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="L150" s="7" t="s">
-        <v>767</v>
       </c>
       <c r="M150" s="2"/>
       <c r="N150" s="2"/>
@@ -11252,7 +11236,7 @@
         <v>30</v>
       </c>
       <c r="S150" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T150" s="5">
         <v>190</v>
@@ -11269,32 +11253,32 @@
     </row>
     <row r="151" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" s="2" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
       <c r="I151" s="2"/>
       <c r="J151" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="K151" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="L151" s="7" t="s">
         <v>770</v>
-      </c>
-      <c r="K151" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="L151" s="7" t="s">
-        <v>772</v>
       </c>
       <c r="M151" s="2"/>
       <c r="N151" s="2"/>
@@ -11305,7 +11289,7 @@
         <v>30</v>
       </c>
       <c r="S151" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T151" s="5">
         <v>174</v>
@@ -11322,32 +11306,32 @@
     </row>
     <row r="152" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" s="2" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
       <c r="I152" s="2"/>
       <c r="J152" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="K152" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="L152" s="7" t="s">
         <v>774</v>
-      </c>
-      <c r="K152" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="L152" s="7" t="s">
-        <v>776</v>
       </c>
       <c r="M152" s="2"/>
       <c r="N152" s="2"/>
@@ -11358,7 +11342,7 @@
         <v>30</v>
       </c>
       <c r="S152" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T152" s="5">
         <v>160</v>
@@ -11375,14 +11359,14 @@
     </row>
     <row r="153" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>113</v>
@@ -11394,13 +11378,13 @@
       <c r="H153" s="2"/>
       <c r="I153" s="2"/>
       <c r="J153" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K153" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="L153" s="7" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="M153" s="2"/>
       <c r="N153" s="2"/>
@@ -11411,7 +11395,7 @@
         <v>30</v>
       </c>
       <c r="S153" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T153" s="5">
         <v>154</v>
@@ -11428,32 +11412,32 @@
     </row>
     <row r="154" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
       <c r="I154" s="2"/>
       <c r="J154" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="K154" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="L154" s="7" t="s">
         <v>778</v>
-      </c>
-      <c r="K154" s="2" t="s">
-        <v>779</v>
-      </c>
-      <c r="L154" s="7" t="s">
-        <v>780</v>
       </c>
       <c r="M154" s="2"/>
       <c r="N154" s="2"/>
@@ -11464,7 +11448,7 @@
         <v>30</v>
       </c>
       <c r="S154" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T154" s="5">
         <v>164</v>
@@ -11481,32 +11465,32 @@
     </row>
     <row r="155" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" s="2" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
       <c r="I155" s="2"/>
       <c r="J155" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="K155" s="2" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="L155" s="7" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="M155" s="2"/>
       <c r="N155" s="2"/>
@@ -11517,7 +11501,7 @@
         <v>30</v>
       </c>
       <c r="S155" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T155" s="5">
         <v>162</v>
@@ -11534,32 +11518,32 @@
     </row>
     <row r="156" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" s="2" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
       <c r="I156" s="2"/>
       <c r="J156" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="K156" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="L156" s="7" t="s">
         <v>785</v>
-      </c>
-      <c r="K156" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="L156" s="7" t="s">
-        <v>787</v>
       </c>
       <c r="M156" s="2"/>
       <c r="N156" s="2"/>
@@ -11570,7 +11554,7 @@
         <v>30</v>
       </c>
       <c r="S156" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T156" s="5">
         <v>53</v>
@@ -11587,32 +11571,32 @@
     </row>
     <row r="157" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="F157" s="2" t="s">
         <v>788</v>
-      </c>
-      <c r="E157" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="F157" s="2" t="s">
-        <v>790</v>
       </c>
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
       <c r="I157" s="2"/>
       <c r="J157" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="K157" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="L157" s="7" t="s">
         <v>791</v>
-      </c>
-      <c r="K157" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="L157" s="7" t="s">
-        <v>793</v>
       </c>
       <c r="M157" s="2"/>
       <c r="N157" s="2"/>
@@ -11623,7 +11607,7 @@
         <v>30</v>
       </c>
       <c r="S157" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T157" s="5">
         <v>160</v>
@@ -11640,32 +11624,32 @@
     </row>
     <row r="158" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A158" s="29" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B158" s="29" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C158" s="29"/>
       <c r="D158" s="29" t="s">
+        <v>794</v>
+      </c>
+      <c r="E158" s="29" t="s">
+        <v>795</v>
+      </c>
+      <c r="F158" s="29" t="s">
         <v>796</v>
-      </c>
-      <c r="E158" s="29" t="s">
-        <v>797</v>
-      </c>
-      <c r="F158" s="29" t="s">
-        <v>798</v>
       </c>
       <c r="G158" s="29"/>
       <c r="H158" s="29"/>
       <c r="I158" s="29"/>
       <c r="J158" s="29" t="s">
+        <v>797</v>
+      </c>
+      <c r="K158" s="29" t="s">
+        <v>798</v>
+      </c>
+      <c r="L158" s="31" t="s">
         <v>799</v>
-      </c>
-      <c r="K158" s="29" t="s">
-        <v>800</v>
-      </c>
-      <c r="L158" s="31" t="s">
-        <v>801</v>
       </c>
       <c r="M158" s="29"/>
       <c r="N158" s="29"/>
@@ -11693,14 +11677,14 @@
     </row>
     <row r="159" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A159" s="29" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B159" s="29" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C159" s="29"/>
       <c r="D159" s="29" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E159" s="29" t="s">
         <v>26</v>
@@ -11712,13 +11696,13 @@
       <c r="H159" s="29"/>
       <c r="I159" s="29"/>
       <c r="J159" s="29" t="s">
+        <v>800</v>
+      </c>
+      <c r="K159" s="29" t="s">
+        <v>801</v>
+      </c>
+      <c r="L159" s="31" t="s">
         <v>802</v>
-      </c>
-      <c r="K159" s="29" t="s">
-        <v>803</v>
-      </c>
-      <c r="L159" s="31" t="s">
-        <v>804</v>
       </c>
       <c r="M159" s="29"/>
       <c r="N159" s="29"/>
@@ -11746,32 +11730,32 @@
     </row>
     <row r="160" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A160" s="29" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B160" s="29" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C160" s="29"/>
       <c r="D160" s="29" t="s">
+        <v>803</v>
+      </c>
+      <c r="E160" s="29" t="s">
+        <v>804</v>
+      </c>
+      <c r="F160" s="29" t="s">
         <v>805</v>
-      </c>
-      <c r="E160" s="29" t="s">
-        <v>806</v>
-      </c>
-      <c r="F160" s="29" t="s">
-        <v>807</v>
       </c>
       <c r="G160" s="29"/>
       <c r="H160" s="29"/>
       <c r="I160" s="29"/>
       <c r="J160" s="29" t="s">
+        <v>806</v>
+      </c>
+      <c r="K160" s="29" t="s">
+        <v>807</v>
+      </c>
+      <c r="L160" s="31" t="s">
         <v>808</v>
-      </c>
-      <c r="K160" s="29" t="s">
-        <v>809</v>
-      </c>
-      <c r="L160" s="31" t="s">
-        <v>810</v>
       </c>
       <c r="M160" s="29"/>
       <c r="N160" s="29"/>
@@ -11785,7 +11769,7 @@
         <v>64</v>
       </c>
       <c r="T160" s="5" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="U160" s="5">
         <v>400</v>
@@ -11799,32 +11783,32 @@
     </row>
     <row r="161" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A161" s="29" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B161" s="29" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C161" s="29"/>
       <c r="D161" s="29" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="E161" s="29" t="s">
         <v>26</v>
       </c>
       <c r="F161" s="29" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="G161" s="29"/>
       <c r="H161" s="29"/>
       <c r="I161" s="29"/>
       <c r="J161" s="29" t="s">
+        <v>812</v>
+      </c>
+      <c r="K161" s="29" t="s">
+        <v>813</v>
+      </c>
+      <c r="L161" s="31" t="s">
         <v>814</v>
-      </c>
-      <c r="K161" s="29" t="s">
-        <v>815</v>
-      </c>
-      <c r="L161" s="31" t="s">
-        <v>816</v>
       </c>
       <c r="M161" s="29"/>
       <c r="N161" s="29"/>
@@ -11852,32 +11836,32 @@
     </row>
     <row r="162" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A162" s="29" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B162" s="29" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C162" s="29"/>
       <c r="D162" s="29" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="E162" s="29" t="s">
         <v>26</v>
       </c>
       <c r="F162" s="29" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="G162" s="29"/>
       <c r="H162" s="29"/>
       <c r="I162" s="29"/>
       <c r="J162" s="29" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="K162" s="29" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="L162" s="31" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="M162" s="29"/>
       <c r="N162" s="29"/>
@@ -11905,32 +11889,32 @@
     </row>
     <row r="163" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A163" s="29" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B163" s="29" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C163" s="29"/>
       <c r="D163" s="29" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="E163" s="29" t="s">
         <v>26</v>
       </c>
       <c r="F163" s="29" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="G163" s="29"/>
       <c r="H163" s="29"/>
       <c r="I163" s="29"/>
       <c r="J163" s="29" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="K163" s="29" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L163" s="31" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="M163" s="29"/>
       <c r="N163" s="29"/>
@@ -11958,30 +11942,30 @@
     </row>
     <row r="164" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C164" s="29"/>
       <c r="D164" s="2" t="s">
         <v>190</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
       <c r="I164" s="2"/>
       <c r="J164" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K164" s="2"/>
       <c r="L164" s="7" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="M164" s="2"/>
       <c r="N164" s="2"/>
@@ -12009,32 +11993,32 @@
     </row>
     <row r="165" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C165" s="29"/>
       <c r="D165" s="2" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
       <c r="I165" s="2"/>
       <c r="J165" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="K165" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="L165" s="7" t="s">
         <v>897</v>
-      </c>
-      <c r="K165" s="2" t="s">
-        <v>898</v>
-      </c>
-      <c r="L165" s="7" t="s">
-        <v>899</v>
       </c>
       <c r="M165" s="2"/>
       <c r="N165" s="2"/>
@@ -12062,32 +12046,32 @@
     </row>
     <row r="166" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C166" s="29"/>
       <c r="D166" s="2" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
       <c r="I166" s="2"/>
       <c r="J166" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="K166" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="L166" s="7" t="s">
         <v>900</v>
-      </c>
-      <c r="K166" s="2" t="s">
-        <v>901</v>
-      </c>
-      <c r="L166" s="7" t="s">
-        <v>902</v>
       </c>
       <c r="M166" s="2"/>
       <c r="N166" s="2"/>
@@ -12115,32 +12099,32 @@
     </row>
     <row r="167" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C167" s="29"/>
       <c r="D167" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="F167" s="2" t="s">
         <v>903</v>
-      </c>
-      <c r="E167" s="2" t="s">
-        <v>904</v>
-      </c>
-      <c r="F167" s="2" t="s">
-        <v>905</v>
       </c>
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
       <c r="I167" s="7" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="J167" s="2" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="K167" s="2"/>
       <c r="L167" s="7" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="M167" s="2"/>
       <c r="N167" s="2"/>
@@ -12171,27 +12155,27 @@
         <v>96</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="F168" s="2" t="s">
         <v>828</v>
-      </c>
-      <c r="E168" s="2" t="s">
-        <v>829</v>
-      </c>
-      <c r="F168" s="2" t="s">
-        <v>830</v>
       </c>
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
       <c r="I168" s="2"/>
       <c r="J168" s="2" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="K168" s="2"/>
       <c r="L168" s="7" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="M168" s="2"/>
       <c r="N168" s="2"/>
@@ -12199,7 +12183,7 @@
       <c r="P168" s="2"/>
       <c r="Q168" s="2"/>
       <c r="R168" s="2" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="S168" s="2" t="s">
         <v>96</v>
@@ -12222,11 +12206,11 @@
         <v>96</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" s="2" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>73</v>
@@ -12238,11 +12222,11 @@
       <c r="H169" s="2"/>
       <c r="I169" s="2"/>
       <c r="J169" s="2" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="K169" s="2"/>
       <c r="L169" s="7" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="M169" s="2"/>
       <c r="N169" s="2"/>
@@ -12273,11 +12257,11 @@
         <v>96</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" s="2" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>73</v>
@@ -12289,11 +12273,11 @@
       <c r="H170" s="2"/>
       <c r="I170" s="2"/>
       <c r="J170" s="2" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="K170" s="2"/>
       <c r="L170" s="7" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="M170" s="2"/>
       <c r="N170" s="2"/>
@@ -12324,11 +12308,11 @@
         <v>96</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>73</v>
@@ -12340,11 +12324,11 @@
       <c r="H171" s="2"/>
       <c r="I171" s="2"/>
       <c r="J171" s="2" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="K171" s="2"/>
       <c r="L171" s="7" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="M171" s="2"/>
       <c r="N171" s="2"/>
@@ -12375,27 +12359,27 @@
         <v>96</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G172" s="2"/>
       <c r="H172" s="2"/>
       <c r="I172" s="2"/>
       <c r="J172" s="2" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="K172" s="2"/>
       <c r="L172" s="7" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="M172" s="2"/>
       <c r="N172" s="2"/>
@@ -12403,7 +12387,7 @@
       <c r="P172" s="2"/>
       <c r="Q172" s="2"/>
       <c r="R172" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="S172" s="2" t="s">
         <v>31</v>
@@ -12426,29 +12410,29 @@
         <v>96</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" s="2" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="G173" s="2"/>
       <c r="H173" s="2"/>
       <c r="I173" s="2"/>
       <c r="J173" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="K173" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="L173" s="7" t="s">
         <v>912</v>
-      </c>
-      <c r="K173" s="2" t="s">
-        <v>913</v>
-      </c>
-      <c r="L173" s="7" t="s">
-        <v>914</v>
       </c>
       <c r="M173" s="2"/>
       <c r="N173" s="2"/>
@@ -12479,29 +12463,29 @@
         <v>96</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" s="2" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
       <c r="I174" s="2"/>
       <c r="J174" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="K174" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="L174" s="7" t="s">
         <v>916</v>
-      </c>
-      <c r="K174" s="2" t="s">
-        <v>917</v>
-      </c>
-      <c r="L174" s="7" t="s">
-        <v>918</v>
       </c>
       <c r="M174" s="2"/>
       <c r="N174" s="2"/>
@@ -12532,11 +12516,11 @@
         <v>96</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>73</v>
@@ -12548,11 +12532,11 @@
       <c r="H175" s="2"/>
       <c r="I175" s="2"/>
       <c r="J175" s="2" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="K175" s="2"/>
       <c r="L175" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="M175" s="2"/>
       <c r="N175" s="2"/>
@@ -12580,30 +12564,30 @@
     </row>
     <row r="176" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" s="2" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="G176" s="2"/>
       <c r="H176" s="2"/>
       <c r="I176" s="2"/>
       <c r="J176" s="2" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="K176" s="2"/>
       <c r="L176" s="7" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="M176" s="2"/>
       <c r="N176" s="2"/>
@@ -12631,32 +12615,30 @@
     </row>
     <row r="177" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" s="2" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="G177" s="2"/>
-      <c r="H177" s="2" t="s">
-        <v>926</v>
-      </c>
+      <c r="H177" s="2"/>
       <c r="I177" s="2"/>
       <c r="J177" s="2" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="K177" s="2"/>
       <c r="L177" s="7" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="M177" s="2"/>
       <c r="N177" s="2"/>
@@ -12664,7 +12646,7 @@
       <c r="P177" s="2"/>
       <c r="Q177" s="2"/>
       <c r="R177" s="2" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="S177" s="2" t="s">
         <v>64</v>
@@ -12684,32 +12666,30 @@
     </row>
     <row r="178" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" s="2" t="s">
         <v>97</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="G178" s="2"/>
-      <c r="H178" s="2" t="s">
-        <v>931</v>
-      </c>
+      <c r="H178" s="2"/>
       <c r="I178" s="2"/>
       <c r="J178" s="2" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="K178" s="2"/>
       <c r="L178" s="7" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="M178" s="2"/>
       <c r="N178" s="2"/>
@@ -12717,7 +12697,7 @@
       <c r="P178" s="2"/>
       <c r="Q178" s="2"/>
       <c r="R178" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="S178" s="2" t="s">
         <v>31</v>
@@ -12737,32 +12717,30 @@
     </row>
     <row r="179" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" s="2" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="G179" s="2"/>
-      <c r="H179" s="2" t="s">
-        <v>931</v>
-      </c>
+      <c r="H179" s="2"/>
       <c r="I179" s="2"/>
       <c r="J179" s="2" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="K179" s="2"/>
       <c r="L179" s="7" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="M179" s="2"/>
       <c r="N179" s="2"/>
@@ -12770,7 +12748,7 @@
       <c r="P179" s="2"/>
       <c r="Q179" s="2"/>
       <c r="R179" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="S179" s="2" t="s">
         <v>31</v>
@@ -12790,32 +12768,30 @@
     </row>
     <row r="180" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" s="2" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="G180" s="2"/>
-      <c r="H180" s="2" t="s">
-        <v>963</v>
-      </c>
+      <c r="H180" s="2"/>
       <c r="I180" s="2"/>
       <c r="J180" s="2" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="K180" s="2"/>
       <c r="L180" s="7" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="M180" s="2"/>
       <c r="N180" s="2"/>
@@ -12843,32 +12819,30 @@
     </row>
     <row r="181" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" s="2" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>942</v>
+        <v>957</v>
       </c>
       <c r="G181" s="2"/>
-      <c r="H181" s="2" t="s">
-        <v>943</v>
-      </c>
+      <c r="H181" s="2"/>
       <c r="I181" s="2"/>
       <c r="J181" s="2" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="K181" s="2"/>
       <c r="L181" s="7" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
       <c r="M181" s="2"/>
       <c r="N181" s="2"/>
@@ -12896,10 +12870,10 @@
     </row>
     <row r="182" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" s="2" t="s">
@@ -12909,17 +12883,17 @@
         <v>26</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="G182" s="2"/>
       <c r="H182" s="2"/>
       <c r="I182" s="2"/>
       <c r="J182" s="2" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="K182" s="2"/>
       <c r="L182" s="7" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="M182" s="2"/>
       <c r="N182" s="2"/>
@@ -12943,36 +12917,36 @@
     </row>
     <row r="183" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="G183" s="2"/>
       <c r="H183" s="2" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="I183" s="2"/>
       <c r="J183" s="2" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="K183" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L183" s="7" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="M183" s="2"/>
       <c r="N183" s="2"/>
@@ -12996,39 +12970,39 @@
     </row>
     <row r="184" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="G184" s="2"/>
       <c r="H184" s="2" t="s">
-        <v>952</v>
+        <v>946</v>
       </c>
       <c r="I184" s="2"/>
       <c r="J184" s="2" t="s">
-        <v>953</v>
+        <v>947</v>
       </c>
       <c r="K184" s="2" t="s">
-        <v>954</v>
+        <v>948</v>
       </c>
       <c r="L184" s="7" t="s">
-        <v>955</v>
+        <v>949</v>
       </c>
       <c r="M184" s="2" t="s">
-        <v>956</v>
+        <v>950</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
@@ -13051,36 +13025,36 @@
     </row>
     <row r="185" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="G185" s="2"/>
       <c r="H185" s="2" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="I185" s="2"/>
       <c r="J185" s="2" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
       <c r="K185" s="2" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="L185" s="7" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
       <c r="M185" s="2"/>
       <c r="N185" s="2"/>
@@ -13104,32 +13078,32 @@
     </row>
     <row r="186" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" s="2" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>141</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="G186" s="2"/>
       <c r="H186" s="2"/>
       <c r="I186" s="2"/>
       <c r="J186" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="K186" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="L186" s="7" t="s">
         <v>854</v>
-      </c>
-      <c r="K186" s="2" t="s">
-        <v>855</v>
-      </c>
-      <c r="L186" s="7" t="s">
-        <v>856</v>
       </c>
       <c r="M186" s="2"/>
       <c r="N186" s="2"/>
@@ -13143,7 +13117,7 @@
         <v>64</v>
       </c>
       <c r="T186" s="5" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="U186" s="5"/>
       <c r="V186" s="5"/>
@@ -13153,32 +13127,32 @@
     </row>
     <row r="187" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="G187" s="2"/>
       <c r="H187" s="2"/>
       <c r="I187" s="2"/>
       <c r="J187" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="K187" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="L187" s="7" t="s">
         <v>860</v>
-      </c>
-      <c r="K187" s="2" t="s">
-        <v>861</v>
-      </c>
-      <c r="L187" s="7" t="s">
-        <v>862</v>
       </c>
       <c r="M187" s="2"/>
       <c r="N187" s="2"/>
@@ -13186,13 +13160,13 @@
       <c r="P187" s="2"/>
       <c r="Q187" s="2"/>
       <c r="R187" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="S187" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="T187" s="5" t="s">
         <v>863</v>
-      </c>
-      <c r="S187" s="2" t="s">
-        <v>864</v>
-      </c>
-      <c r="T187" s="5" t="s">
-        <v>865</v>
       </c>
       <c r="U187" s="5"/>
       <c r="V187" s="5"/>
@@ -13202,32 +13176,32 @@
     </row>
     <row r="188" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" s="2" t="s">
         <v>65</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="G188" s="2"/>
       <c r="H188" s="2"/>
       <c r="I188" s="2"/>
       <c r="J188" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="K188" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="L188" s="7" t="s">
         <v>867</v>
-      </c>
-      <c r="K188" s="2" t="s">
-        <v>868</v>
-      </c>
-      <c r="L188" s="7" t="s">
-        <v>869</v>
       </c>
       <c r="M188" s="2"/>
       <c r="N188" s="2"/>
@@ -13235,13 +13209,13 @@
       <c r="P188" s="2"/>
       <c r="Q188" s="2"/>
       <c r="R188" s="2" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="S188" s="2" t="s">
         <v>64</v>
       </c>
       <c r="T188" s="5" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="U188" s="5"/>
       <c r="V188" s="5"/>
@@ -13251,32 +13225,32 @@
     </row>
     <row r="189" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>141</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G189" s="2"/>
       <c r="H189" s="2"/>
       <c r="I189" s="2"/>
       <c r="J189" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="K189" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="L189" s="7" t="s">
         <v>873</v>
-      </c>
-      <c r="K189" s="2" t="s">
-        <v>874</v>
-      </c>
-      <c r="L189" s="7" t="s">
-        <v>875</v>
       </c>
       <c r="M189" s="2"/>
       <c r="N189" s="2"/>
@@ -13290,7 +13264,7 @@
         <v>64</v>
       </c>
       <c r="T189" s="5" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="U189" s="5"/>
       <c r="V189" s="5"/>
@@ -13300,32 +13274,32 @@
     </row>
     <row r="190" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>141</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="G190" s="2"/>
       <c r="H190" s="2"/>
       <c r="I190" s="2"/>
       <c r="J190" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="K190" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="L190" s="7" t="s">
         <v>877</v>
-      </c>
-      <c r="K190" s="2" t="s">
-        <v>878</v>
-      </c>
-      <c r="L190" s="7" t="s">
-        <v>879</v>
       </c>
       <c r="M190" s="2"/>
       <c r="N190" s="2"/>
@@ -13339,7 +13313,7 @@
         <v>64</v>
       </c>
       <c r="T190" s="5" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="U190" s="5"/>
       <c r="V190" s="5"/>
@@ -13349,32 +13323,32 @@
     </row>
     <row r="191" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="F191" s="2" t="s">
         <v>881</v>
-      </c>
-      <c r="E191" s="2" t="s">
-        <v>882</v>
-      </c>
-      <c r="F191" s="2" t="s">
-        <v>883</v>
       </c>
       <c r="G191" s="2"/>
       <c r="H191" s="2"/>
       <c r="I191" s="2"/>
       <c r="J191" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="K191" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="L191" s="7" t="s">
         <v>884</v>
-      </c>
-      <c r="K191" s="2" t="s">
-        <v>885</v>
-      </c>
-      <c r="L191" s="7" t="s">
-        <v>886</v>
       </c>
       <c r="M191" s="2"/>
       <c r="N191" s="2"/>
@@ -13382,10 +13356,10 @@
       <c r="P191" s="2"/>
       <c r="Q191" s="2"/>
       <c r="R191" s="2" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="S191" s="2" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="T191" s="5">
         <v>85</v>
@@ -13398,14 +13372,14 @@
     </row>
     <row r="192" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A192" s="10" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B192" s="10" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="C192" s="10"/>
       <c r="D192" s="14" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="E192" s="10"/>
       <c r="F192" s="10" t="s">
@@ -13413,15 +13387,15 @@
       </c>
       <c r="G192" s="10"/>
       <c r="H192" s="10" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="I192" s="10"/>
       <c r="J192" s="10" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="K192" s="10"/>
       <c r="L192" s="11" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="M192" s="10"/>
       <c r="N192" s="10"/>
@@ -13432,7 +13406,7 @@
         <v>30</v>
       </c>
       <c r="S192" s="10" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="T192" s="23">
         <v>240</v>

--- a/quizzes/sculpture-17e.xlsx
+++ b/quizzes/sculpture-17e.xlsx
@@ -6987,7 +6987,7 @@
       <c r="Q88" s="2" t="n"/>
       <c r="R88" s="2" t="inlineStr">
         <is>
-          <t>Monument</t>
+          <t>Elément architectural</t>
         </is>
       </c>
       <c r="S88" s="2" t="inlineStr">

--- a/quizzes/sculpture-17e.xlsx
+++ b/quizzes/sculpture-17e.xlsx
@@ -7186,8 +7186,10 @@
       <c r="R73" s="2" t="s">
         <v>923</v>
       </c>
-      <c r="S73" s="2" t="s">
-        <v>921</v>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bronze pour la statue, marbre pour le socle</t>
+        </is>
       </c>
       <c r="T73" s="5" t="s">
         <v>922</v>
@@ -10885,8 +10887,10 @@
       <c r="R143" s="28" t="s">
         <v>914</v>
       </c>
-      <c r="S143" s="28" t="s">
-        <v>915</v>
+      <c r="S143" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bronze pour la ronde-bosse et le bas-relief, marbre pour le socle</t>
+        </is>
       </c>
       <c r="T143" s="5" t="s">
         <v>916</v>
@@ -12251,8 +12255,10 @@
       <c r="R169" s="2" t="s">
         <v>911</v>
       </c>
-      <c r="S169" s="2" t="s">
-        <v>910</v>
+      <c r="S169" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bronze pour la statue et le bas-relief, marbre pour le socle</t>
+        </is>
       </c>
       <c r="T169" s="5" t="s">
         <v>912</v>
@@ -12362,8 +12368,10 @@
           <t xml:space="preserve">Monument avec ronde-bosse, l'artiste n'a conçu que la ronde-bosse. Le socle fontaine date du 19e siècle.</t>
         </is>
       </c>
-      <c r="S171" s="2" t="s">
-        <v>918</v>
+      <c r="S171" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bronze pour la ronde-bosse, granite et marbre pour le socle</t>
+        </is>
       </c>
       <c r="T171" s="5" t="s">
         <v>919</v>

--- a/quizzes/sculpture-17e.xlsx
+++ b/quizzes/sculpture-17e.xlsx
@@ -7183,8 +7183,10 @@
       <c r="O73" s="2"/>
       <c r="P73" s="2"/>
       <c r="Q73" s="2"/>
-      <c r="R73" s="2" t="s">
-        <v>923</v>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monument avec ronde-bosse en bronze, sur un socle en marbre, l'artiste a conçu une première statue détruite en 1792. Lemot a créé une réplique en 1825, le socle datant également de 1825.</t>
+        </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
@@ -10884,8 +10886,10 @@
       <c r="O143" s="28"/>
       <c r="P143" s="28"/>
       <c r="Q143" s="28"/>
-      <c r="R143" s="28" t="s">
-        <v>914</v>
+      <c r="R143" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monument avec ronde-bosse et bas-relief en bronze, conçu intégralement par l'artiste, sur un socle en marbre.</t>
+        </is>
       </c>
       <c r="S143" s="28" t="inlineStr">
         <is>
@@ -12252,8 +12256,10 @@
       <c r="O169" s="2"/>
       <c r="P169" s="2"/>
       <c r="Q169" s="2"/>
-      <c r="R169" s="2" t="s">
-        <v>911</v>
+      <c r="R169" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monument avec ronde-bosse et bas-relief en bronze, imaginé par Jean Bologne et réalisé intégralement par son élève, Pietro Tacca, sur un socle en marbre.</t>
+        </is>
       </c>
       <c r="S169" s="2" t="inlineStr">
         <is>
@@ -12365,7 +12371,7 @@
       <c r="Q171" s="2"/>
       <c r="R171" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monument avec ronde-bosse, l'artiste n'a conçu que la ronde-bosse. Le socle fontaine date du 19e siècle.</t>
+          <t xml:space="preserve">Monument avec ronde-bosse en bronze, l'artiste n'a conçu que la ronde-bosse. Le socle fontaine en granite et marbre date du 19e siècle.</t>
         </is>
       </c>
       <c r="S171" s="2" t="inlineStr">

--- a/quizzes/sculpture-17e.xlsx
+++ b/quizzes/sculpture-17e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4E82648-3F00-4892-93AC-CB4CCDBBB394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73EDEA9E-943A-424D-8CC8-2784C9E7A36F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="928">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1825" uniqueCount="949">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -1294,15 +1294,9 @@
     <t>Rijksmuseum</t>
   </si>
   <si>
-    <t>Triton soufflant dans une conque (fontaine de Neptune de Frederiksborg)</t>
-  </si>
-  <si>
     <t>Triton, Blowing on a Trumpet Shell</t>
   </si>
   <si>
-    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6e/Triton%2C_blazend_op_een_kinkhoorn%2C_BK-C-1997-2.jpg/960px-Triton%2C_blazend_op_een_kinkhoorn%2C_BK-C-1997-2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>1620 environ</t>
   </si>
   <si>
@@ -1666,12 +1660,6 @@
     <t>1675-1678</t>
   </si>
   <si>
-    <t>Queluz (Sintra)</t>
-  </si>
-  <si>
-    <t>Palais royal de Queluz</t>
-  </si>
-  <si>
     <t>Jardins</t>
   </si>
   <si>
@@ -2752,48 +2740,24 @@
     <t>Jean BOLOGNE</t>
   </si>
   <si>
-    <t>Bronze (statue et bas-relief) et  marbre (socle)</t>
-  </si>
-  <si>
-    <t>Monument avec ronde-bosse et bas-relief, imaginé par Jean Bologne et réalisé intégralement par son élève, Pietro Tacca.</t>
-  </si>
-  <si>
     <t>450 pour la statue, 400 pour le socle</t>
   </si>
   <si>
     <t>Monument équestre d'Alexandre Farnèse</t>
   </si>
   <si>
-    <t>Monument avec ronde-bosse et bas-relief, conçu intégralement par l'artiste.</t>
-  </si>
-  <si>
-    <t>Marbre (socle) Bronze (ronde-bosse et bas-relief)</t>
-  </si>
-  <si>
     <t>400 pour la statue, 450 pour le socle</t>
   </si>
   <si>
-    <t>Monument avec ronde-bosse, l'artiste n'a conçu que la ronde-bosse. Le socle fontaine dta du 19e siècle.</t>
-  </si>
-  <si>
-    <t>Bronze (ronde-bosse) granite et marbre (socle)</t>
-  </si>
-  <si>
     <t>420 pour la statue et 780 pour le socle</t>
   </si>
   <si>
     <t xml:space="preserve">François-Frédéric LEMOT </t>
   </si>
   <si>
-    <t>Bronze (statue) et marbre (socle)</t>
-  </si>
-  <si>
     <t>520 pour la statue, 400 pour le socle</t>
   </si>
   <si>
-    <t xml:space="preserve">Monument avec ronde-bosse, l'artiste a conçu une première statue  détruite en 1792. Lemot a créé une réplique  en 1825, le socle datant également de 1825. </t>
-  </si>
-  <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV_-_Apr%C3%A8s_r%C3%A9fection_des_murets_01.jpg/1280px-Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV_-_Apr%C3%A8s_r%C3%A9fection_des_murets_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -2804,6 +2768,105 @@
   </si>
   <si>
     <t xml:space="preserve">Ronde-bosse </t>
+  </si>
+  <si>
+    <t>Monument avec ronde-bosse en bronze, sur un socle en marbre, l'artiste a conçu une première statue détruite en 1792. Lemot a créé une réplique en 1825, le socle datant également de 1825.</t>
+  </si>
+  <si>
+    <t>Bronze pour la statue, marbre pour le socle</t>
+  </si>
+  <si>
+    <t>Monument avec ronde-bosse et bas-relief en bronze, conçu intégralement par l'artiste, sur un socle en marbre.</t>
+  </si>
+  <si>
+    <t>Bronze pour la ronde-bosse et le bas-relief, marbre pour le socle</t>
+  </si>
+  <si>
+    <t>1608</t>
+  </si>
+  <si>
+    <t>Monument avec ronde-bosse et bas-relief en bronze, imaginé par Jean Bologne et réalisé intégralement par son élève, Pietro Tacca, sur un socle en marbre.</t>
+  </si>
+  <si>
+    <t>Bronze pour la statue et le bas-relief, marbre pour le socle</t>
+  </si>
+  <si>
+    <t>Monument avec ronde-bosse en bronze, l'artiste n'a conçu que la ronde-bosse. Le socle fontaine en granite et marbre date du 19e siècle.</t>
+  </si>
+  <si>
+    <t>Bronze pour la ronde-bosse, granite et marbre pour le socle</t>
+  </si>
+  <si>
+    <t>Statues de la fontaine de Neptune de Frederiksborg</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/23/Hiller%C3%B8d_106.jpg/960px-Hiller%C3%B8d_106.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/90/Hiller%C3%B8d_109.jpg/1280px-Hiller%C3%B8d_109.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/4/45/FrbSlotNeptunspringvand14.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>Stockholm</t>
+  </si>
+  <si>
+    <t>Château de Drottningholm</t>
+  </si>
+  <si>
+    <t>Pierre et bronze</t>
+  </si>
+  <si>
+    <t>Fontaine monumentale dont les rondes-bosses en bronze ont été réalisées par Adrian de Vries.le bassin et la colonne ont été créés par des artisans locaux. L'ensemble des bronzes a été pillé en 1659 et remonté de façon dispersée au château de Drottningholm en Suède, puis placés dans le musée de Vries du château.  La fontaine de Frederiskborg actuelle est une reconstitution de 1888 par Heinrich Hansen à partir de moulages sur les originaux.</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/ba/Logge_del_mercato_nuovo%2C_il_porcellino.jpg/1280px-Logge_del_mercato_nuovo%2C_il_porcellino.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/a/aa/Florencja_Il_Porcelino_RB.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monument avec ronde-bosse. Il a été intégralement conçu par l'artiste pour la ville de Livourne. A la mort de Tacca, le grand duc de Florence l'a gardé pour la ville. </t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/79/Ferdinando_Tacca%2C_fontana_dei_mostri_marini%2C_dx%2C_12.JPG/1280px-Ferdinando_Tacca%2C_fontana_dei_mostri_marini%2C_dx%2C_12.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d2/Pietro_Tacca-Mannerist_fountain-Florence.jpg/1280px-Pietro_Tacca-Mannerist_fountain-Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Monument avec ronde-bosse. Il a été intégralement conçu par l'artiste.</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Fontaine_Triton_-_Rome_%28IT62%29_-_2021-08-30_-_1.jpg/1280px-Fontaine_Triton_-_Rome_%28IT62%29_-_2021-08-30_-_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c2/Fontaine_Triton_-_Rome_%28IT62%29_-_2021-08-30_-_3.jpg/960px-Fontaine_Triton_-_Rome_%28IT62%29_-_2021-08-30_-_3.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Monument avec groupe en ronde-bosse. Le projet a été intégralement conçu par l'artiste, chacun des fleuves ayant été créé par un sculpteur différent. L'obélique antique a été récupéré sur le cirque de Maxence pour être intégré au monument.</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3f/Obelisk_Navona_Rom.jpg/960px-Obelisk_Navona_Rom.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Piazza_Navona_Roma_Italy_HDR_2013_03.jpg/1280px-Piazza_Navona_Roma_Italy_HDR_2013_03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>Gian Lorenzo BERNINI</t>
+  </si>
+  <si>
+    <t>Monument avec groupe en ronde-bosse. Le projet a été intégralement conçu parLe Bernin. Agé de quatre-vingt ans, il a confié à son élève Ercole Ferrata l'éxécution de la fontaine,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queluz </t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7b/Fonte_de_Neptuno_Pal%C3%A1cio_Queluz_01.jpg/1280px-Fonte_de_Neptuno_Pal%C3%A1cio_Queluz_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/37/Throwing_blessings_%2829790747562%29.jpg/1280px-Throwing_blessings_%2829790747562%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -3459,7 +3522,7 @@
         <v>22</v>
       </c>
       <c r="X1" s="21" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4560,9 +4623,13 @@
       <c r="F23" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="G23" s="2"/>
+      <c r="G23" s="25" t="s">
+        <v>939</v>
+      </c>
       <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
+      <c r="I23" s="25" t="s">
+        <v>940</v>
+      </c>
       <c r="J23" s="2" t="s">
         <v>128</v>
       </c>
@@ -4576,7 +4643,7 @@
       <c r="P23" s="2"/>
       <c r="Q23" s="16"/>
       <c r="R23" s="2" t="s">
-        <v>130</v>
+        <v>938</v>
       </c>
       <c r="S23" s="6" t="s">
         <v>131</v>
@@ -4662,9 +4729,13 @@
       <c r="F25" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G25" s="2"/>
+      <c r="G25" s="25" t="s">
+        <v>943</v>
+      </c>
       <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
+      <c r="I25" s="25" t="s">
+        <v>942</v>
+      </c>
       <c r="J25" s="2" t="s">
         <v>138</v>
       </c>
@@ -4678,7 +4749,7 @@
       <c r="P25" s="2"/>
       <c r="Q25" s="16"/>
       <c r="R25" s="2" t="s">
-        <v>130</v>
+        <v>941</v>
       </c>
       <c r="S25" s="6" t="s">
         <v>140</v>
@@ -7165,11 +7236,11 @@
         <v>395</v>
       </c>
       <c r="G73" s="25" t="s">
-        <v>924</v>
+        <v>912</v>
       </c>
       <c r="H73" s="2"/>
       <c r="I73" s="25" t="s">
-        <v>925</v>
+        <v>913</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>396</v>
@@ -7183,18 +7254,14 @@
       <c r="O73" s="2"/>
       <c r="P73" s="2"/>
       <c r="Q73" s="2"/>
-      <c r="R73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Monument avec ronde-bosse en bronze, sur un socle en marbre, l'artiste a conçu une première statue détruite en 1792. Lemot a créé une réplique en 1825, le socle datant également de 1825.</t>
-        </is>
-      </c>
-      <c r="S73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bronze pour la statue, marbre pour le socle</t>
-        </is>
+      <c r="R73" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="S73" s="2" t="s">
+        <v>917</v>
       </c>
       <c r="T73" s="5" t="s">
-        <v>922</v>
+        <v>911</v>
       </c>
       <c r="U73" s="5">
         <v>540</v>
@@ -7206,7 +7273,7 @@
         <v>3</v>
       </c>
       <c r="X73" t="s">
-        <v>920</v>
+        <v>910</v>
       </c>
     </row>
     <row r="74" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7429,22 +7496,26 @@
         <v>421</v>
       </c>
       <c r="E78" s="35" t="s">
-        <v>422</v>
+        <v>929</v>
       </c>
       <c r="F78" s="35" t="s">
-        <v>423</v>
-      </c>
-      <c r="G78" s="35"/>
+        <v>930</v>
+      </c>
+      <c r="G78" s="25" t="s">
+        <v>927</v>
+      </c>
       <c r="H78" s="35"/>
-      <c r="I78" s="35"/>
+      <c r="I78" s="25" t="s">
+        <v>928</v>
+      </c>
       <c r="J78" s="35" t="s">
+        <v>925</v>
+      </c>
+      <c r="K78" s="35" t="s">
         <v>424</v>
       </c>
-      <c r="K78" s="35" t="s">
-        <v>425</v>
-      </c>
       <c r="L78" s="25" t="s">
-        <v>426</v>
+        <v>926</v>
       </c>
       <c r="M78" s="35"/>
       <c r="N78" s="35"/>
@@ -7452,19 +7523,19 @@
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
       <c r="R78" s="35" t="s">
-        <v>30</v>
+        <v>932</v>
       </c>
       <c r="S78" s="35" t="s">
-        <v>62</v>
+        <v>931</v>
       </c>
       <c r="T78" s="34">
-        <v>157</v>
+        <v>600</v>
       </c>
       <c r="U78" s="34">
-        <v>88</v>
+        <v>1000</v>
       </c>
       <c r="V78" s="34">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="W78" s="31">
         <v>1</v>
@@ -7479,25 +7550,25 @@
       </c>
       <c r="C79" s="33"/>
       <c r="D79" s="33" t="s">
+        <v>425</v>
+      </c>
+      <c r="E79" s="33" t="s">
+        <v>426</v>
+      </c>
+      <c r="F79" s="33" t="s">
         <v>427</v>
-      </c>
-      <c r="E79" s="33" t="s">
-        <v>428</v>
-      </c>
-      <c r="F79" s="33" t="s">
-        <v>429</v>
       </c>
       <c r="G79" s="33"/>
       <c r="H79" s="33"/>
       <c r="I79" s="33"/>
       <c r="J79" s="33" t="s">
+        <v>428</v>
+      </c>
+      <c r="K79" s="33" t="s">
+        <v>429</v>
+      </c>
+      <c r="L79" s="25" t="s">
         <v>430</v>
-      </c>
-      <c r="K79" s="33" t="s">
-        <v>431</v>
-      </c>
-      <c r="L79" s="25" t="s">
-        <v>432</v>
       </c>
       <c r="M79" s="33"/>
       <c r="N79" s="33"/>
@@ -7508,7 +7579,7 @@
         <v>36</v>
       </c>
       <c r="S79" s="33" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="T79" s="32">
         <v>500</v>
@@ -7528,27 +7599,27 @@
         <v>68</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
       <c r="J80" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="K80" s="2"/>
       <c r="L80" s="7" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
@@ -7579,27 +7650,27 @@
         <v>68</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
       <c r="J81" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="K81" s="2"/>
       <c r="L81" s="7" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
@@ -7628,11 +7699,11 @@
         <v>68</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>26</v>
@@ -7644,11 +7715,11 @@
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
       <c r="J82" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="K82" s="2"/>
       <c r="L82" s="7" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
@@ -7679,27 +7750,27 @@
         <v>68</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
       <c r="J83" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="K83" s="2"/>
       <c r="L83" s="7" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
@@ -7728,27 +7799,27 @@
         <v>68</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
       <c r="J84" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="K84" s="2"/>
       <c r="L84" s="7" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="M84" s="2"/>
       <c r="N84" s="2"/>
@@ -7756,7 +7827,7 @@
       <c r="P84" s="2"/>
       <c r="Q84" s="2"/>
       <c r="R84" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="S84" s="2" t="s">
         <v>31</v>
@@ -7779,31 +7850,31 @@
         <v>68</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="F85" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>455</v>
       </c>
       <c r="G85" s="2"/>
       <c r="H85" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="I85" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="J85" s="2" t="s">
         <v>456</v>
-      </c>
-      <c r="I85" s="7" t="s">
-        <v>457</v>
-      </c>
-      <c r="J85" s="2" t="s">
-        <v>458</v>
       </c>
       <c r="K85" s="2"/>
       <c r="L85" s="7" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
@@ -7831,30 +7902,30 @@
     </row>
     <row r="86" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
       <c r="J86" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="K86" s="2"/>
       <c r="L86" s="7" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
@@ -7882,36 +7953,36 @@
     </row>
     <row r="87" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="G87" s="2"/>
       <c r="H87" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="I87" s="25" t="s">
+        <v>466</v>
+      </c>
+      <c r="J87" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="I87" s="25" t="s">
+      <c r="K87" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="J87" s="2" t="s">
+      <c r="L87" s="7" t="s">
         <v>469</v>
-      </c>
-      <c r="K87" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="L87" s="7" t="s">
-        <v>471</v>
       </c>
       <c r="M87" s="2"/>
       <c r="N87" s="2"/>
@@ -7939,30 +8010,30 @@
     </row>
     <row r="88" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
       <c r="I88" s="2"/>
       <c r="J88" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K88" s="2"/>
       <c r="L88" s="25" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="M88" s="2"/>
       <c r="N88" s="2"/>
@@ -7970,7 +8041,7 @@
       <c r="P88" s="2"/>
       <c r="Q88" s="2"/>
       <c r="R88" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="S88" s="2" t="s">
         <v>31</v>
@@ -7990,36 +8061,36 @@
     </row>
     <row r="89" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G89" s="2"/>
       <c r="H89" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="I89" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="J89" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="I89" s="7" t="s">
+      <c r="K89" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="J89" s="2" t="s">
+      <c r="L89" s="7" t="s">
         <v>481</v>
-      </c>
-      <c r="K89" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="L89" s="7" t="s">
-        <v>483</v>
       </c>
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
@@ -8047,14 +8118,14 @@
     </row>
     <row r="90" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>204</v>
@@ -8066,11 +8137,11 @@
       <c r="H90" s="2"/>
       <c r="I90" s="2"/>
       <c r="J90" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="K90" s="2"/>
       <c r="L90" s="7" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
@@ -8098,14 +8169,14 @@
     </row>
     <row r="91" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>204</v>
@@ -8117,13 +8188,13 @@
       <c r="H91" s="2"/>
       <c r="I91" s="2"/>
       <c r="J91" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="K91" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="L91" s="7" t="s">
         <v>490</v>
-      </c>
-      <c r="K91" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="L91" s="7" t="s">
-        <v>492</v>
       </c>
       <c r="M91" s="2"/>
       <c r="N91" s="2"/>
@@ -8151,30 +8222,30 @@
     </row>
     <row r="92" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="F92" s="2" t="s">
         <v>493</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>495</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
       <c r="I92" s="2"/>
       <c r="J92" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="K92" s="2"/>
       <c r="L92" s="7" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="M92" s="2"/>
       <c r="N92" s="2"/>
@@ -8202,32 +8273,32 @@
     </row>
     <row r="93" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>204</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
       <c r="I93" s="2"/>
       <c r="J93" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="K93" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="L93" s="7" t="s">
         <v>500</v>
-      </c>
-      <c r="K93" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="L93" s="7" t="s">
-        <v>502</v>
       </c>
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
@@ -8255,14 +8326,14 @@
     </row>
     <row r="94" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>204</v>
@@ -8277,10 +8348,10 @@
         <v>163</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="L94" s="7" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
@@ -8308,32 +8379,32 @@
     </row>
     <row r="95" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>204</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
       <c r="I95" s="2"/>
       <c r="J95" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="K95" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="L95" s="7" t="s">
         <v>507</v>
-      </c>
-      <c r="K95" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="L95" s="7" t="s">
-        <v>509</v>
       </c>
       <c r="M95" s="2"/>
       <c r="N95" s="2"/>
@@ -8341,7 +8412,7 @@
       <c r="P95" s="2"/>
       <c r="Q95" s="2"/>
       <c r="R95" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S95" s="2" t="s">
         <v>192</v>
@@ -8361,14 +8432,14 @@
     </row>
     <row r="96" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>204</v>
@@ -8380,13 +8451,13 @@
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
       <c r="J96" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="K96" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="L96" s="7" t="s">
         <v>512</v>
-      </c>
-      <c r="K96" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="L96" s="7" t="s">
-        <v>514</v>
       </c>
       <c r="M96" s="2"/>
       <c r="N96" s="2"/>
@@ -8394,7 +8465,7 @@
       <c r="P96" s="2"/>
       <c r="Q96" s="2"/>
       <c r="R96" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="S96" s="2" t="s">
         <v>192</v>
@@ -8412,16 +8483,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>204</v>
@@ -8433,13 +8504,13 @@
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
       <c r="J97" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="K97" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="L97" s="7" t="s">
         <v>517</v>
-      </c>
-      <c r="K97" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="L97" s="7" t="s">
-        <v>519</v>
       </c>
       <c r="M97" s="2"/>
       <c r="N97" s="2"/>
@@ -8465,16 +8536,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>26</v>
@@ -8486,13 +8557,13 @@
       <c r="H98" s="2"/>
       <c r="I98" s="2"/>
       <c r="J98" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="K98" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="L98" s="7" t="s">
         <v>523</v>
-      </c>
-      <c r="K98" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="L98" s="7" t="s">
-        <v>525</v>
       </c>
       <c r="M98" s="2"/>
       <c r="N98" s="2"/>
@@ -8518,16 +8589,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>26</v>
@@ -8539,13 +8610,13 @@
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
       <c r="J99" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="K99" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="L99" s="7" t="s">
         <v>527</v>
-      </c>
-      <c r="K99" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="L99" s="7" t="s">
-        <v>529</v>
       </c>
       <c r="M99" s="2"/>
       <c r="N99" s="2"/>
@@ -8571,34 +8642,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
       <c r="I100" s="2"/>
       <c r="J100" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="K100" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="L100" s="7" t="s">
         <v>532</v>
-      </c>
-      <c r="K100" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="L100" s="7" t="s">
-        <v>534</v>
       </c>
       <c r="M100" s="2"/>
       <c r="N100" s="2"/>
@@ -8624,12 +8695,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" s="2" t="s">
@@ -8639,19 +8710,19 @@
         <v>26</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
       <c r="J101" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="K101" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="L101" s="7" t="s">
         <v>536</v>
-      </c>
-      <c r="K101" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="L101" s="7" t="s">
-        <v>538</v>
       </c>
       <c r="M101" s="2"/>
       <c r="N101" s="2"/>
@@ -8659,7 +8730,7 @@
       <c r="P101" s="2"/>
       <c r="Q101" s="2"/>
       <c r="R101" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="S101" s="2" t="s">
         <v>31</v>
@@ -8677,36 +8748,35 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="F102" s="2" t="s">
         <v>540</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>542</v>
       </c>
       <c r="G102" s="2"/>
       <c r="H102" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="K102" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="I102" s="2"/>
-      <c r="J102" s="2" t="s">
+      <c r="L102" s="7" t="s">
         <v>544</v>
-      </c>
-      <c r="K102" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="L102" s="7" t="s">
-        <v>546</v>
       </c>
       <c r="M102" s="2"/>
       <c r="N102" s="2"/>
@@ -8732,36 +8802,40 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="G103" s="25" t="s">
+        <v>947</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="I103" s="25" t="s">
+        <v>948</v>
+      </c>
+      <c r="J103" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="E103" s="2" t="s">
+      <c r="K103" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="F103" s="2" t="s">
+      <c r="L103" s="7" t="s">
         <v>549</v>
-      </c>
-      <c r="G103" s="2"/>
-      <c r="H103" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="I103" s="2"/>
-      <c r="J103" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="K103" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="L103" s="7" t="s">
-        <v>553</v>
       </c>
       <c r="M103" s="2"/>
       <c r="N103" s="2"/>
@@ -8769,7 +8843,7 @@
       <c r="P103" s="2"/>
       <c r="Q103" s="2"/>
       <c r="R103" s="2" t="s">
-        <v>130</v>
+        <v>945</v>
       </c>
       <c r="S103" s="2" t="s">
         <v>31</v>
@@ -8786,17 +8860,20 @@
       <c r="W103" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="104" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="X103" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="104" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>71</v>
@@ -8808,11 +8885,11 @@
       <c r="H104" s="2"/>
       <c r="I104" s="2"/>
       <c r="J104" s="2" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="K104" s="2"/>
       <c r="L104" s="7" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="M104" s="2"/>
       <c r="N104" s="2"/>
@@ -8838,32 +8915,32 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" s="2" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>122</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
       <c r="I105" s="2"/>
       <c r="J105" s="2" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="K105" s="2"/>
       <c r="L105" s="7" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="M105" s="2"/>
       <c r="N105" s="2"/>
@@ -8877,7 +8954,7 @@
         <v>31</v>
       </c>
       <c r="T105" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="U105" s="5">
         <v>65</v>
@@ -8889,16 +8966,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" s="2" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>347</v>
@@ -8910,13 +8987,13 @@
       <c r="H106" s="2"/>
       <c r="I106" s="2"/>
       <c r="J106" s="2" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="L106" s="7" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="M106" s="2"/>
       <c r="N106" s="2"/>
@@ -8930,7 +9007,7 @@
         <v>31</v>
       </c>
       <c r="T106" s="5" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="U106" s="5">
         <v>78</v>
@@ -8942,16 +9019,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" s="2" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>369</v>
@@ -8963,13 +9040,13 @@
       <c r="H107" s="2"/>
       <c r="I107" s="2"/>
       <c r="J107" s="2" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="L107" s="7" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
@@ -8995,34 +9072,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" s="2" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
       <c r="I108" s="2"/>
       <c r="J108" s="2" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="L108" s="7" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="M108" s="2"/>
       <c r="N108" s="2"/>
@@ -9048,34 +9125,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" s="2" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
       <c r="I109" s="2"/>
       <c r="J109" s="2" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="L109" s="7" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="M109" s="2"/>
       <c r="N109" s="2"/>
@@ -9101,34 +9178,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" s="2" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>122</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="G110" s="2"/>
       <c r="H110" s="2" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="I110" s="2"/>
       <c r="J110" s="2" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="K110" s="2"/>
       <c r="L110" s="7" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="M110" s="2"/>
       <c r="N110" s="2"/>
@@ -9154,34 +9231,34 @@
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" s="2" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>122</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
       <c r="I111" s="2"/>
       <c r="J111" s="2" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="L111" s="7" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="M111" s="2"/>
       <c r="N111" s="2"/>
@@ -9207,16 +9284,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" s="2" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>369</v>
@@ -9228,13 +9305,13 @@
       <c r="H112" s="2"/>
       <c r="I112" s="2"/>
       <c r="J112" s="2" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L112" s="7" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="M112" s="2"/>
       <c r="N112" s="2"/>
@@ -9262,10 +9339,10 @@
     </row>
     <row r="113" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" s="2" t="s">
@@ -9275,21 +9352,21 @@
         <v>122</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="G113" s="2"/>
       <c r="H113" s="2" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="I113" s="2"/>
       <c r="J113" s="2" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="L113" s="7" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="M113" s="2"/>
       <c r="N113" s="2"/>
@@ -9317,36 +9394,36 @@
     </row>
     <row r="114" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="5" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="G114" s="2"/>
       <c r="H114" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="I114" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="J114" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="K114" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="L114" s="7" t="s">
         <v>606</v>
-      </c>
-      <c r="I114" s="7" t="s">
-        <v>607</v>
-      </c>
-      <c r="J114" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="K114" s="4" t="s">
-        <v>609</v>
-      </c>
-      <c r="L114" s="7" t="s">
-        <v>610</v>
       </c>
       <c r="M114" s="2"/>
       <c r="N114" s="2"/>
@@ -9374,14 +9451,14 @@
     </row>
     <row r="115" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="C115" s="8"/>
       <c r="D115" s="13" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="E115" s="8" t="s">
         <v>347</v>
@@ -9393,13 +9470,13 @@
       <c r="H115" s="8"/>
       <c r="I115" s="8"/>
       <c r="J115" s="8" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="K115" s="26" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="L115" s="25" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="M115" s="8"/>
       <c r="N115" s="8"/>
@@ -9430,11 +9507,11 @@
         <v>68</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="2" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>105</v>
@@ -9444,37 +9521,37 @@
       </c>
       <c r="G116" s="2"/>
       <c r="H116" s="2" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="I116" s="2"/>
       <c r="J116" s="2" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="K116" s="2"/>
       <c r="L116" s="27" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
       <c r="P116" s="2"/>
       <c r="Q116" s="2"/>
       <c r="R116" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S116" s="2" t="s">
         <v>31</v>
       </c>
       <c r="T116" s="5" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="U116" s="5" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="V116" s="5" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="W116" s="5">
         <v>1</v>
@@ -9485,11 +9562,11 @@
         <v>68</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" s="2" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>105</v>
@@ -9501,11 +9578,11 @@
       <c r="H117" s="2"/>
       <c r="I117" s="2"/>
       <c r="J117" s="2" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="K117" s="2"/>
       <c r="L117" s="27" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="M117" s="2"/>
       <c r="N117" s="2"/>
@@ -9516,16 +9593,16 @@
         <v>245</v>
       </c>
       <c r="S117" s="2" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="T117" s="5" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="U117" s="5" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="V117" s="5" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="W117" s="5">
         <v>1</v>
@@ -9536,27 +9613,27 @@
         <v>68</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" s="2" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>71</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
       <c r="I118" s="2"/>
       <c r="J118" s="2" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="K118" s="2"/>
       <c r="L118" s="27" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="M118" s="2"/>
       <c r="N118" s="2"/>
@@ -9570,13 +9647,13 @@
         <v>31</v>
       </c>
       <c r="T118" s="5" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="U118" s="5" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="V118" s="5" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="W118" s="5">
         <v>1</v>
@@ -9587,11 +9664,11 @@
         <v>68</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" s="2" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>105</v>
@@ -9601,15 +9678,15 @@
       </c>
       <c r="G119" s="2"/>
       <c r="H119" s="2" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="I119" s="2"/>
       <c r="J119" s="2" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="K119" s="2"/>
       <c r="L119" s="27" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="M119" s="2"/>
       <c r="N119" s="2"/>
@@ -9623,13 +9700,13 @@
         <v>31</v>
       </c>
       <c r="T119" s="5" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="U119" s="5" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="V119" s="5" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="W119" s="5">
         <v>1</v>
@@ -9640,11 +9717,11 @@
         <v>68</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" s="2" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>105</v>
@@ -9654,15 +9731,15 @@
       </c>
       <c r="G120" s="2"/>
       <c r="H120" s="2" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="I120" s="2"/>
       <c r="J120" s="2" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="K120" s="2"/>
       <c r="L120" s="27" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="M120" s="2"/>
       <c r="N120" s="2"/>
@@ -9673,16 +9750,16 @@
         <v>30</v>
       </c>
       <c r="S120" s="2" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="T120" s="5" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="U120" s="5" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="V120" s="5" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="W120" s="5">
         <v>1</v>
@@ -9693,11 +9770,11 @@
         <v>68</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" s="2" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>71</v>
@@ -9709,13 +9786,13 @@
       <c r="H121" s="2"/>
       <c r="I121" s="2"/>
       <c r="J121" s="2" t="s">
-        <v>926</v>
+        <v>914</v>
       </c>
       <c r="K121" s="2" t="s">
         <v>396</v>
       </c>
       <c r="L121" s="7" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="M121" s="2"/>
       <c r="N121" s="2"/>
@@ -9723,16 +9800,16 @@
       <c r="P121" s="2"/>
       <c r="Q121" s="2"/>
       <c r="R121" s="2" t="s">
-        <v>927</v>
+        <v>915</v>
       </c>
       <c r="S121" s="2" t="s">
         <v>62</v>
       </c>
       <c r="T121" s="5" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="U121" s="5" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="V121" s="5" t="s">
         <v>364</v>
@@ -9746,11 +9823,11 @@
         <v>68</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" s="2" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>105</v>
@@ -9760,15 +9837,15 @@
       </c>
       <c r="G122" s="2"/>
       <c r="H122" s="2" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="I122" s="2"/>
       <c r="J122" s="2" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="K122" s="2"/>
       <c r="L122" s="7" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="M122" s="2"/>
       <c r="N122" s="2"/>
@@ -9782,13 +9859,13 @@
         <v>31</v>
       </c>
       <c r="T122" s="5" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="U122" s="5" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="V122" s="5" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="W122" s="5">
         <v>1</v>
@@ -9799,11 +9876,11 @@
         <v>68</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" s="2" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>71</v>
@@ -9815,11 +9892,11 @@
       <c r="H123" s="2"/>
       <c r="I123" s="2"/>
       <c r="J123" s="2" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="K123" s="2"/>
       <c r="L123" s="7" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="M123" s="2"/>
       <c r="N123" s="2"/>
@@ -9839,7 +9916,7 @@
         <v>364</v>
       </c>
       <c r="V123" s="5" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="W123" s="5">
         <v>1</v>
@@ -9847,30 +9924,30 @@
     </row>
     <row r="124" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" s="2" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
       <c r="I124" s="2"/>
       <c r="J124" s="2" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="K124" s="2"/>
       <c r="L124" s="7" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="M124" s="2"/>
       <c r="N124" s="2"/>
@@ -9898,14 +9975,14 @@
     </row>
     <row r="125" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" s="2" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>105</v>
@@ -9915,15 +9992,15 @@
       </c>
       <c r="G125" s="2"/>
       <c r="H125" s="2" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="I125" s="2"/>
       <c r="J125" s="2" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="K125" s="2"/>
       <c r="L125" s="7" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="M125" s="2"/>
       <c r="N125" s="2"/>
@@ -9937,13 +10014,13 @@
         <v>31</v>
       </c>
       <c r="T125" s="5" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="U125" s="5" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="V125" s="5" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="W125" s="5">
         <v>3</v>
@@ -9951,10 +10028,10 @@
     </row>
     <row r="126" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" s="2" t="s">
@@ -9964,19 +10041,19 @@
         <v>26</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
       <c r="I126" s="2"/>
       <c r="J126" s="2" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="K126" s="2" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="L126" s="7" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="M126" s="2"/>
       <c r="N126" s="2"/>
@@ -10004,14 +10081,14 @@
     </row>
     <row r="127" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" s="2" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>26</v>
@@ -10021,17 +10098,17 @@
       </c>
       <c r="G127" s="2"/>
       <c r="H127" s="2" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="I127" s="2"/>
       <c r="J127" s="2" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="K127" s="2" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="L127" s="7" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="M127" s="2"/>
       <c r="N127" s="2"/>
@@ -10059,30 +10136,30 @@
     </row>
     <row r="128" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" s="5" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
       <c r="I128" s="2"/>
       <c r="J128" s="2" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="K128" s="2"/>
       <c r="L128" s="7" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="M128" s="2"/>
       <c r="N128" s="2"/>
@@ -10110,23 +10187,23 @@
     </row>
     <row r="129" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="28" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="B129" s="28" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="C129" s="28"/>
       <c r="D129" s="28" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="E129" s="28" t="s">
         <v>26</v>
       </c>
       <c r="F129" s="28" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="G129" s="29" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="H129" s="28"/>
       <c r="I129" s="28"/>
@@ -10135,7 +10212,7 @@
       </c>
       <c r="K129" s="28"/>
       <c r="L129" s="29" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="M129" s="28"/>
       <c r="N129" s="28"/>
@@ -10149,7 +10226,7 @@
         <v>261</v>
       </c>
       <c r="T129" s="5" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="U129" s="5">
         <v>120</v>
@@ -10163,34 +10240,34 @@
     </row>
     <row r="130" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="28" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="B130" s="28" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="C130" s="28"/>
       <c r="D130" s="28" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="E130" s="28" t="s">
         <v>26</v>
       </c>
       <c r="F130" s="28" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="G130" s="29" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="H130" s="28"/>
       <c r="I130" s="28"/>
       <c r="J130" s="28" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="K130" s="28" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="L130" s="29" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="M130" s="28"/>
       <c r="N130" s="28"/>
@@ -10218,32 +10295,32 @@
     </row>
     <row r="131" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="28" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="B131" s="28" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="C131" s="28"/>
       <c r="D131" s="28" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="E131" s="28" t="s">
         <v>26</v>
       </c>
       <c r="F131" s="28" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="G131" s="29" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="H131" s="28"/>
       <c r="I131" s="28"/>
       <c r="J131" s="28" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="K131" s="28"/>
       <c r="L131" s="29" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M131" s="28"/>
       <c r="N131" s="28"/>
@@ -10271,32 +10348,32 @@
     </row>
     <row r="132" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="28" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="B132" s="28" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="C132" s="28"/>
       <c r="D132" s="28" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="E132" s="28" t="s">
         <v>26</v>
       </c>
       <c r="F132" s="28" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="G132" s="29" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="H132" s="28"/>
       <c r="I132" s="28"/>
       <c r="J132" s="28" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="K132" s="28"/>
       <c r="L132" s="29" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="M132" s="28"/>
       <c r="N132" s="28"/>
@@ -10324,10 +10401,10 @@
     </row>
     <row r="133" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" s="2" t="s">
@@ -10337,19 +10414,19 @@
         <v>342</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
       <c r="I133" s="2"/>
       <c r="J133" s="2" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="K133" s="2" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="L133" s="7" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="M133" s="2"/>
       <c r="N133" s="2"/>
@@ -10377,32 +10454,32 @@
     </row>
     <row r="134" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" s="2" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>342</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
       <c r="I134" s="2"/>
       <c r="J134" s="2" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="K134" s="2" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="L134" s="7" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="M134" s="2"/>
       <c r="N134" s="2"/>
@@ -10430,14 +10507,14 @@
     </row>
     <row r="135" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" s="2" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>342</v>
@@ -10449,13 +10526,13 @@
       <c r="H135" s="2"/>
       <c r="I135" s="2"/>
       <c r="J135" s="2" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="K135" s="2" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="L135" s="7" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="M135" s="2"/>
       <c r="N135" s="2"/>
@@ -10483,14 +10560,14 @@
     </row>
     <row r="136" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>347</v>
@@ -10508,7 +10585,7 @@
         <v>207</v>
       </c>
       <c r="L136" s="7" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="M136" s="2"/>
       <c r="N136" s="2"/>
@@ -10536,32 +10613,32 @@
     </row>
     <row r="137" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" s="2" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>342</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
       <c r="I137" s="2"/>
       <c r="J137" s="2" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="K137" s="2" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="L137" s="7" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="M137" s="2"/>
       <c r="N137" s="2"/>
@@ -10589,20 +10666,20 @@
     </row>
     <row r="138" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" s="2" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>342</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
@@ -10614,7 +10691,7 @@
         <v>335</v>
       </c>
       <c r="L138" s="7" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="M138" s="2"/>
       <c r="N138" s="2"/>
@@ -10642,32 +10719,32 @@
     </row>
     <row r="139" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" s="2" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>342</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
       <c r="I139" s="2"/>
       <c r="J139" s="2" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="K139" s="2" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="L139" s="7" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="M139" s="2"/>
       <c r="N139" s="2"/>
@@ -10695,32 +10772,32 @@
     </row>
     <row r="140" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" s="2" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="G140" s="2"/>
       <c r="H140" s="2"/>
       <c r="I140" s="2"/>
       <c r="J140" s="2" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="K140" s="2" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="L140" s="7" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="M140" s="2"/>
       <c r="N140" s="2"/>
@@ -10748,32 +10825,32 @@
     </row>
     <row r="141" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="28" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B141" s="28" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="C141" s="28"/>
       <c r="D141" s="28" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="E141" s="28" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="F141" s="28" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="G141" s="28"/>
       <c r="H141" s="28"/>
       <c r="I141" s="28"/>
       <c r="J141" s="28" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="K141" s="28" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="L141" s="30" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="M141" s="28"/>
       <c r="N141" s="28"/>
@@ -10801,14 +10878,14 @@
     </row>
     <row r="142" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="28" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B142" s="28" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="C142" s="28"/>
       <c r="D142" s="28" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E142" s="28" t="s">
         <v>26</v>
@@ -10820,13 +10897,13 @@
       <c r="H142" s="28"/>
       <c r="I142" s="28"/>
       <c r="J142" s="28" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="K142" s="28" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="L142" s="30" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="M142" s="28"/>
       <c r="N142" s="28"/>
@@ -10854,50 +10931,46 @@
     </row>
     <row r="143" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="28" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B143" s="28" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="C143" s="28"/>
       <c r="D143" s="28" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="E143" s="28" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="F143" s="28" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="G143" s="28"/>
       <c r="H143" s="28"/>
       <c r="I143" s="28"/>
       <c r="J143" s="28" t="s">
-        <v>913</v>
+        <v>907</v>
       </c>
       <c r="K143" s="28" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="L143" s="30" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="M143" s="28"/>
       <c r="N143" s="28"/>
       <c r="O143" s="28"/>
       <c r="P143" s="28"/>
       <c r="Q143" s="28"/>
-      <c r="R143" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Monument avec ronde-bosse et bas-relief en bronze, conçu intégralement par l'artiste, sur un socle en marbre.</t>
-        </is>
-      </c>
-      <c r="S143" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bronze pour la ronde-bosse et le bas-relief, marbre pour le socle</t>
-        </is>
+      <c r="R143" s="28" t="s">
+        <v>918</v>
+      </c>
+      <c r="S143" s="28" t="s">
+        <v>919</v>
       </c>
       <c r="T143" s="5" t="s">
-        <v>916</v>
+        <v>908</v>
       </c>
       <c r="U143" s="5">
         <v>400</v>
@@ -10911,32 +10984,32 @@
     </row>
     <row r="144" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="28" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B144" s="28" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="C144" s="28"/>
       <c r="D144" s="28" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="E144" s="28" t="s">
         <v>26</v>
       </c>
       <c r="F144" s="28" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="G144" s="28"/>
       <c r="H144" s="28"/>
       <c r="I144" s="28"/>
       <c r="J144" s="28" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="K144" s="28" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="L144" s="30" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="M144" s="28"/>
       <c r="N144" s="28"/>
@@ -10964,20 +11037,20 @@
     </row>
     <row r="145" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="28" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B145" s="28" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="C145" s="28"/>
       <c r="D145" s="28" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="E145" s="28" t="s">
         <v>26</v>
       </c>
       <c r="F145" s="28" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="G145" s="28"/>
       <c r="H145" s="28"/>
@@ -10989,7 +11062,7 @@
         <v>181</v>
       </c>
       <c r="L145" s="30" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="M145" s="28"/>
       <c r="N145" s="28"/>
@@ -11017,32 +11090,32 @@
     </row>
     <row r="146" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="28" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B146" s="28" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="C146" s="28"/>
       <c r="D146" s="28" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="E146" s="28" t="s">
         <v>26</v>
       </c>
       <c r="F146" s="28" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="G146" s="28"/>
       <c r="H146" s="28"/>
       <c r="I146" s="28"/>
       <c r="J146" s="28" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="K146" s="28" t="s">
         <v>164</v>
       </c>
       <c r="L146" s="30" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="M146" s="28"/>
       <c r="N146" s="28"/>
@@ -11070,20 +11143,20 @@
     </row>
     <row r="147" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="C147" s="28"/>
       <c r="D147" s="2" t="s">
         <v>150</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
@@ -11093,7 +11166,7 @@
       </c>
       <c r="K147" s="2"/>
       <c r="L147" s="7" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="M147" s="2"/>
       <c r="N147" s="2"/>
@@ -11121,32 +11194,32 @@
     </row>
     <row r="148" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="C148" s="28"/>
       <c r="D148" s="2" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="E148" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="F148" s="2" t="s">
         <v>767</v>
-      </c>
-      <c r="F148" s="2" t="s">
-        <v>771</v>
       </c>
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
       <c r="I148" s="2"/>
       <c r="J148" s="2" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="K148" s="2" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="L148" s="7" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="M148" s="2"/>
       <c r="N148" s="2"/>
@@ -11174,32 +11247,32 @@
     </row>
     <row r="149" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="C149" s="28"/>
       <c r="D149" s="2" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="E149" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="F149" s="2" t="s">
         <v>767</v>
-      </c>
-      <c r="F149" s="2" t="s">
-        <v>771</v>
       </c>
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
       <c r="I149" s="2"/>
       <c r="J149" s="2" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="K149" s="2" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="L149" s="7" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="M149" s="2"/>
       <c r="N149" s="2"/>
@@ -11227,32 +11300,32 @@
     </row>
     <row r="150" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="C150" s="28"/>
       <c r="D150" s="2" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
       <c r="I150" s="7" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="J150" s="2" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="K150" s="2"/>
       <c r="L150" s="7" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="M150" s="2"/>
       <c r="N150" s="2"/>
@@ -11283,14 +11356,14 @@
         <v>94</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" s="2" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>300</v>
@@ -11299,11 +11372,11 @@
       <c r="H151" s="2"/>
       <c r="I151" s="2"/>
       <c r="J151" s="2" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="K151" s="2"/>
       <c r="L151" s="7" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="M151" s="2"/>
       <c r="N151" s="2"/>
@@ -11311,7 +11384,7 @@
       <c r="P151" s="2"/>
       <c r="Q151" s="2"/>
       <c r="R151" s="2" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="S151" s="2" t="s">
         <v>94</v>
@@ -11334,11 +11407,11 @@
         <v>94</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" s="2" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>71</v>
@@ -11350,11 +11423,11 @@
       <c r="H152" s="2"/>
       <c r="I152" s="2"/>
       <c r="J152" s="2" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="K152" s="2"/>
       <c r="L152" s="7" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="M152" s="2"/>
       <c r="N152" s="2"/>
@@ -11385,11 +11458,11 @@
         <v>94</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" s="2" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>71</v>
@@ -11401,11 +11474,11 @@
       <c r="H153" s="2"/>
       <c r="I153" s="2"/>
       <c r="J153" s="2" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="K153" s="2"/>
       <c r="L153" s="7" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="M153" s="2"/>
       <c r="N153" s="2"/>
@@ -11436,7 +11509,7 @@
         <v>94</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" s="2" t="s">
@@ -11452,11 +11525,11 @@
       <c r="H154" s="2"/>
       <c r="I154" s="2"/>
       <c r="J154" s="2" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="K154" s="2"/>
       <c r="L154" s="7" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="M154" s="2"/>
       <c r="N154" s="2"/>
@@ -11487,14 +11560,14 @@
         <v>94</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" s="2" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>211</v>
@@ -11503,11 +11576,11 @@
       <c r="H155" s="2"/>
       <c r="I155" s="2"/>
       <c r="J155" s="2" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="K155" s="2"/>
       <c r="L155" s="7" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="M155" s="2"/>
       <c r="N155" s="2"/>
@@ -11538,29 +11611,29 @@
         <v>94</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" s="2" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
       <c r="I156" s="2"/>
       <c r="J156" s="2" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="K156" s="2" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="L156" s="7" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="M156" s="2"/>
       <c r="N156" s="2"/>
@@ -11591,29 +11664,29 @@
         <v>94</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" s="2" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
       <c r="I157" s="2"/>
       <c r="J157" s="2" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="K157" s="2" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="L157" s="7" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="M157" s="2"/>
       <c r="N157" s="2"/>
@@ -11644,7 +11717,7 @@
         <v>94</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" s="2" t="s">
@@ -11660,11 +11733,11 @@
       <c r="H158" s="2"/>
       <c r="I158" s="2"/>
       <c r="J158" s="2" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="K158" s="2"/>
       <c r="L158" s="7" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="M158" s="2"/>
       <c r="N158" s="2"/>
@@ -11692,30 +11765,30 @@
     </row>
     <row r="159" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" s="2" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>422</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
       <c r="I159" s="2"/>
       <c r="J159" s="2" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="K159" s="2"/>
       <c r="L159" s="7" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="M159" s="2"/>
       <c r="N159" s="2"/>
@@ -11743,30 +11816,30 @@
     </row>
     <row r="160" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" s="2" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>422</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
       <c r="I160" s="2"/>
       <c r="J160" s="2" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="K160" s="2"/>
       <c r="L160" s="7" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="M160" s="2"/>
       <c r="N160" s="2"/>
@@ -11774,7 +11847,7 @@
       <c r="P160" s="2"/>
       <c r="Q160" s="2"/>
       <c r="R160" s="2" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="S160" s="2" t="s">
         <v>62</v>
@@ -11794,10 +11867,10 @@
     </row>
     <row r="161" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" s="2" t="s">
@@ -11813,11 +11886,11 @@
       <c r="H161" s="2"/>
       <c r="I161" s="2"/>
       <c r="J161" s="2" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="K161" s="2"/>
       <c r="L161" s="7" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="M161" s="2"/>
       <c r="N161" s="2"/>
@@ -11825,7 +11898,7 @@
       <c r="P161" s="2"/>
       <c r="Q161" s="2"/>
       <c r="R161" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="S161" s="2" t="s">
         <v>31</v>
@@ -11845,14 +11918,14 @@
     </row>
     <row r="162" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" s="2" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>422</v>
@@ -11864,11 +11937,11 @@
       <c r="H162" s="2"/>
       <c r="I162" s="2"/>
       <c r="J162" s="2" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="K162" s="2"/>
       <c r="L162" s="7" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="M162" s="2"/>
       <c r="N162" s="2"/>
@@ -11876,7 +11949,7 @@
       <c r="P162" s="2"/>
       <c r="Q162" s="2"/>
       <c r="R162" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="S162" s="2" t="s">
         <v>31</v>
@@ -11896,30 +11969,30 @@
     </row>
     <row r="163" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" s="2" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>422</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
       <c r="I163" s="2"/>
       <c r="J163" s="2" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="K163" s="2"/>
       <c r="L163" s="7" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="M163" s="2"/>
       <c r="N163" s="2"/>
@@ -11947,30 +12020,30 @@
     </row>
     <row r="164" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" s="2" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
       <c r="I164" s="2"/>
       <c r="J164" s="2" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="K164" s="2"/>
       <c r="L164" s="7" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="M164" s="2"/>
       <c r="N164" s="2"/>
@@ -11998,10 +12071,10 @@
     </row>
     <row r="165" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" s="2" t="s">
@@ -12011,17 +12084,17 @@
         <v>26</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
       <c r="I165" s="2"/>
       <c r="J165" s="2" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="K165" s="2"/>
       <c r="L165" s="7" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="M165" s="2"/>
       <c r="N165" s="2"/>
@@ -12049,36 +12122,36 @@
     </row>
     <row r="166" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="B166" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="C166" s="2" t="s">
         <v>835</v>
       </c>
-      <c r="C166" s="2" t="s">
-        <v>839</v>
-      </c>
       <c r="D166" s="2" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="G166" s="2"/>
       <c r="H166" s="2" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="I166" s="2"/>
       <c r="J166" s="2" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="K166" s="2" t="s">
         <v>164</v>
       </c>
       <c r="L166" s="7" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="M166" s="2"/>
       <c r="N166" s="2"/>
@@ -12106,39 +12179,39 @@
     </row>
     <row r="167" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="B167" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="C167" s="2" t="s">
         <v>835</v>
       </c>
-      <c r="C167" s="2" t="s">
-        <v>839</v>
-      </c>
       <c r="D167" s="2" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="G167" s="2"/>
       <c r="H167" s="2" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="I167" s="2"/>
       <c r="J167" s="2" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="K167" s="2" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="L167" s="7" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="M167" s="2" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -12165,16 +12238,16 @@
     </row>
     <row r="168" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="B168" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="C168" s="2" t="s">
         <v>835</v>
       </c>
-      <c r="C168" s="2" t="s">
-        <v>839</v>
-      </c>
       <c r="D168" s="2" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>26</v>
@@ -12184,17 +12257,17 @@
       </c>
       <c r="G168" s="2"/>
       <c r="H168" s="2" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="I168" s="2"/>
       <c r="J168" s="2" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="K168" s="2" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="L168" s="7" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="M168" s="2"/>
       <c r="N168" s="2"/>
@@ -12222,52 +12295,46 @@
     </row>
     <row r="169" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="C169" s="2"/>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1608</t>
-        </is>
+      <c r="D169" s="2" t="s">
+        <v>920</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>122</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
       <c r="I169" s="2"/>
       <c r="J169" s="2" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="K169" s="2" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="L169" s="7" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="M169" s="2"/>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
       <c r="P169" s="2"/>
       <c r="Q169" s="2"/>
-      <c r="R169" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Monument avec ronde-bosse et bas-relief en bronze, imaginé par Jean Bologne et réalisé intégralement par son élève, Pietro Tacca, sur un socle en marbre.</t>
-        </is>
-      </c>
-      <c r="S169" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bronze pour la statue et le bas-relief, marbre pour le socle</t>
-        </is>
+      <c r="R169" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="S169" s="2" t="s">
+        <v>922</v>
       </c>
       <c r="T169" s="5" t="s">
-        <v>912</v>
+        <v>906</v>
       </c>
       <c r="U169" s="5">
         <v>380</v>
@@ -12279,37 +12346,37 @@
         <v>2</v>
       </c>
       <c r="X169" s="5" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
     </row>
     <row r="170" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
       <c r="I170" s="2"/>
       <c r="J170" s="2" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="K170" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="L170" s="7" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="M170" s="2"/>
       <c r="N170" s="2"/>
@@ -12317,13 +12384,13 @@
       <c r="P170" s="2"/>
       <c r="Q170" s="2"/>
       <c r="R170" s="2" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="S170" s="2" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="T170" s="5" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="U170" s="5">
         <v>350</v>
@@ -12337,50 +12404,46 @@
     </row>
     <row r="171" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" s="2" t="s">
         <v>63</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="G171" s="2"/>
       <c r="H171" s="2"/>
       <c r="I171" s="2"/>
       <c r="J171" s="2" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="K171" s="2" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="L171" s="7" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="M171" s="2"/>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
       <c r="P171" s="2"/>
       <c r="Q171" s="2"/>
-      <c r="R171" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Monument avec ronde-bosse en bronze, l'artiste n'a conçu que la ronde-bosse. Le socle fontaine en granite et marbre date du 19e siècle.</t>
-        </is>
-      </c>
-      <c r="S171" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bronze pour la ronde-bosse, granite et marbre pour le socle</t>
-        </is>
+      <c r="R171" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="S171" s="2" t="s">
+        <v>924</v>
       </c>
       <c r="T171" s="5" t="s">
-        <v>919</v>
+        <v>909</v>
       </c>
       <c r="U171" s="5">
         <v>400</v>
@@ -12394,32 +12457,36 @@
     </row>
     <row r="172" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>122</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>874</v>
-      </c>
-      <c r="G172" s="2"/>
+        <v>870</v>
+      </c>
+      <c r="G172" s="25" t="s">
+        <v>934</v>
+      </c>
       <c r="H172" s="2"/>
-      <c r="I172" s="2"/>
+      <c r="I172" s="25" t="s">
+        <v>933</v>
+      </c>
       <c r="J172" s="2" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="K172" s="2" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="L172" s="7" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="M172" s="2"/>
       <c r="N172" s="2"/>
@@ -12433,7 +12500,7 @@
         <v>62</v>
       </c>
       <c r="T172" s="5" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="U172" s="5">
         <v>140</v>
@@ -12447,32 +12514,36 @@
     </row>
     <row r="173" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>122</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>857</v>
-      </c>
-      <c r="G173" s="2"/>
+        <v>853</v>
+      </c>
+      <c r="G173" s="25" t="s">
+        <v>937</v>
+      </c>
       <c r="H173" s="2"/>
-      <c r="I173" s="2"/>
+      <c r="I173" s="7" t="s">
+        <v>877</v>
+      </c>
       <c r="J173" s="2" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="K173" s="2" t="s">
-        <v>880</v>
-      </c>
-      <c r="L173" s="7" t="s">
-        <v>881</v>
+        <v>876</v>
+      </c>
+      <c r="L173" s="25" t="s">
+        <v>936</v>
       </c>
       <c r="M173" s="2"/>
       <c r="N173" s="2"/>
@@ -12480,13 +12551,13 @@
       <c r="P173" s="2"/>
       <c r="Q173" s="2"/>
       <c r="R173" s="2" t="s">
-        <v>130</v>
+        <v>935</v>
       </c>
       <c r="S173" s="2" t="s">
         <v>62</v>
       </c>
       <c r="T173" s="5" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="U173" s="5">
         <v>150</v>
@@ -12500,32 +12571,32 @@
     </row>
     <row r="174" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" s="2" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
       <c r="I174" s="2"/>
       <c r="J174" s="2" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="K174" s="2" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="L174" s="7" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="M174" s="2"/>
       <c r="N174" s="2"/>
@@ -12533,10 +12604,10 @@
       <c r="P174" s="2"/>
       <c r="Q174" s="2"/>
       <c r="R174" s="2" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="S174" s="2" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="T174" s="5">
         <v>85</v>
@@ -12553,14 +12624,14 @@
     </row>
     <row r="175" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="10" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="B175" s="10" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C175" s="10"/>
       <c r="D175" s="14" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="E175" s="10" t="s">
         <v>105</v>
@@ -12570,15 +12641,15 @@
       </c>
       <c r="G175" s="10"/>
       <c r="H175" s="10" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="I175" s="10"/>
       <c r="J175" s="10" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="K175" s="10"/>
       <c r="L175" s="11" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="M175" s="10"/>
       <c r="N175" s="10"/>
@@ -12589,7 +12660,7 @@
         <v>420</v>
       </c>
       <c r="S175" s="10" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="T175" s="23">
         <v>240</v>
@@ -12606,14 +12677,14 @@
     </row>
     <row r="176" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" s="2" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>105</v>
@@ -12623,15 +12694,15 @@
       </c>
       <c r="G176" s="2"/>
       <c r="H176" s="2" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="I176" s="2"/>
       <c r="J176" s="2" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="K176" s="2"/>
       <c r="L176" s="25" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="M176" s="2"/>
       <c r="N176" s="2"/>
@@ -12642,7 +12713,7 @@
         <v>420</v>
       </c>
       <c r="S176" s="2" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="T176" s="2">
         <v>200</v>
@@ -12659,14 +12730,14 @@
     </row>
     <row r="177" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" s="2" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>105</v>
@@ -12676,15 +12747,15 @@
       </c>
       <c r="G177" s="2"/>
       <c r="H177" s="2" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="I177" s="2"/>
       <c r="J177" s="2" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="K177" s="2"/>
       <c r="L177" s="25" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="M177" s="2"/>
       <c r="N177" s="2"/>
@@ -12712,14 +12783,14 @@
     </row>
     <row r="178" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" s="2" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>105</v>
@@ -12729,15 +12800,15 @@
       </c>
       <c r="G178" s="2"/>
       <c r="H178" s="2" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="I178" s="2"/>
       <c r="J178" s="2" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="K178" s="2"/>
       <c r="L178" s="25" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="M178" s="2"/>
       <c r="N178" s="2"/>
@@ -12846,118 +12917,130 @@
     <hyperlink ref="L75" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
     <hyperlink ref="L76" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
     <hyperlink ref="L77" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="L78" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="L79" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="L80" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="L81" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="L82" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="L83" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="L84" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="I85" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="L85" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="L86" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="I87" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="L87" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="L88" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="I89" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="L89" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="L90" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="L91" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="L92" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="L93" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="L94" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="L95" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="L96" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="L97" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="L98" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="L99" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="L100" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="L101" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="L102" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="L103" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="L104" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="L105" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="L106" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="L107" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="L108" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="L109" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="L110" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="L111" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="L112" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="L113" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="I114" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="L114" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="L115" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="L116" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="L117" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="L118" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="L119" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="L120" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="L121" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="L122" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="L123" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="L124" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="L125" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="L126" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="L127" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="L128" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="G129" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="L129" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="G130" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="L130" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="G131" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="L131" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="G132" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="L132" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="L133" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="L134" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="L135" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="L136" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="L137" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="L138" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="L139" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="L140" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="L141" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="L142" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="L143" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="L144" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="L145" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="L146" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="L147" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="L148" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="L149" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="I150" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="L150" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="L151" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="L152" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="L153" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="L154" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="L155" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="L156" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="L157" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="L158" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="L159" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="L160" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="L161" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="L162" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="L163" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="L164" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="L165" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="L166" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="L167" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="L168" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="L169" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="L170" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="L171" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="L172" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="L173" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="L174" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="L175" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="L176" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="L177" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="L178" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="G73" r:id="rId192" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV_-_Apr%C3%A8s_r%C3%A9fection_des_murets_01.jpg/1280px-Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV_-_Apr%C3%A8s_r%C3%A9fection_des_murets_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{22828DEA-EBCC-4B8A-A415-6877B7018EDC}"/>
-    <hyperlink ref="I73" r:id="rId193" xr:uid="{A4A34E13-DEE9-4B28-BBA5-7FF5B17F77B1}"/>
+    <hyperlink ref="L79" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="L80" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="L81" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="L82" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="L83" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="L84" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="I85" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="L85" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="L86" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="I87" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="L87" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="L88" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="I89" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="L89" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="L90" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="L91" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="L92" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="L93" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="L94" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="L95" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="L96" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="L97" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="L98" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="L99" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="L100" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="L101" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="L102" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="L103" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="L104" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="L105" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="L106" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="L107" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="L108" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="L109" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="L110" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="L111" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="L112" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="L113" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="I114" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="L114" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="L115" r:id="rId122" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="L116" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="L117" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="L118" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="L119" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="L120" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="L121" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="L122" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="L123" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="L124" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="L125" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="L126" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="L127" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="L128" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="G129" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="L129" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="G130" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="L130" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="G131" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="L131" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="G132" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="L132" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="L133" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="L134" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="L135" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="L136" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="L137" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="L138" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="L139" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="L140" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="L141" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="L142" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="L143" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="L144" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="L145" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="L146" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="L147" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="L148" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="L149" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="I150" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="L150" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="L151" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="L152" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="L153" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="L154" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="L155" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="L156" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="L157" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="L158" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="L159" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="L160" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="L161" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="L162" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="L163" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="L164" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="L165" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="L166" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="L167" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="L168" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="L169" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="L170" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="L171" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="L172" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="I173" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="L174" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="L175" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="L176" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="L177" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="L178" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="G73" r:id="rId191" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV_-_Apr%C3%A8s_r%C3%A9fection_des_murets_01.jpg/1280px-Lyon_2e_-_Place_Bellecour_-_Statue_%C3%A9questre_de_Louis_XIV_-_Apr%C3%A8s_r%C3%A9fection_des_murets_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{22828DEA-EBCC-4B8A-A415-6877B7018EDC}"/>
+    <hyperlink ref="I73" r:id="rId192" xr:uid="{A4A34E13-DEE9-4B28-BBA5-7FF5B17F77B1}"/>
+    <hyperlink ref="L78" r:id="rId193" xr:uid="{7BF35C1B-B7E6-4045-BFAB-F71E87FB2644}"/>
+    <hyperlink ref="G78" r:id="rId194" xr:uid="{D6863217-6E77-400A-BB7F-344268AFB74C}"/>
+    <hyperlink ref="I78" r:id="rId195" xr:uid="{EB427032-FF13-4E55-AEC3-E11BC4848245}"/>
+    <hyperlink ref="I172" r:id="rId196" xr:uid="{2220F8E5-5A03-48BF-B003-8F1388AC2E1E}"/>
+    <hyperlink ref="G172" r:id="rId197" xr:uid="{F5F77249-C0D1-4A4E-914C-BCBB6A4F2576}"/>
+    <hyperlink ref="L173" r:id="rId198" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/79/Ferdinando_Tacca%2C_fontana_dei_mostri_marini%2C_dx%2C_12.JPG/1280px-Ferdinando_Tacca%2C_fontana_dei_mostri_marini%2C_dx%2C_12.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DC2CA6E2-E0A3-4B34-997B-727B5408F84F}"/>
+    <hyperlink ref="G173" r:id="rId199" xr:uid="{DA60B939-F274-4298-B8DE-B18328E4BFF0}"/>
+    <hyperlink ref="G23" r:id="rId200" xr:uid="{6EA40FED-CF7A-428C-BFD5-072012954873}"/>
+    <hyperlink ref="I23" r:id="rId201" xr:uid="{BADCAF9A-4E1C-414A-8A70-BE2AD746A439}"/>
+    <hyperlink ref="I25" r:id="rId202" xr:uid="{FFE9AB7A-BE54-419F-B879-89D334E128C0}"/>
+    <hyperlink ref="G25" r:id="rId203" xr:uid="{2CBFEF7B-00A6-421C-8982-068DC03B242A}"/>
+    <hyperlink ref="G103" r:id="rId204" xr:uid="{9432C2E3-4F5D-4745-B442-B1D101717D8D}"/>
+    <hyperlink ref="I103" r:id="rId205" xr:uid="{463AAD48-98EA-4FAA-B042-B8EF4F5B0BAB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-17e.xlsx
+++ b/quizzes/sculpture-17e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E959CF4-40DD-4BBD-978B-3FA17CD2312E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9799D512-04F2-4B13-AB13-9016807FBF15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1863" uniqueCount="980">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1863" uniqueCount="979">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -2810,9 +2810,6 @@
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/58/Carrara%2C_duomo%2C_interno%2C_altare_dell%27annunziata%2C_crocifisso_in_gesso_attr._a_pietro_tacca_01.jpg/960px-Carrara%2C_duomo%2C_interno%2C_altare_dell%27annunziata%2C_crocifisso_in_gesso_attr._a_pietro_tacca_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
-  </si>
-  <si>
-    <t>Objet liturgique</t>
   </si>
   <si>
     <t>Plâtre peint</t>
@@ -9668,11 +9665,11 @@
         <v>107</v>
       </c>
       <c r="G117" s="25" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H117" s="2"/>
       <c r="I117" s="25" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>645</v>
@@ -12135,7 +12132,7 @@
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
       <c r="I164" s="25" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="J164" s="2" t="s">
         <v>783</v>
@@ -12186,11 +12183,11 @@
         <v>863</v>
       </c>
       <c r="G165" s="25" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H165" s="2"/>
       <c r="I165" s="25" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>864</v>
@@ -12413,7 +12410,7 @@
         <v>885</v>
       </c>
       <c r="G169" s="25" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H169" s="2"/>
       <c r="I169" s="7" t="s">
@@ -12426,7 +12423,7 @@
         <v>887</v>
       </c>
       <c r="L169" s="25" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="M169" s="2"/>
       <c r="N169" s="2"/>
@@ -12525,11 +12522,11 @@
         <v>902</v>
       </c>
       <c r="G171" s="25" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H171" s="2"/>
       <c r="I171" s="25" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="J171" s="2" t="s">
         <v>903</v>
@@ -12713,10 +12710,10 @@
       <c r="P174" s="2"/>
       <c r="Q174" s="2"/>
       <c r="R174" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="S174" s="2" t="s">
         <v>930</v>
-      </c>
-      <c r="S174" s="2" t="s">
-        <v>931</v>
       </c>
       <c r="T174" s="5">
         <v>85</v>
@@ -12733,14 +12730,14 @@
     </row>
     <row r="175" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="10" t="s">
+        <v>931</v>
+      </c>
+      <c r="B175" s="10" t="s">
         <v>932</v>
-      </c>
-      <c r="B175" s="10" t="s">
-        <v>933</v>
       </c>
       <c r="C175" s="10"/>
       <c r="D175" s="14" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="E175" s="10" t="s">
         <v>106</v>
@@ -12749,20 +12746,20 @@
         <v>107</v>
       </c>
       <c r="G175" s="25" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H175" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="I175" s="25" t="s">
+        <v>960</v>
+      </c>
+      <c r="J175" s="10" t="s">
         <v>935</v>
-      </c>
-      <c r="I175" s="25" t="s">
-        <v>961</v>
-      </c>
-      <c r="J175" s="10" t="s">
-        <v>936</v>
       </c>
       <c r="K175" s="10"/>
       <c r="L175" s="11" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="M175" s="10"/>
       <c r="N175" s="10"/>
@@ -12790,14 +12787,14 @@
     </row>
     <row r="176" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="B176" s="2" t="s">
         <v>932</v>
-      </c>
-      <c r="B176" s="2" t="s">
-        <v>933</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>106</v>
@@ -12806,20 +12803,20 @@
         <v>107</v>
       </c>
       <c r="G176" s="25" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H176" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="I176" s="25" t="s">
+        <v>966</v>
+      </c>
+      <c r="J176" s="2" t="s">
         <v>939</v>
-      </c>
-      <c r="I176" s="25" t="s">
-        <v>967</v>
-      </c>
-      <c r="J176" s="2" t="s">
-        <v>940</v>
       </c>
       <c r="K176" s="2"/>
       <c r="L176" s="25" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="M176" s="2"/>
       <c r="N176" s="2"/>
@@ -12847,14 +12844,14 @@
     </row>
     <row r="177" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="B177" s="2" t="s">
         <v>932</v>
-      </c>
-      <c r="B177" s="2" t="s">
-        <v>933</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" s="2" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>106</v>
@@ -12863,20 +12860,20 @@
         <v>107</v>
       </c>
       <c r="G177" s="25" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H177" s="8" t="s">
+        <v>942</v>
+      </c>
+      <c r="I177" s="25" t="s">
+        <v>975</v>
+      </c>
+      <c r="J177" s="2" t="s">
         <v>943</v>
-      </c>
-      <c r="I177" s="25" t="s">
-        <v>976</v>
-      </c>
-      <c r="J177" s="2" t="s">
-        <v>944</v>
       </c>
       <c r="K177" s="2"/>
       <c r="L177" s="25" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="M177" s="2"/>
       <c r="N177" s="2"/>
@@ -12904,10 +12901,10 @@
     </row>
     <row r="178" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="B178" s="2" t="s">
         <v>932</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>933</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" s="2" t="s">
@@ -12921,15 +12918,15 @@
       </c>
       <c r="G178" s="2"/>
       <c r="H178" s="2" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="I178" s="2"/>
       <c r="J178" s="2" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="K178" s="2"/>
       <c r="L178" s="25" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="M178" s="2"/>
       <c r="N178" s="2"/>
@@ -12964,32 +12961,32 @@
       </c>
       <c r="C179" s="2"/>
       <c r="D179" s="2" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="G179" s="15" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H179" s="2"/>
       <c r="I179" s="15" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="J179" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="K179" s="2" t="s">
         <v>951</v>
       </c>
-      <c r="K179" s="2" t="s">
+      <c r="L179" s="25" t="s">
         <v>952</v>
       </c>
-      <c r="L179" s="25" t="s">
+      <c r="R179" s="2" t="s">
         <v>953</v>
-      </c>
-      <c r="R179" s="2" t="s">
-        <v>954</v>
       </c>
       <c r="S179" s="2" t="s">
         <v>134</v>
@@ -13009,10 +13006,10 @@
     </row>
     <row r="180" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="B180" s="2" t="s">
         <v>955</v>
-      </c>
-      <c r="B180" s="2" t="s">
-        <v>956</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" s="2" t="s">
@@ -13025,24 +13022,24 @@
         <v>107</v>
       </c>
       <c r="G180" s="15" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H180" s="2"/>
       <c r="I180" s="15" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="J180" s="2" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="K180" s="2"/>
       <c r="L180" s="25" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="R180" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="S180" s="2" t="s">
         <v>959</v>
-      </c>
-      <c r="S180" s="2" t="s">
-        <v>960</v>
       </c>
       <c r="T180" s="2">
         <v>204</v>

--- a/quizzes/sculpture-17e.xlsx
+++ b/quizzes/sculpture-17e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9799D512-04F2-4B13-AB13-9016807FBF15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D6B354-0AD4-4EEC-A8E4-E22A8F2F33B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1863" uniqueCount="979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="981">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -2944,9 +2944,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Monumento_equestre_a_ferdinando_I_02.JPG/960px-Monumento_equestre_a_ferdinando_I_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fe/Giambologna_e_Pietro_Tacca%2C_Statua_equestre_di_Ferdinando_I_de%27_Medici%2C_1602-07%2C_01.JPG/960px-Giambologna_e_Pietro_Tacca%2C_Statua_equestre_di_Ferdinando_I_de%27_Medici%2C_1602-07%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e8/Versailles_2014.jpg/1280px-Versailles_2014.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=de</t>
   </si>
   <si>
@@ -2957,6 +2954,15 @@
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/24/Bain_des_Nymphes_-_Ch%C3%A2teau_de_Versailles_-_P1050589-P1050594.jpg/1280px-Bain_des_Nymphes_-_Ch%C3%A2teau_de_Versailles_-_P1050589-P1050594.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f9/033032598_-_Piacenza_Statue_Equestri_Farnesiane.jpg/1280px-033032598_-_Piacenza_Statue_Equestri_Farnesiane.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f2/%22_Un_cavallo_del_Mochi_%22.jpg/960px-%22_Un_cavallo_del_Mochi_%22.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/37/Piazza_SS_Annunziata_Firenze_Apr_2008.jpg/1280px-Piazza_SS_Annunziata_Firenze_Apr_2008.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -9665,11 +9671,11 @@
         <v>107</v>
       </c>
       <c r="G117" s="25" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H117" s="2"/>
       <c r="I117" s="25" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>645</v>
@@ -10989,7 +10995,6 @@
       </c>
       <c r="G142" s="28"/>
       <c r="H142" s="28"/>
-      <c r="I142" s="28"/>
       <c r="J142" s="28" t="s">
         <v>769</v>
       </c>
@@ -11040,17 +11045,21 @@
       <c r="F143" s="28" t="s">
         <v>774</v>
       </c>
-      <c r="G143" s="28"/>
+      <c r="G143" s="25" t="s">
+        <v>979</v>
+      </c>
       <c r="H143" s="28"/>
-      <c r="I143" s="28"/>
+      <c r="I143" s="30" t="s">
+        <v>777</v>
+      </c>
       <c r="J143" s="28" t="s">
         <v>775</v>
       </c>
       <c r="K143" s="28" t="s">
         <v>776</v>
       </c>
-      <c r="L143" s="30" t="s">
-        <v>777</v>
+      <c r="L143" s="25" t="s">
+        <v>978</v>
       </c>
       <c r="M143" s="28"/>
       <c r="N143" s="28"/>
@@ -12410,7 +12419,7 @@
         <v>885</v>
       </c>
       <c r="G169" s="25" t="s">
-        <v>974</v>
+        <v>980</v>
       </c>
       <c r="H169" s="2"/>
       <c r="I169" s="7" t="s">
@@ -12860,13 +12869,13 @@
         <v>107</v>
       </c>
       <c r="G177" s="25" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H177" s="8" t="s">
         <v>942</v>
       </c>
       <c r="I177" s="25" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="J177" s="2" t="s">
         <v>943</v>
@@ -13216,7 +13225,7 @@
     <hyperlink ref="L140" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
     <hyperlink ref="L141" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
     <hyperlink ref="L142" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="L143" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="I143" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
     <hyperlink ref="L144" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
     <hyperlink ref="L145" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
     <hyperlink ref="L146" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
@@ -13273,11 +13282,13 @@
     <hyperlink ref="G165" r:id="rId219" xr:uid="{447ABB97-9C6F-4F2E-BC06-5A7B781E37B9}"/>
     <hyperlink ref="I165" r:id="rId220" xr:uid="{0FC493CC-32A3-4D65-BAD9-5F24A451ED3F}"/>
     <hyperlink ref="L169" r:id="rId221" xr:uid="{FA24E464-D5E2-4A13-8C8A-18DBFD625A34}"/>
-    <hyperlink ref="G169" r:id="rId222" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fe/Giambologna_e_Pietro_Tacca%2C_Statua_equestre_di_Ferdinando_I_de%27_Medici%2C_1602-07%2C_01.JPG/960px-Giambologna_e_Pietro_Tacca%2C_Statua_equestre_di_Ferdinando_I_de%27_Medici%2C_1602-07%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F852EC73-9644-47C5-B7C1-41175CA3CF35}"/>
-    <hyperlink ref="I177" r:id="rId223" xr:uid="{0DF002DB-E208-44E1-BA86-CBDB031A544D}"/>
-    <hyperlink ref="G177" r:id="rId224" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3d/Versailles_-_panoramio_-_Patrick_Nouhailler%27s%E2%80%A6_%2866%29.jpg/1280px-Versailles_-_panoramio_-_Patrick_Nouhailler%27s%E2%80%A6_%2866%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9E80C09B-BCD2-4C81-908A-08494CFD4E5A}"/>
-    <hyperlink ref="I117" r:id="rId225" xr:uid="{854BD5A0-A1B1-4398-A5F9-20CD5F69D6B8}"/>
-    <hyperlink ref="G117" r:id="rId226" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/24/Bain_des_Nymphes_-_Ch%C3%A2teau_de_Versailles_-_P1050589-P1050594.jpg/1280px-Bain_des_Nymphes_-_Ch%C3%A2teau_de_Versailles_-_P1050589-P1050594.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5582FA22-80A3-4361-855A-DBA8DB99F65D}"/>
+    <hyperlink ref="I177" r:id="rId222" xr:uid="{0DF002DB-E208-44E1-BA86-CBDB031A544D}"/>
+    <hyperlink ref="G177" r:id="rId223" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3d/Versailles_-_panoramio_-_Patrick_Nouhailler%27s%E2%80%A6_%2866%29.jpg/1280px-Versailles_-_panoramio_-_Patrick_Nouhailler%27s%E2%80%A6_%2866%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9E80C09B-BCD2-4C81-908A-08494CFD4E5A}"/>
+    <hyperlink ref="I117" r:id="rId224" xr:uid="{854BD5A0-A1B1-4398-A5F9-20CD5F69D6B8}"/>
+    <hyperlink ref="G117" r:id="rId225" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/24/Bain_des_Nymphes_-_Ch%C3%A2teau_de_Versailles_-_P1050589-P1050594.jpg/1280px-Bain_des_Nymphes_-_Ch%C3%A2teau_de_Versailles_-_P1050589-P1050594.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5582FA22-80A3-4361-855A-DBA8DB99F65D}"/>
+    <hyperlink ref="L143" r:id="rId226" xr:uid="{0D537F89-5B9E-43EF-A01B-DD9745C81851}"/>
+    <hyperlink ref="G143" r:id="rId227" xr:uid="{EFAE1AE3-FD24-4F52-B4D3-ACF1021D9576}"/>
+    <hyperlink ref="G169" r:id="rId228" xr:uid="{041EE9DF-84EF-419A-ABDC-FB66BC7BCE39}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-17e.xlsx
+++ b/quizzes/sculpture-17e.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\éléments à uploader\vers quizzes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D6B354-0AD4-4EEC-A8E4-E22A8F2F33B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5CBDBCF-3168-49BF-AD56-2E9AF389C107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2959,10 +2959,10 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f9/033032598_-_Piacenza_Statue_Equestri_Farnesiane.jpg/1280px-033032598_-_Piacenza_Statue_Equestri_Farnesiane.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f2/%22_Un_cavallo_del_Mochi_%22.jpg/960px-%22_Un_cavallo_del_Mochi_%22.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/37/Piazza_SS_Annunziata_Firenze_Apr_2008.jpg/1280px-Piazza_SS_Annunziata_Firenze_Apr_2008.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/56/Padre_e_figlio_nella_storia.jpg/1280px-Padre_e_figlio_nella_storia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -11046,7 +11046,7 @@
         <v>774</v>
       </c>
       <c r="G143" s="25" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H143" s="28"/>
       <c r="I143" s="30" t="s">
@@ -11899,7 +11899,7 @@
       <c r="P159" s="2"/>
       <c r="Q159" s="2"/>
       <c r="R159" s="2" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="S159" s="2" t="s">
         <v>32</v>
@@ -12419,7 +12419,7 @@
         <v>885</v>
       </c>
       <c r="G169" s="25" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H169" s="2"/>
       <c r="I169" s="7" t="s">
@@ -12838,16 +12838,16 @@
       <c r="S176" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="T176" s="2">
+      <c r="T176" s="5">
         <v>200</v>
       </c>
-      <c r="U176" s="2">
+      <c r="U176" s="5">
         <v>120</v>
       </c>
-      <c r="V176" s="2">
+      <c r="V176" s="5">
         <v>120</v>
       </c>
-      <c r="W176" s="2">
+      <c r="W176" s="5">
         <v>3</v>
       </c>
     </row>
@@ -12895,16 +12895,16 @@
       <c r="S177" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="T177" s="2">
+      <c r="T177" s="5">
         <v>133</v>
       </c>
-      <c r="U177" s="2">
+      <c r="U177" s="5">
         <v>246</v>
       </c>
-      <c r="V177" s="2">
+      <c r="V177" s="5">
         <v>124</v>
       </c>
-      <c r="W177" s="2">
+      <c r="W177" s="5">
         <v>3</v>
       </c>
     </row>
@@ -12948,16 +12948,16 @@
       <c r="S178" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="T178" s="2">
+      <c r="T178" s="5">
         <v>197</v>
       </c>
-      <c r="U178" s="2">
+      <c r="U178" s="5">
         <v>98</v>
       </c>
-      <c r="V178" s="2">
+      <c r="V178" s="5">
         <v>60</v>
       </c>
-      <c r="W178" s="2">
+      <c r="W178" s="5">
         <v>3</v>
       </c>
     </row>
@@ -13000,16 +13000,16 @@
       <c r="S179" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="T179" s="2">
+      <c r="T179" s="5">
         <v>150</v>
       </c>
-      <c r="U179" s="2">
+      <c r="U179" s="5">
         <v>750</v>
       </c>
-      <c r="V179" s="2">
+      <c r="V179" s="5">
         <v>450</v>
       </c>
-      <c r="W179" s="2">
+      <c r="W179" s="5">
         <v>3</v>
       </c>
     </row>
@@ -13050,12 +13050,12 @@
       <c r="S180" s="2" t="s">
         <v>959</v>
       </c>
-      <c r="T180" s="2">
+      <c r="T180" s="5">
         <v>204</v>
       </c>
       <c r="U180" s="21"/>
       <c r="V180" s="21"/>
-      <c r="W180" s="2">
+      <c r="W180" s="5">
         <v>3</v>
       </c>
     </row>
@@ -13287,8 +13287,8 @@
     <hyperlink ref="I117" r:id="rId224" xr:uid="{854BD5A0-A1B1-4398-A5F9-20CD5F69D6B8}"/>
     <hyperlink ref="G117" r:id="rId225" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/24/Bain_des_Nymphes_-_Ch%C3%A2teau_de_Versailles_-_P1050589-P1050594.jpg/1280px-Bain_des_Nymphes_-_Ch%C3%A2teau_de_Versailles_-_P1050589-P1050594.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5582FA22-80A3-4361-855A-DBA8DB99F65D}"/>
     <hyperlink ref="L143" r:id="rId226" xr:uid="{0D537F89-5B9E-43EF-A01B-DD9745C81851}"/>
-    <hyperlink ref="G143" r:id="rId227" xr:uid="{EFAE1AE3-FD24-4F52-B4D3-ACF1021D9576}"/>
-    <hyperlink ref="G169" r:id="rId228" xr:uid="{041EE9DF-84EF-419A-ABDC-FB66BC7BCE39}"/>
+    <hyperlink ref="G169" r:id="rId227" xr:uid="{041EE9DF-84EF-419A-ABDC-FB66BC7BCE39}"/>
+    <hyperlink ref="G143" r:id="rId228" xr:uid="{CEE7C428-4FCE-4D4D-8130-0816DDD88F27}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
